--- a/uploads/warehouse-stock-template.xlsx
+++ b/uploads/warehouse-stock-template.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="101">
   <si>
     <t xml:space="preserve">A — Loose Items (what you count on the shelf)</t>
   </si>
   <si>
-    <t xml:space="preserve">Type in the amber columns only; grey columns work themselves out. Opening Qty is your starting count — everything after it comes from the Movements tab.</t>
+    <t xml:space="preserve">Type in the amber columns only; grey columns work themselves out. Opening Qty is your starting count — everything after it comes from the Movements tab. The three Sold columns say where the stock went: sold loose on its own, gone into a B item, or gone straight into a kit. Opening + Received - the three Sold columns + Adjusted = Stock in Hand.</t>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -48,13 +48,19 @@
     <t xml:space="preserve">Received</t>
   </si>
   <si>
+    <t xml:space="preserve">Sold as A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sold as B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sold as C</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adjusted</t>
   </si>
   <si>
-    <t xml:space="preserve">Used (B items + kits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON HAND</t>
+    <t xml:space="preserve">STOCK IN HAND</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
@@ -106,6 +112,9 @@
   </si>
   <si>
     <t xml:space="preserve">Needed by Kits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON HAND</t>
   </si>
   <si>
     <t xml:space="preserve">Effective Built</t>
@@ -255,7 +264,7 @@
     <t xml:space="preserve">Movements — every stock event</t>
   </si>
   <si>
-    <t xml:space="preserve">The only tab where quantities are typed. Receive = loose stock in (A code). Build = B items assembled (B code). Sell = kits sold (C code). Adjust = correction, damage or recount, signed + or - (A or B code).</t>
+    <t xml:space="preserve">The only tab where quantities are typed. Receive = loose stock in (A code). Build = B items assembled (B code). Sell = sold — a kit (C code) or a loose item sold on its own (A code). Adjust = correction, damage or recount, signed + or - (A or B code).</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -784,17 +793,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -835,16 +844,22 @@
       <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1000</v>
@@ -854,30 +869,38 @@
         <v>500</v>
       </c>
       <c r="F5" s="5" t="n">
+        <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Sell"))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <f aca="false">IF($A5="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A5,Recipes!$B$5:$B$104,"B"))</f>
+        <v>780</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <f aca="false">IF($A5="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A5,Recipes!$B$5:$B$104,"C"))</f>
+        <v>120</v>
+      </c>
+      <c r="I5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>-20</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <f aca="false">IF($A5="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A5))</f>
-        <v>900</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <f aca="false">IF($A5="","",$D5+$E5+$F5-$G5)</f>
+      <c r="J5" s="5" t="n">
+        <f aca="false">IF($A5="","",$D5+$E5-$F5-$G5-$H5+$I5)</f>
         <v>580</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>14</v>
+      <c r="K5" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>60</v>
@@ -887,28 +910,36 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
+        <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Sell"))</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <f aca="false">IF($A6="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A6,Recipes!$B$5:$B$104,"B"))</f>
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <f aca="false">IF($A6="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A6,Recipes!$B$5:$B$104,"C"))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <f aca="false">IF($A6="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A6))</f>
-        <v>22</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <f aca="false">IF($A6="","",$D6+$E6+$F6-$G6)</f>
+      <c r="J6" s="5" t="n">
+        <f aca="false">IF($A6="","",$D6+$E6-$F6-$G6-$H6+$I6)</f>
         <v>38</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>200</v>
@@ -918,28 +949,36 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
+        <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Sell"))</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <f aca="false">IF($A7="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A7,Recipes!$B$5:$B$104,"B"))</f>
+        <v>22</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <f aca="false">IF($A7="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A7,Recipes!$B$5:$B$104,"C"))</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <f aca="false">IF($A7="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A7))</f>
-        <v>22</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <f aca="false">IF($A7="","",$D7+$E7+$F7-$G7)</f>
+      <c r="J7" s="5" t="n">
+        <f aca="false">IF($A7="","",$D7+$E7-$F7-$G7-$H7+$I7)</f>
         <v>178</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>150</v>
@@ -949,28 +988,36 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
+        <f aca="false">IF($A8="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A8,Movements!$B$5:$B$304,"Sell"))</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <f aca="false">IF($A8="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A8,Recipes!$B$5:$B$104,"B"))</f>
+        <v>12</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <f aca="false">IF($A8="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A8,Recipes!$B$5:$B$104,"C"))</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
         <f aca="false">IF($A8="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A8,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <f aca="false">IF($A8="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A8))</f>
-        <v>12</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <f aca="false">IF($A8="","",$D8+$E8+$F8-$G8)</f>
+      <c r="J8" s="5" t="n">
+        <f aca="false">IF($A8="","",$D8+$E8-$F8-$G8-$H8+$I8)</f>
         <v>138</v>
       </c>
-      <c r="I8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>80</v>
@@ -980,18 +1027,26 @@
         <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
+        <f aca="false">IF($A9="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A9,Movements!$B$5:$B$304,"Sell"))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <f aca="false">IF($A9="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A9,Recipes!$B$5:$B$104,"B"))</f>
+        <v>17</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <f aca="false">IF($A9="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A9,Recipes!$B$5:$B$104,"C"))</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="n">
         <f aca="false">IF($A9="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A9,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">IF($A9="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A9))</f>
-        <v>17</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <f aca="false">IF($A9="","",$D9+$E9+$F9-$G9)</f>
+      <c r="J9" s="5" t="n">
+        <f aca="false">IF($A9="","",$D9+$E9-$F9-$G9-$H9+$I9)</f>
         <v>63</v>
       </c>
-      <c r="I9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
@@ -1003,18 +1058,26 @@
         <v/>
       </c>
       <c r="F10" s="5" t="str">
+        <f aca="false">IF($A10="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A10,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="5" t="str">
+        <f aca="false">IF($A10="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A10,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="5" t="str">
+        <f aca="false">IF($A10="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A10,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="5" t="str">
         <f aca="false">IF($A10="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A10,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G10" s="5" t="str">
-        <f aca="false">IF($A10="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A10))</f>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="str">
-        <f aca="false">IF($A10="","",$D10+$E10+$F10-$G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="4"/>
+      <c r="J10" s="5" t="str">
+        <f aca="false">IF($A10="","",$D10+$E10-$F10-$G10-$H10+$I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
@@ -1026,18 +1089,26 @@
         <v/>
       </c>
       <c r="F11" s="5" t="str">
+        <f aca="false">IF($A11="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A11,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="5" t="str">
+        <f aca="false">IF($A11="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A11,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="5" t="str">
+        <f aca="false">IF($A11="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A11,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="5" t="str">
         <f aca="false">IF($A11="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A11,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G11" s="5" t="str">
-        <f aca="false">IF($A11="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A11))</f>
-        <v/>
-      </c>
-      <c r="H11" s="5" t="str">
-        <f aca="false">IF($A11="","",$D11+$E11+$F11-$G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="4"/>
+      <c r="J11" s="5" t="str">
+        <f aca="false">IF($A11="","",$D11+$E11-$F11-$G11-$H11+$I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -1049,18 +1120,26 @@
         <v/>
       </c>
       <c r="F12" s="5" t="str">
+        <f aca="false">IF($A12="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A12,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="5" t="str">
+        <f aca="false">IF($A12="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A12,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="5" t="str">
+        <f aca="false">IF($A12="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A12,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="5" t="str">
         <f aca="false">IF($A12="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A12,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G12" s="5" t="str">
-        <f aca="false">IF($A12="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A12))</f>
-        <v/>
-      </c>
-      <c r="H12" s="5" t="str">
-        <f aca="false">IF($A12="","",$D12+$E12+$F12-$G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="4"/>
+      <c r="J12" s="5" t="str">
+        <f aca="false">IF($A12="","",$D12+$E12-$F12-$G12-$H12+$I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
@@ -1072,18 +1151,26 @@
         <v/>
       </c>
       <c r="F13" s="5" t="str">
+        <f aca="false">IF($A13="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A13,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="5" t="str">
+        <f aca="false">IF($A13="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A13,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="5" t="str">
+        <f aca="false">IF($A13="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A13,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="5" t="str">
         <f aca="false">IF($A13="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A13,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G13" s="5" t="str">
-        <f aca="false">IF($A13="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="5" t="str">
-        <f aca="false">IF($A13="","",$D13+$E13+$F13-$G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="4"/>
+      <c r="J13" s="5" t="str">
+        <f aca="false">IF($A13="","",$D13+$E13-$F13-$G13-$H13+$I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
@@ -1095,18 +1182,26 @@
         <v/>
       </c>
       <c r="F14" s="5" t="str">
+        <f aca="false">IF($A14="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A14,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="5" t="str">
+        <f aca="false">IF($A14="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A14,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="5" t="str">
+        <f aca="false">IF($A14="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A14,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="5" t="str">
         <f aca="false">IF($A14="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A14,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G14" s="5" t="str">
-        <f aca="false">IF($A14="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A14))</f>
-        <v/>
-      </c>
-      <c r="H14" s="5" t="str">
-        <f aca="false">IF($A14="","",$D14+$E14+$F14-$G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="4"/>
+      <c r="J14" s="5" t="str">
+        <f aca="false">IF($A14="","",$D14+$E14-$F14-$G14-$H14+$I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
@@ -1118,18 +1213,26 @@
         <v/>
       </c>
       <c r="F15" s="5" t="str">
+        <f aca="false">IF($A15="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A15,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="5" t="str">
+        <f aca="false">IF($A15="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A15,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="5" t="str">
+        <f aca="false">IF($A15="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A15,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="5" t="str">
         <f aca="false">IF($A15="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A15,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G15" s="5" t="str">
-        <f aca="false">IF($A15="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A15))</f>
-        <v/>
-      </c>
-      <c r="H15" s="5" t="str">
-        <f aca="false">IF($A15="","",$D15+$E15+$F15-$G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="4"/>
+      <c r="J15" s="5" t="str">
+        <f aca="false">IF($A15="","",$D15+$E15-$F15-$G15-$H15+$I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
@@ -1141,18 +1244,26 @@
         <v/>
       </c>
       <c r="F16" s="5" t="str">
+        <f aca="false">IF($A16="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A16,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="5" t="str">
+        <f aca="false">IF($A16="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A16,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="5" t="str">
+        <f aca="false">IF($A16="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A16,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="5" t="str">
         <f aca="false">IF($A16="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A16,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G16" s="5" t="str">
-        <f aca="false">IF($A16="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="5" t="str">
-        <f aca="false">IF($A16="","",$D16+$E16+$F16-$G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="4"/>
+      <c r="J16" s="5" t="str">
+        <f aca="false">IF($A16="","",$D16+$E16-$F16-$G16-$H16+$I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
@@ -1164,18 +1275,26 @@
         <v/>
       </c>
       <c r="F17" s="5" t="str">
+        <f aca="false">IF($A17="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A17,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="5" t="str">
+        <f aca="false">IF($A17="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A17,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF($A17="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A17,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="5" t="str">
         <f aca="false">IF($A17="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A17,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF($A17="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="5" t="str">
-        <f aca="false">IF($A17="","",$D17+$E17+$F17-$G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="4"/>
+      <c r="J17" s="5" t="str">
+        <f aca="false">IF($A17="","",$D17+$E17-$F17-$G17-$H17+$I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
@@ -1187,18 +1306,26 @@
         <v/>
       </c>
       <c r="F18" s="5" t="str">
+        <f aca="false">IF($A18="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A18,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="5" t="str">
+        <f aca="false">IF($A18="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A18,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="5" t="str">
+        <f aca="false">IF($A18="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A18,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="5" t="str">
         <f aca="false">IF($A18="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A18,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G18" s="5" t="str">
-        <f aca="false">IF($A18="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="5" t="str">
-        <f aca="false">IF($A18="","",$D18+$E18+$F18-$G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="4"/>
+      <c r="J18" s="5" t="str">
+        <f aca="false">IF($A18="","",$D18+$E18-$F18-$G18-$H18+$I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
@@ -1210,18 +1337,26 @@
         <v/>
       </c>
       <c r="F19" s="5" t="str">
+        <f aca="false">IF($A19="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A19,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="5" t="str">
+        <f aca="false">IF($A19="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A19,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF($A19="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A19,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="5" t="str">
         <f aca="false">IF($A19="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A19,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF($A19="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="5" t="str">
-        <f aca="false">IF($A19="","",$D19+$E19+$F19-$G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="4"/>
+      <c r="J19" s="5" t="str">
+        <f aca="false">IF($A19="","",$D19+$E19-$F19-$G19-$H19+$I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
@@ -1233,18 +1368,26 @@
         <v/>
       </c>
       <c r="F20" s="5" t="str">
+        <f aca="false">IF($A20="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A20,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="5" t="str">
+        <f aca="false">IF($A20="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A20,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="5" t="str">
+        <f aca="false">IF($A20="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A20,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I20" s="5" t="str">
         <f aca="false">IF($A20="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A20,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G20" s="5" t="str">
-        <f aca="false">IF($A20="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A20))</f>
-        <v/>
-      </c>
-      <c r="H20" s="5" t="str">
-        <f aca="false">IF($A20="","",$D20+$E20+$F20-$G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="4"/>
+      <c r="J20" s="5" t="str">
+        <f aca="false">IF($A20="","",$D20+$E20-$F20-$G20-$H20+$I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
@@ -1256,18 +1399,26 @@
         <v/>
       </c>
       <c r="F21" s="5" t="str">
+        <f aca="false">IF($A21="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A21,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G21" s="5" t="str">
+        <f aca="false">IF($A21="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A21,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="5" t="str">
+        <f aca="false">IF($A21="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A21,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I21" s="5" t="str">
         <f aca="false">IF($A21="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A21,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G21" s="5" t="str">
-        <f aca="false">IF($A21="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A21))</f>
-        <v/>
-      </c>
-      <c r="H21" s="5" t="str">
-        <f aca="false">IF($A21="","",$D21+$E21+$F21-$G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="4"/>
+      <c r="J21" s="5" t="str">
+        <f aca="false">IF($A21="","",$D21+$E21-$F21-$G21-$H21+$I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
@@ -1279,18 +1430,26 @@
         <v/>
       </c>
       <c r="F22" s="5" t="str">
+        <f aca="false">IF($A22="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A22,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="5" t="str">
+        <f aca="false">IF($A22="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A22,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H22" s="5" t="str">
+        <f aca="false">IF($A22="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A22,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I22" s="5" t="str">
         <f aca="false">IF($A22="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A22,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G22" s="5" t="str">
-        <f aca="false">IF($A22="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A22))</f>
-        <v/>
-      </c>
-      <c r="H22" s="5" t="str">
-        <f aca="false">IF($A22="","",$D22+$E22+$F22-$G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="4"/>
+      <c r="J22" s="5" t="str">
+        <f aca="false">IF($A22="","",$D22+$E22-$F22-$G22-$H22+$I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
@@ -1302,18 +1461,26 @@
         <v/>
       </c>
       <c r="F23" s="5" t="str">
+        <f aca="false">IF($A23="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A23,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="5" t="str">
+        <f aca="false">IF($A23="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A23,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF($A23="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A23,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I23" s="5" t="str">
         <f aca="false">IF($A23="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A23,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF($A23="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A23))</f>
-        <v/>
-      </c>
-      <c r="H23" s="5" t="str">
-        <f aca="false">IF($A23="","",$D23+$E23+$F23-$G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="4"/>
+      <c r="J23" s="5" t="str">
+        <f aca="false">IF($A23="","",$D23+$E23-$F23-$G23-$H23+$I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1325,18 +1492,26 @@
         <v/>
       </c>
       <c r="F24" s="5" t="str">
+        <f aca="false">IF($A24="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A24,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="5" t="str">
+        <f aca="false">IF($A24="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A24,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H24" s="5" t="str">
+        <f aca="false">IF($A24="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A24,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="5" t="str">
         <f aca="false">IF($A24="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A24,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G24" s="5" t="str">
-        <f aca="false">IF($A24="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A24))</f>
-        <v/>
-      </c>
-      <c r="H24" s="5" t="str">
-        <f aca="false">IF($A24="","",$D24+$E24+$F24-$G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="4"/>
+      <c r="J24" s="5" t="str">
+        <f aca="false">IF($A24="","",$D24+$E24-$F24-$G24-$H24+$I24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
@@ -1348,18 +1523,26 @@
         <v/>
       </c>
       <c r="F25" s="5" t="str">
+        <f aca="false">IF($A25="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A25,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="5" t="str">
+        <f aca="false">IF($A25="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A25,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF($A25="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A25,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="5" t="str">
         <f aca="false">IF($A25="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A25,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF($A25="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A25))</f>
-        <v/>
-      </c>
-      <c r="H25" s="5" t="str">
-        <f aca="false">IF($A25="","",$D25+$E25+$F25-$G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="4"/>
+      <c r="J25" s="5" t="str">
+        <f aca="false">IF($A25="","",$D25+$E25-$F25-$G25-$H25+$I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -1371,18 +1554,26 @@
         <v/>
       </c>
       <c r="F26" s="5" t="str">
+        <f aca="false">IF($A26="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A26,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G26" s="5" t="str">
+        <f aca="false">IF($A26="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A26,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H26" s="5" t="str">
+        <f aca="false">IF($A26="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A26,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I26" s="5" t="str">
         <f aca="false">IF($A26="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A26,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G26" s="5" t="str">
-        <f aca="false">IF($A26="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A26))</f>
-        <v/>
-      </c>
-      <c r="H26" s="5" t="str">
-        <f aca="false">IF($A26="","",$D26+$E26+$F26-$G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="4"/>
+      <c r="J26" s="5" t="str">
+        <f aca="false">IF($A26="","",$D26+$E26-$F26-$G26-$H26+$I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
@@ -1394,18 +1585,26 @@
         <v/>
       </c>
       <c r="F27" s="5" t="str">
+        <f aca="false">IF($A27="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A27,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G27" s="5" t="str">
+        <f aca="false">IF($A27="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A27,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H27" s="5" t="str">
+        <f aca="false">IF($A27="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A27,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I27" s="5" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A27,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G27" s="5" t="str">
-        <f aca="false">IF($A27="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A27))</f>
-        <v/>
-      </c>
-      <c r="H27" s="5" t="str">
-        <f aca="false">IF($A27="","",$D27+$E27+$F27-$G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="4"/>
+      <c r="J27" s="5" t="str">
+        <f aca="false">IF($A27="","",$D27+$E27-$F27-$G27-$H27+$I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -1417,18 +1616,26 @@
         <v/>
       </c>
       <c r="F28" s="5" t="str">
+        <f aca="false">IF($A28="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A28,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G28" s="5" t="str">
+        <f aca="false">IF($A28="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A28,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H28" s="5" t="str">
+        <f aca="false">IF($A28="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A28,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I28" s="5" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A28,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G28" s="5" t="str">
-        <f aca="false">IF($A28="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A28))</f>
-        <v/>
-      </c>
-      <c r="H28" s="5" t="str">
-        <f aca="false">IF($A28="","",$D28+$E28+$F28-$G28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="4"/>
+      <c r="J28" s="5" t="str">
+        <f aca="false">IF($A28="","",$D28+$E28-$F28-$G28-$H28+$I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
@@ -1440,18 +1647,26 @@
         <v/>
       </c>
       <c r="F29" s="5" t="str">
+        <f aca="false">IF($A29="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A29,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="5" t="str">
+        <f aca="false">IF($A29="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A29,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H29" s="5" t="str">
+        <f aca="false">IF($A29="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A29,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I29" s="5" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A29,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G29" s="5" t="str">
-        <f aca="false">IF($A29="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A29))</f>
-        <v/>
-      </c>
-      <c r="H29" s="5" t="str">
-        <f aca="false">IF($A29="","",$D29+$E29+$F29-$G29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="4"/>
+      <c r="J29" s="5" t="str">
+        <f aca="false">IF($A29="","",$D29+$E29-$F29-$G29-$H29+$I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -1463,18 +1678,26 @@
         <v/>
       </c>
       <c r="F30" s="5" t="str">
+        <f aca="false">IF($A30="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A30,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="5" t="str">
+        <f aca="false">IF($A30="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A30,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H30" s="5" t="str">
+        <f aca="false">IF($A30="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A30,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I30" s="5" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A30,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G30" s="5" t="str">
-        <f aca="false">IF($A30="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A30))</f>
-        <v/>
-      </c>
-      <c r="H30" s="5" t="str">
-        <f aca="false">IF($A30="","",$D30+$E30+$F30-$G30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="4"/>
+      <c r="J30" s="5" t="str">
+        <f aca="false">IF($A30="","",$D30+$E30-$F30-$G30-$H30+$I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
@@ -1486,18 +1709,26 @@
         <v/>
       </c>
       <c r="F31" s="5" t="str">
+        <f aca="false">IF($A31="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A31,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="5" t="str">
+        <f aca="false">IF($A31="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A31,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="5" t="str">
+        <f aca="false">IF($A31="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A31,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I31" s="5" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A31,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G31" s="5" t="str">
-        <f aca="false">IF($A31="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A31))</f>
-        <v/>
-      </c>
-      <c r="H31" s="5" t="str">
-        <f aca="false">IF($A31="","",$D31+$E31+$F31-$G31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="4"/>
+      <c r="J31" s="5" t="str">
+        <f aca="false">IF($A31="","",$D31+$E31-$F31-$G31-$H31+$I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
@@ -1509,18 +1740,26 @@
         <v/>
       </c>
       <c r="F32" s="5" t="str">
+        <f aca="false">IF($A32="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A32,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="5" t="str">
+        <f aca="false">IF($A32="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A32,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H32" s="5" t="str">
+        <f aca="false">IF($A32="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A32,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="5" t="str">
         <f aca="false">IF($A32="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A32,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G32" s="5" t="str">
-        <f aca="false">IF($A32="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A32))</f>
-        <v/>
-      </c>
-      <c r="H32" s="5" t="str">
-        <f aca="false">IF($A32="","",$D32+$E32+$F32-$G32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="4"/>
+      <c r="J32" s="5" t="str">
+        <f aca="false">IF($A32="","",$D32+$E32-$F32-$G32-$H32+$I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
@@ -1532,18 +1771,26 @@
         <v/>
       </c>
       <c r="F33" s="5" t="str">
+        <f aca="false">IF($A33="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A33,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G33" s="5" t="str">
+        <f aca="false">IF($A33="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A33,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H33" s="5" t="str">
+        <f aca="false">IF($A33="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A33,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="5" t="str">
         <f aca="false">IF($A33="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A33,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G33" s="5" t="str">
-        <f aca="false">IF($A33="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A33))</f>
-        <v/>
-      </c>
-      <c r="H33" s="5" t="str">
-        <f aca="false">IF($A33="","",$D33+$E33+$F33-$G33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="4"/>
+      <c r="J33" s="5" t="str">
+        <f aca="false">IF($A33="","",$D33+$E33-$F33-$G33-$H33+$I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -1555,18 +1802,26 @@
         <v/>
       </c>
       <c r="F34" s="5" t="str">
+        <f aca="false">IF($A34="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A34,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f aca="false">IF($A34="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A34,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H34" s="5" t="str">
+        <f aca="false">IF($A34="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A34,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="5" t="str">
         <f aca="false">IF($A34="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A34,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G34" s="5" t="str">
-        <f aca="false">IF($A34="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="5" t="str">
-        <f aca="false">IF($A34="","",$D34+$E34+$F34-$G34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="4"/>
+      <c r="J34" s="5" t="str">
+        <f aca="false">IF($A34="","",$D34+$E34-$F34-$G34-$H34+$I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
@@ -1578,18 +1833,26 @@
         <v/>
       </c>
       <c r="F35" s="5" t="str">
+        <f aca="false">IF($A35="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A35,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="5" t="str">
+        <f aca="false">IF($A35="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A35,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H35" s="5" t="str">
+        <f aca="false">IF($A35="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A35,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="5" t="str">
         <f aca="false">IF($A35="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A35,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G35" s="5" t="str">
-        <f aca="false">IF($A35="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A35))</f>
-        <v/>
-      </c>
-      <c r="H35" s="5" t="str">
-        <f aca="false">IF($A35="","",$D35+$E35+$F35-$G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="4"/>
+      <c r="J35" s="5" t="str">
+        <f aca="false">IF($A35="","",$D35+$E35-$F35-$G35-$H35+$I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
@@ -1601,18 +1864,26 @@
         <v/>
       </c>
       <c r="F36" s="5" t="str">
+        <f aca="false">IF($A36="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A36,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="5" t="str">
+        <f aca="false">IF($A36="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A36,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H36" s="5" t="str">
+        <f aca="false">IF($A36="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A36,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I36" s="5" t="str">
         <f aca="false">IF($A36="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A36,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G36" s="5" t="str">
-        <f aca="false">IF($A36="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A36))</f>
-        <v/>
-      </c>
-      <c r="H36" s="5" t="str">
-        <f aca="false">IF($A36="","",$D36+$E36+$F36-$G36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="4"/>
+      <c r="J36" s="5" t="str">
+        <f aca="false">IF($A36="","",$D36+$E36-$F36-$G36-$H36+$I36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
@@ -1624,18 +1895,26 @@
         <v/>
       </c>
       <c r="F37" s="5" t="str">
+        <f aca="false">IF($A37="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A37,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="5" t="str">
+        <f aca="false">IF($A37="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A37,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H37" s="5" t="str">
+        <f aca="false">IF($A37="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A37,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I37" s="5" t="str">
         <f aca="false">IF($A37="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A37,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G37" s="5" t="str">
-        <f aca="false">IF($A37="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A37))</f>
-        <v/>
-      </c>
-      <c r="H37" s="5" t="str">
-        <f aca="false">IF($A37="","",$D37+$E37+$F37-$G37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="4"/>
+      <c r="J37" s="5" t="str">
+        <f aca="false">IF($A37="","",$D37+$E37-$F37-$G37-$H37+$I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
@@ -1647,18 +1926,26 @@
         <v/>
       </c>
       <c r="F38" s="5" t="str">
+        <f aca="false">IF($A38="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A38,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="5" t="str">
+        <f aca="false">IF($A38="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A38,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H38" s="5" t="str">
+        <f aca="false">IF($A38="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A38,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I38" s="5" t="str">
         <f aca="false">IF($A38="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A38,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G38" s="5" t="str">
-        <f aca="false">IF($A38="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A38))</f>
-        <v/>
-      </c>
-      <c r="H38" s="5" t="str">
-        <f aca="false">IF($A38="","",$D38+$E38+$F38-$G38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="4"/>
+      <c r="J38" s="5" t="str">
+        <f aca="false">IF($A38="","",$D38+$E38-$F38-$G38-$H38+$I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
@@ -1670,18 +1957,26 @@
         <v/>
       </c>
       <c r="F39" s="5" t="str">
+        <f aca="false">IF($A39="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A39,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="5" t="str">
+        <f aca="false">IF($A39="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A39,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H39" s="5" t="str">
+        <f aca="false">IF($A39="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A39,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I39" s="5" t="str">
         <f aca="false">IF($A39="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A39,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G39" s="5" t="str">
-        <f aca="false">IF($A39="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A39))</f>
-        <v/>
-      </c>
-      <c r="H39" s="5" t="str">
-        <f aca="false">IF($A39="","",$D39+$E39+$F39-$G39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="4"/>
+      <c r="J39" s="5" t="str">
+        <f aca="false">IF($A39="","",$D39+$E39-$F39-$G39-$H39+$I39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
@@ -1693,18 +1988,26 @@
         <v/>
       </c>
       <c r="F40" s="5" t="str">
+        <f aca="false">IF($A40="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A40,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="5" t="str">
+        <f aca="false">IF($A40="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A40,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H40" s="5" t="str">
+        <f aca="false">IF($A40="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A40,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I40" s="5" t="str">
         <f aca="false">IF($A40="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A40,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G40" s="5" t="str">
-        <f aca="false">IF($A40="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A40))</f>
-        <v/>
-      </c>
-      <c r="H40" s="5" t="str">
-        <f aca="false">IF($A40="","",$D40+$E40+$F40-$G40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="4"/>
+      <c r="J40" s="5" t="str">
+        <f aca="false">IF($A40="","",$D40+$E40-$F40-$G40-$H40+$I40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
@@ -1716,18 +2019,26 @@
         <v/>
       </c>
       <c r="F41" s="5" t="str">
+        <f aca="false">IF($A41="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A41,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="5" t="str">
+        <f aca="false">IF($A41="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A41,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H41" s="5" t="str">
+        <f aca="false">IF($A41="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A41,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I41" s="5" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A41,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G41" s="5" t="str">
-        <f aca="false">IF($A41="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A41))</f>
-        <v/>
-      </c>
-      <c r="H41" s="5" t="str">
-        <f aca="false">IF($A41="","",$D41+$E41+$F41-$G41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="4"/>
+      <c r="J41" s="5" t="str">
+        <f aca="false">IF($A41="","",$D41+$E41-$F41-$G41-$H41+$I41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
@@ -1739,18 +2050,26 @@
         <v/>
       </c>
       <c r="F42" s="5" t="str">
+        <f aca="false">IF($A42="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A42,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="5" t="str">
+        <f aca="false">IF($A42="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A42,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H42" s="5" t="str">
+        <f aca="false">IF($A42="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A42,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I42" s="5" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A42,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G42" s="5" t="str">
-        <f aca="false">IF($A42="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A42))</f>
-        <v/>
-      </c>
-      <c r="H42" s="5" t="str">
-        <f aca="false">IF($A42="","",$D42+$E42+$F42-$G42)</f>
-        <v/>
-      </c>
-      <c r="I42" s="4"/>
+      <c r="J42" s="5" t="str">
+        <f aca="false">IF($A42="","",$D42+$E42-$F42-$G42-$H42+$I42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
@@ -1762,18 +2081,26 @@
         <v/>
       </c>
       <c r="F43" s="5" t="str">
+        <f aca="false">IF($A43="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A43,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="5" t="str">
+        <f aca="false">IF($A43="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A43,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H43" s="5" t="str">
+        <f aca="false">IF($A43="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A43,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I43" s="5" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A43,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G43" s="5" t="str">
-        <f aca="false">IF($A43="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A43))</f>
-        <v/>
-      </c>
-      <c r="H43" s="5" t="str">
-        <f aca="false">IF($A43="","",$D43+$E43+$F43-$G43)</f>
-        <v/>
-      </c>
-      <c r="I43" s="4"/>
+      <c r="J43" s="5" t="str">
+        <f aca="false">IF($A43="","",$D43+$E43-$F43-$G43-$H43+$I43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
@@ -1785,18 +2112,26 @@
         <v/>
       </c>
       <c r="F44" s="5" t="str">
+        <f aca="false">IF($A44="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A44,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="5" t="str">
+        <f aca="false">IF($A44="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A44,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H44" s="5" t="str">
+        <f aca="false">IF($A44="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A44,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I44" s="5" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A44,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G44" s="5" t="str">
-        <f aca="false">IF($A44="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A44))</f>
-        <v/>
-      </c>
-      <c r="H44" s="5" t="str">
-        <f aca="false">IF($A44="","",$D44+$E44+$F44-$G44)</f>
-        <v/>
-      </c>
-      <c r="I44" s="4"/>
+      <c r="J44" s="5" t="str">
+        <f aca="false">IF($A44="","",$D44+$E44-$F44-$G44-$H44+$I44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
@@ -1808,18 +2143,26 @@
         <v/>
       </c>
       <c r="F45" s="5" t="str">
+        <f aca="false">IF($A45="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A45,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="5" t="str">
+        <f aca="false">IF($A45="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A45,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H45" s="5" t="str">
+        <f aca="false">IF($A45="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A45,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I45" s="5" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A45,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G45" s="5" t="str">
-        <f aca="false">IF($A45="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A45))</f>
-        <v/>
-      </c>
-      <c r="H45" s="5" t="str">
-        <f aca="false">IF($A45="","",$D45+$E45+$F45-$G45)</f>
-        <v/>
-      </c>
-      <c r="I45" s="4"/>
+      <c r="J45" s="5" t="str">
+        <f aca="false">IF($A45="","",$D45+$E45-$F45-$G45-$H45+$I45)</f>
+        <v/>
+      </c>
+      <c r="K45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
@@ -1831,18 +2174,26 @@
         <v/>
       </c>
       <c r="F46" s="5" t="str">
+        <f aca="false">IF($A46="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A46,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="5" t="str">
+        <f aca="false">IF($A46="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A46,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H46" s="5" t="str">
+        <f aca="false">IF($A46="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A46,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I46" s="5" t="str">
         <f aca="false">IF($A46="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A46,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G46" s="5" t="str">
-        <f aca="false">IF($A46="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A46))</f>
-        <v/>
-      </c>
-      <c r="H46" s="5" t="str">
-        <f aca="false">IF($A46="","",$D46+$E46+$F46-$G46)</f>
-        <v/>
-      </c>
-      <c r="I46" s="4"/>
+      <c r="J46" s="5" t="str">
+        <f aca="false">IF($A46="","",$D46+$E46-$F46-$G46-$H46+$I46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4"/>
@@ -1854,18 +2205,26 @@
         <v/>
       </c>
       <c r="F47" s="5" t="str">
+        <f aca="false">IF($A47="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A47,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="5" t="str">
+        <f aca="false">IF($A47="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A47,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H47" s="5" t="str">
+        <f aca="false">IF($A47="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A47,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I47" s="5" t="str">
         <f aca="false">IF($A47="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A47,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G47" s="5" t="str">
-        <f aca="false">IF($A47="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A47))</f>
-        <v/>
-      </c>
-      <c r="H47" s="5" t="str">
-        <f aca="false">IF($A47="","",$D47+$E47+$F47-$G47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="4"/>
+      <c r="J47" s="5" t="str">
+        <f aca="false">IF($A47="","",$D47+$E47-$F47-$G47-$H47+$I47)</f>
+        <v/>
+      </c>
+      <c r="K47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4"/>
@@ -1877,18 +2236,26 @@
         <v/>
       </c>
       <c r="F48" s="5" t="str">
+        <f aca="false">IF($A48="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A48,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="5" t="str">
+        <f aca="false">IF($A48="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A48,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H48" s="5" t="str">
+        <f aca="false">IF($A48="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A48,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I48" s="5" t="str">
         <f aca="false">IF($A48="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A48,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G48" s="5" t="str">
-        <f aca="false">IF($A48="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A48))</f>
-        <v/>
-      </c>
-      <c r="H48" s="5" t="str">
-        <f aca="false">IF($A48="","",$D48+$E48+$F48-$G48)</f>
-        <v/>
-      </c>
-      <c r="I48" s="4"/>
+      <c r="J48" s="5" t="str">
+        <f aca="false">IF($A48="","",$D48+$E48-$F48-$G48-$H48+$I48)</f>
+        <v/>
+      </c>
+      <c r="K48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4"/>
@@ -1900,18 +2267,26 @@
         <v/>
       </c>
       <c r="F49" s="5" t="str">
+        <f aca="false">IF($A49="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A49,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="5" t="str">
+        <f aca="false">IF($A49="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A49,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H49" s="5" t="str">
+        <f aca="false">IF($A49="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A49,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I49" s="5" t="str">
         <f aca="false">IF($A49="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A49,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G49" s="5" t="str">
-        <f aca="false">IF($A49="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A49))</f>
-        <v/>
-      </c>
-      <c r="H49" s="5" t="str">
-        <f aca="false">IF($A49="","",$D49+$E49+$F49-$G49)</f>
-        <v/>
-      </c>
-      <c r="I49" s="4"/>
+      <c r="J49" s="5" t="str">
+        <f aca="false">IF($A49="","",$D49+$E49-$F49-$G49-$H49+$I49)</f>
+        <v/>
+      </c>
+      <c r="K49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4"/>
@@ -1923,18 +2298,26 @@
         <v/>
       </c>
       <c r="F50" s="5" t="str">
+        <f aca="false">IF($A50="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A50,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="5" t="str">
+        <f aca="false">IF($A50="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A50,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H50" s="5" t="str">
+        <f aca="false">IF($A50="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A50,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I50" s="5" t="str">
         <f aca="false">IF($A50="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A50,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G50" s="5" t="str">
-        <f aca="false">IF($A50="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A50))</f>
-        <v/>
-      </c>
-      <c r="H50" s="5" t="str">
-        <f aca="false">IF($A50="","",$D50+$E50+$F50-$G50)</f>
-        <v/>
-      </c>
-      <c r="I50" s="4"/>
+      <c r="J50" s="5" t="str">
+        <f aca="false">IF($A50="","",$D50+$E50-$F50-$G50-$H50+$I50)</f>
+        <v/>
+      </c>
+      <c r="K50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4"/>
@@ -1946,18 +2329,26 @@
         <v/>
       </c>
       <c r="F51" s="5" t="str">
+        <f aca="false">IF($A51="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A51,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="5" t="str">
+        <f aca="false">IF($A51="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A51,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H51" s="5" t="str">
+        <f aca="false">IF($A51="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A51,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I51" s="5" t="str">
         <f aca="false">IF($A51="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A51,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G51" s="5" t="str">
-        <f aca="false">IF($A51="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A51))</f>
-        <v/>
-      </c>
-      <c r="H51" s="5" t="str">
-        <f aca="false">IF($A51="","",$D51+$E51+$F51-$G51)</f>
-        <v/>
-      </c>
-      <c r="I51" s="4"/>
+      <c r="J51" s="5" t="str">
+        <f aca="false">IF($A51="","",$D51+$E51-$F51-$G51-$H51+$I51)</f>
+        <v/>
+      </c>
+      <c r="K51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4"/>
@@ -1969,18 +2360,26 @@
         <v/>
       </c>
       <c r="F52" s="5" t="str">
+        <f aca="false">IF($A52="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A52,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="5" t="str">
+        <f aca="false">IF($A52="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A52,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H52" s="5" t="str">
+        <f aca="false">IF($A52="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A52,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I52" s="5" t="str">
         <f aca="false">IF($A52="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A52,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G52" s="5" t="str">
-        <f aca="false">IF($A52="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A52))</f>
-        <v/>
-      </c>
-      <c r="H52" s="5" t="str">
-        <f aca="false">IF($A52="","",$D52+$E52+$F52-$G52)</f>
-        <v/>
-      </c>
-      <c r="I52" s="4"/>
+      <c r="J52" s="5" t="str">
+        <f aca="false">IF($A52="","",$D52+$E52-$F52-$G52-$H52+$I52)</f>
+        <v/>
+      </c>
+      <c r="K52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4"/>
@@ -1992,18 +2391,26 @@
         <v/>
       </c>
       <c r="F53" s="5" t="str">
+        <f aca="false">IF($A53="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A53,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="5" t="str">
+        <f aca="false">IF($A53="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A53,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H53" s="5" t="str">
+        <f aca="false">IF($A53="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A53,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I53" s="5" t="str">
         <f aca="false">IF($A53="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A53,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G53" s="5" t="str">
-        <f aca="false">IF($A53="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A53))</f>
-        <v/>
-      </c>
-      <c r="H53" s="5" t="str">
-        <f aca="false">IF($A53="","",$D53+$E53+$F53-$G53)</f>
-        <v/>
-      </c>
-      <c r="I53" s="4"/>
+      <c r="J53" s="5" t="str">
+        <f aca="false">IF($A53="","",$D53+$E53-$F53-$G53-$H53+$I53)</f>
+        <v/>
+      </c>
+      <c r="K53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4"/>
@@ -2015,18 +2422,26 @@
         <v/>
       </c>
       <c r="F54" s="5" t="str">
+        <f aca="false">IF($A54="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A54,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="5" t="str">
+        <f aca="false">IF($A54="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A54,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H54" s="5" t="str">
+        <f aca="false">IF($A54="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A54,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I54" s="5" t="str">
         <f aca="false">IF($A54="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A54,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G54" s="5" t="str">
-        <f aca="false">IF($A54="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A54))</f>
-        <v/>
-      </c>
-      <c r="H54" s="5" t="str">
-        <f aca="false">IF($A54="","",$D54+$E54+$F54-$G54)</f>
-        <v/>
-      </c>
-      <c r="I54" s="4"/>
+      <c r="J54" s="5" t="str">
+        <f aca="false">IF($A54="","",$D54+$E54-$F54-$G54-$H54+$I54)</f>
+        <v/>
+      </c>
+      <c r="K54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4"/>
@@ -2038,18 +2453,26 @@
         <v/>
       </c>
       <c r="F55" s="5" t="str">
+        <f aca="false">IF($A55="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A55,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="5" t="str">
+        <f aca="false">IF($A55="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A55,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H55" s="5" t="str">
+        <f aca="false">IF($A55="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A55,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I55" s="5" t="str">
         <f aca="false">IF($A55="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A55,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G55" s="5" t="str">
-        <f aca="false">IF($A55="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A55))</f>
-        <v/>
-      </c>
-      <c r="H55" s="5" t="str">
-        <f aca="false">IF($A55="","",$D55+$E55+$F55-$G55)</f>
-        <v/>
-      </c>
-      <c r="I55" s="4"/>
+      <c r="J55" s="5" t="str">
+        <f aca="false">IF($A55="","",$D55+$E55-$F55-$G55-$H55+$I55)</f>
+        <v/>
+      </c>
+      <c r="K55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4"/>
@@ -2061,18 +2484,26 @@
         <v/>
       </c>
       <c r="F56" s="5" t="str">
+        <f aca="false">IF($A56="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A56,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G56" s="5" t="str">
+        <f aca="false">IF($A56="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A56,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H56" s="5" t="str">
+        <f aca="false">IF($A56="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A56,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I56" s="5" t="str">
         <f aca="false">IF($A56="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A56,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G56" s="5" t="str">
-        <f aca="false">IF($A56="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A56))</f>
-        <v/>
-      </c>
-      <c r="H56" s="5" t="str">
-        <f aca="false">IF($A56="","",$D56+$E56+$F56-$G56)</f>
-        <v/>
-      </c>
-      <c r="I56" s="4"/>
+      <c r="J56" s="5" t="str">
+        <f aca="false">IF($A56="","",$D56+$E56-$F56-$G56-$H56+$I56)</f>
+        <v/>
+      </c>
+      <c r="K56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4"/>
@@ -2084,18 +2515,26 @@
         <v/>
       </c>
       <c r="F57" s="5" t="str">
+        <f aca="false">IF($A57="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A57,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G57" s="5" t="str">
+        <f aca="false">IF($A57="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A57,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H57" s="5" t="str">
+        <f aca="false">IF($A57="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A57,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I57" s="5" t="str">
         <f aca="false">IF($A57="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A57,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G57" s="5" t="str">
-        <f aca="false">IF($A57="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A57))</f>
-        <v/>
-      </c>
-      <c r="H57" s="5" t="str">
-        <f aca="false">IF($A57="","",$D57+$E57+$F57-$G57)</f>
-        <v/>
-      </c>
-      <c r="I57" s="4"/>
+      <c r="J57" s="5" t="str">
+        <f aca="false">IF($A57="","",$D57+$E57-$F57-$G57-$H57+$I57)</f>
+        <v/>
+      </c>
+      <c r="K57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4"/>
@@ -2107,18 +2546,26 @@
         <v/>
       </c>
       <c r="F58" s="5" t="str">
+        <f aca="false">IF($A58="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A58,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="5" t="str">
+        <f aca="false">IF($A58="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A58,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H58" s="5" t="str">
+        <f aca="false">IF($A58="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A58,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I58" s="5" t="str">
         <f aca="false">IF($A58="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A58,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G58" s="5" t="str">
-        <f aca="false">IF($A58="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A58))</f>
-        <v/>
-      </c>
-      <c r="H58" s="5" t="str">
-        <f aca="false">IF($A58="","",$D58+$E58+$F58-$G58)</f>
-        <v/>
-      </c>
-      <c r="I58" s="4"/>
+      <c r="J58" s="5" t="str">
+        <f aca="false">IF($A58="","",$D58+$E58-$F58-$G58-$H58+$I58)</f>
+        <v/>
+      </c>
+      <c r="K58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4"/>
@@ -2130,18 +2577,26 @@
         <v/>
       </c>
       <c r="F59" s="5" t="str">
+        <f aca="false">IF($A59="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A59,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G59" s="5" t="str">
+        <f aca="false">IF($A59="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A59,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H59" s="5" t="str">
+        <f aca="false">IF($A59="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A59,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I59" s="5" t="str">
         <f aca="false">IF($A59="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A59,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G59" s="5" t="str">
-        <f aca="false">IF($A59="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A59))</f>
-        <v/>
-      </c>
-      <c r="H59" s="5" t="str">
-        <f aca="false">IF($A59="","",$D59+$E59+$F59-$G59)</f>
-        <v/>
-      </c>
-      <c r="I59" s="4"/>
+      <c r="J59" s="5" t="str">
+        <f aca="false">IF($A59="","",$D59+$E59-$F59-$G59-$H59+$I59)</f>
+        <v/>
+      </c>
+      <c r="K59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4"/>
@@ -2153,18 +2608,26 @@
         <v/>
       </c>
       <c r="F60" s="5" t="str">
+        <f aca="false">IF($A60="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A60,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G60" s="5" t="str">
+        <f aca="false">IF($A60="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A60,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H60" s="5" t="str">
+        <f aca="false">IF($A60="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A60,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I60" s="5" t="str">
         <f aca="false">IF($A60="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A60,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G60" s="5" t="str">
-        <f aca="false">IF($A60="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A60))</f>
-        <v/>
-      </c>
-      <c r="H60" s="5" t="str">
-        <f aca="false">IF($A60="","",$D60+$E60+$F60-$G60)</f>
-        <v/>
-      </c>
-      <c r="I60" s="4"/>
+      <c r="J60" s="5" t="str">
+        <f aca="false">IF($A60="","",$D60+$E60-$F60-$G60-$H60+$I60)</f>
+        <v/>
+      </c>
+      <c r="K60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4"/>
@@ -2176,18 +2639,26 @@
         <v/>
       </c>
       <c r="F61" s="5" t="str">
+        <f aca="false">IF($A61="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A61,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G61" s="5" t="str">
+        <f aca="false">IF($A61="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A61,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H61" s="5" t="str">
+        <f aca="false">IF($A61="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A61,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I61" s="5" t="str">
         <f aca="false">IF($A61="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A61,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G61" s="5" t="str">
-        <f aca="false">IF($A61="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A61))</f>
-        <v/>
-      </c>
-      <c r="H61" s="5" t="str">
-        <f aca="false">IF($A61="","",$D61+$E61+$F61-$G61)</f>
-        <v/>
-      </c>
-      <c r="I61" s="4"/>
+      <c r="J61" s="5" t="str">
+        <f aca="false">IF($A61="","",$D61+$E61-$F61-$G61-$H61+$I61)</f>
+        <v/>
+      </c>
+      <c r="K61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4"/>
@@ -2199,18 +2670,26 @@
         <v/>
       </c>
       <c r="F62" s="5" t="str">
+        <f aca="false">IF($A62="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A62,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G62" s="5" t="str">
+        <f aca="false">IF($A62="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A62,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H62" s="5" t="str">
+        <f aca="false">IF($A62="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A62,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I62" s="5" t="str">
         <f aca="false">IF($A62="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A62,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G62" s="5" t="str">
-        <f aca="false">IF($A62="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A62))</f>
-        <v/>
-      </c>
-      <c r="H62" s="5" t="str">
-        <f aca="false">IF($A62="","",$D62+$E62+$F62-$G62)</f>
-        <v/>
-      </c>
-      <c r="I62" s="4"/>
+      <c r="J62" s="5" t="str">
+        <f aca="false">IF($A62="","",$D62+$E62-$F62-$G62-$H62+$I62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4"/>
@@ -2222,18 +2701,26 @@
         <v/>
       </c>
       <c r="F63" s="5" t="str">
+        <f aca="false">IF($A63="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A63,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G63" s="5" t="str">
+        <f aca="false">IF($A63="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A63,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H63" s="5" t="str">
+        <f aca="false">IF($A63="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A63,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I63" s="5" t="str">
         <f aca="false">IF($A63="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A63,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G63" s="5" t="str">
-        <f aca="false">IF($A63="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A63))</f>
-        <v/>
-      </c>
-      <c r="H63" s="5" t="str">
-        <f aca="false">IF($A63="","",$D63+$E63+$F63-$G63)</f>
-        <v/>
-      </c>
-      <c r="I63" s="4"/>
+      <c r="J63" s="5" t="str">
+        <f aca="false">IF($A63="","",$D63+$E63-$F63-$G63-$H63+$I63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4"/>
@@ -2245,18 +2732,26 @@
         <v/>
       </c>
       <c r="F64" s="5" t="str">
+        <f aca="false">IF($A64="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A64,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G64" s="5" t="str">
+        <f aca="false">IF($A64="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A64,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H64" s="5" t="str">
+        <f aca="false">IF($A64="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A64,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I64" s="5" t="str">
         <f aca="false">IF($A64="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A64,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G64" s="5" t="str">
-        <f aca="false">IF($A64="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A64))</f>
-        <v/>
-      </c>
-      <c r="H64" s="5" t="str">
-        <f aca="false">IF($A64="","",$D64+$E64+$F64-$G64)</f>
-        <v/>
-      </c>
-      <c r="I64" s="4"/>
+      <c r="J64" s="5" t="str">
+        <f aca="false">IF($A64="","",$D64+$E64-$F64-$G64-$H64+$I64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4"/>
@@ -2268,18 +2763,26 @@
         <v/>
       </c>
       <c r="F65" s="5" t="str">
+        <f aca="false">IF($A65="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A65,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G65" s="5" t="str">
+        <f aca="false">IF($A65="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A65,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H65" s="5" t="str">
+        <f aca="false">IF($A65="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A65,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I65" s="5" t="str">
         <f aca="false">IF($A65="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A65,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G65" s="5" t="str">
-        <f aca="false">IF($A65="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A65))</f>
-        <v/>
-      </c>
-      <c r="H65" s="5" t="str">
-        <f aca="false">IF($A65="","",$D65+$E65+$F65-$G65)</f>
-        <v/>
-      </c>
-      <c r="I65" s="4"/>
+      <c r="J65" s="5" t="str">
+        <f aca="false">IF($A65="","",$D65+$E65-$F65-$G65-$H65+$I65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4"/>
@@ -2291,18 +2794,26 @@
         <v/>
       </c>
       <c r="F66" s="5" t="str">
+        <f aca="false">IF($A66="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A66,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G66" s="5" t="str">
+        <f aca="false">IF($A66="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A66,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H66" s="5" t="str">
+        <f aca="false">IF($A66="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A66,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I66" s="5" t="str">
         <f aca="false">IF($A66="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A66,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G66" s="5" t="str">
-        <f aca="false">IF($A66="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A66))</f>
-        <v/>
-      </c>
-      <c r="H66" s="5" t="str">
-        <f aca="false">IF($A66="","",$D66+$E66+$F66-$G66)</f>
-        <v/>
-      </c>
-      <c r="I66" s="4"/>
+      <c r="J66" s="5" t="str">
+        <f aca="false">IF($A66="","",$D66+$E66-$F66-$G66-$H66+$I66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4"/>
@@ -2314,18 +2825,26 @@
         <v/>
       </c>
       <c r="F67" s="5" t="str">
+        <f aca="false">IF($A67="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A67,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G67" s="5" t="str">
+        <f aca="false">IF($A67="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A67,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H67" s="5" t="str">
+        <f aca="false">IF($A67="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A67,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I67" s="5" t="str">
         <f aca="false">IF($A67="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A67,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G67" s="5" t="str">
-        <f aca="false">IF($A67="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A67))</f>
-        <v/>
-      </c>
-      <c r="H67" s="5" t="str">
-        <f aca="false">IF($A67="","",$D67+$E67+$F67-$G67)</f>
-        <v/>
-      </c>
-      <c r="I67" s="4"/>
+      <c r="J67" s="5" t="str">
+        <f aca="false">IF($A67="","",$D67+$E67-$F67-$G67-$H67+$I67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4"/>
@@ -2337,18 +2856,26 @@
         <v/>
       </c>
       <c r="F68" s="5" t="str">
+        <f aca="false">IF($A68="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A68,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G68" s="5" t="str">
+        <f aca="false">IF($A68="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A68,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H68" s="5" t="str">
+        <f aca="false">IF($A68="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A68,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I68" s="5" t="str">
         <f aca="false">IF($A68="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A68,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G68" s="5" t="str">
-        <f aca="false">IF($A68="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A68))</f>
-        <v/>
-      </c>
-      <c r="H68" s="5" t="str">
-        <f aca="false">IF($A68="","",$D68+$E68+$F68-$G68)</f>
-        <v/>
-      </c>
-      <c r="I68" s="4"/>
+      <c r="J68" s="5" t="str">
+        <f aca="false">IF($A68="","",$D68+$E68-$F68-$G68-$H68+$I68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4"/>
@@ -2360,18 +2887,26 @@
         <v/>
       </c>
       <c r="F69" s="5" t="str">
+        <f aca="false">IF($A69="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A69,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G69" s="5" t="str">
+        <f aca="false">IF($A69="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A69,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H69" s="5" t="str">
+        <f aca="false">IF($A69="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A69,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I69" s="5" t="str">
         <f aca="false">IF($A69="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A69,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G69" s="5" t="str">
-        <f aca="false">IF($A69="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A69))</f>
-        <v/>
-      </c>
-      <c r="H69" s="5" t="str">
-        <f aca="false">IF($A69="","",$D69+$E69+$F69-$G69)</f>
-        <v/>
-      </c>
-      <c r="I69" s="4"/>
+      <c r="J69" s="5" t="str">
+        <f aca="false">IF($A69="","",$D69+$E69-$F69-$G69-$H69+$I69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4"/>
@@ -2383,18 +2918,26 @@
         <v/>
       </c>
       <c r="F70" s="5" t="str">
+        <f aca="false">IF($A70="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A70,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G70" s="5" t="str">
+        <f aca="false">IF($A70="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A70,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H70" s="5" t="str">
+        <f aca="false">IF($A70="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A70,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I70" s="5" t="str">
         <f aca="false">IF($A70="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A70,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G70" s="5" t="str">
-        <f aca="false">IF($A70="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A70))</f>
-        <v/>
-      </c>
-      <c r="H70" s="5" t="str">
-        <f aca="false">IF($A70="","",$D70+$E70+$F70-$G70)</f>
-        <v/>
-      </c>
-      <c r="I70" s="4"/>
+      <c r="J70" s="5" t="str">
+        <f aca="false">IF($A70="","",$D70+$E70-$F70-$G70-$H70+$I70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4"/>
@@ -2406,18 +2949,26 @@
         <v/>
       </c>
       <c r="F71" s="5" t="str">
+        <f aca="false">IF($A71="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A71,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G71" s="5" t="str">
+        <f aca="false">IF($A71="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A71,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H71" s="5" t="str">
+        <f aca="false">IF($A71="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A71,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I71" s="5" t="str">
         <f aca="false">IF($A71="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A71,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G71" s="5" t="str">
-        <f aca="false">IF($A71="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A71))</f>
-        <v/>
-      </c>
-      <c r="H71" s="5" t="str">
-        <f aca="false">IF($A71="","",$D71+$E71+$F71-$G71)</f>
-        <v/>
-      </c>
-      <c r="I71" s="4"/>
+      <c r="J71" s="5" t="str">
+        <f aca="false">IF($A71="","",$D71+$E71-$F71-$G71-$H71+$I71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4"/>
@@ -2429,18 +2980,26 @@
         <v/>
       </c>
       <c r="F72" s="5" t="str">
+        <f aca="false">IF($A72="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A72,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G72" s="5" t="str">
+        <f aca="false">IF($A72="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A72,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H72" s="5" t="str">
+        <f aca="false">IF($A72="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A72,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I72" s="5" t="str">
         <f aca="false">IF($A72="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A72,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G72" s="5" t="str">
-        <f aca="false">IF($A72="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A72))</f>
-        <v/>
-      </c>
-      <c r="H72" s="5" t="str">
-        <f aca="false">IF($A72="","",$D72+$E72+$F72-$G72)</f>
-        <v/>
-      </c>
-      <c r="I72" s="4"/>
+      <c r="J72" s="5" t="str">
+        <f aca="false">IF($A72="","",$D72+$E72-$F72-$G72-$H72+$I72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4"/>
@@ -2452,18 +3011,26 @@
         <v/>
       </c>
       <c r="F73" s="5" t="str">
+        <f aca="false">IF($A73="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A73,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G73" s="5" t="str">
+        <f aca="false">IF($A73="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A73,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H73" s="5" t="str">
+        <f aca="false">IF($A73="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A73,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I73" s="5" t="str">
         <f aca="false">IF($A73="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A73,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G73" s="5" t="str">
-        <f aca="false">IF($A73="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A73))</f>
-        <v/>
-      </c>
-      <c r="H73" s="5" t="str">
-        <f aca="false">IF($A73="","",$D73+$E73+$F73-$G73)</f>
-        <v/>
-      </c>
-      <c r="I73" s="4"/>
+      <c r="J73" s="5" t="str">
+        <f aca="false">IF($A73="","",$D73+$E73-$F73-$G73-$H73+$I73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4"/>
@@ -2475,18 +3042,26 @@
         <v/>
       </c>
       <c r="F74" s="5" t="str">
+        <f aca="false">IF($A74="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A74,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G74" s="5" t="str">
+        <f aca="false">IF($A74="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A74,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H74" s="5" t="str">
+        <f aca="false">IF($A74="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A74,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I74" s="5" t="str">
         <f aca="false">IF($A74="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A74,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G74" s="5" t="str">
-        <f aca="false">IF($A74="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A74))</f>
-        <v/>
-      </c>
-      <c r="H74" s="5" t="str">
-        <f aca="false">IF($A74="","",$D74+$E74+$F74-$G74)</f>
-        <v/>
-      </c>
-      <c r="I74" s="4"/>
+      <c r="J74" s="5" t="str">
+        <f aca="false">IF($A74="","",$D74+$E74-$F74-$G74-$H74+$I74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4"/>
@@ -2498,18 +3073,26 @@
         <v/>
       </c>
       <c r="F75" s="5" t="str">
+        <f aca="false">IF($A75="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A75,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G75" s="5" t="str">
+        <f aca="false">IF($A75="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A75,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H75" s="5" t="str">
+        <f aca="false">IF($A75="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A75,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I75" s="5" t="str">
         <f aca="false">IF($A75="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A75,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G75" s="5" t="str">
-        <f aca="false">IF($A75="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A75))</f>
-        <v/>
-      </c>
-      <c r="H75" s="5" t="str">
-        <f aca="false">IF($A75="","",$D75+$E75+$F75-$G75)</f>
-        <v/>
-      </c>
-      <c r="I75" s="4"/>
+      <c r="J75" s="5" t="str">
+        <f aca="false">IF($A75="","",$D75+$E75-$F75-$G75-$H75+$I75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4"/>
@@ -2521,18 +3104,26 @@
         <v/>
       </c>
       <c r="F76" s="5" t="str">
+        <f aca="false">IF($A76="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A76,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G76" s="5" t="str">
+        <f aca="false">IF($A76="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A76,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H76" s="5" t="str">
+        <f aca="false">IF($A76="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A76,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I76" s="5" t="str">
         <f aca="false">IF($A76="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A76,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G76" s="5" t="str">
-        <f aca="false">IF($A76="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A76))</f>
-        <v/>
-      </c>
-      <c r="H76" s="5" t="str">
-        <f aca="false">IF($A76="","",$D76+$E76+$F76-$G76)</f>
-        <v/>
-      </c>
-      <c r="I76" s="4"/>
+      <c r="J76" s="5" t="str">
+        <f aca="false">IF($A76="","",$D76+$E76-$F76-$G76-$H76+$I76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4"/>
@@ -2544,18 +3135,26 @@
         <v/>
       </c>
       <c r="F77" s="5" t="str">
+        <f aca="false">IF($A77="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A77,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G77" s="5" t="str">
+        <f aca="false">IF($A77="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A77,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H77" s="5" t="str">
+        <f aca="false">IF($A77="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A77,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I77" s="5" t="str">
         <f aca="false">IF($A77="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A77,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G77" s="5" t="str">
-        <f aca="false">IF($A77="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A77))</f>
-        <v/>
-      </c>
-      <c r="H77" s="5" t="str">
-        <f aca="false">IF($A77="","",$D77+$E77+$F77-$G77)</f>
-        <v/>
-      </c>
-      <c r="I77" s="4"/>
+      <c r="J77" s="5" t="str">
+        <f aca="false">IF($A77="","",$D77+$E77-$F77-$G77-$H77+$I77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4"/>
@@ -2567,18 +3166,26 @@
         <v/>
       </c>
       <c r="F78" s="5" t="str">
+        <f aca="false">IF($A78="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A78,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G78" s="5" t="str">
+        <f aca="false">IF($A78="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A78,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H78" s="5" t="str">
+        <f aca="false">IF($A78="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A78,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I78" s="5" t="str">
         <f aca="false">IF($A78="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A78,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G78" s="5" t="str">
-        <f aca="false">IF($A78="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A78))</f>
-        <v/>
-      </c>
-      <c r="H78" s="5" t="str">
-        <f aca="false">IF($A78="","",$D78+$E78+$F78-$G78)</f>
-        <v/>
-      </c>
-      <c r="I78" s="4"/>
+      <c r="J78" s="5" t="str">
+        <f aca="false">IF($A78="","",$D78+$E78-$F78-$G78-$H78+$I78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4"/>
@@ -2590,18 +3197,26 @@
         <v/>
       </c>
       <c r="F79" s="5" t="str">
+        <f aca="false">IF($A79="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A79,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G79" s="5" t="str">
+        <f aca="false">IF($A79="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A79,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H79" s="5" t="str">
+        <f aca="false">IF($A79="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A79,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I79" s="5" t="str">
         <f aca="false">IF($A79="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A79,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G79" s="5" t="str">
-        <f aca="false">IF($A79="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A79))</f>
-        <v/>
-      </c>
-      <c r="H79" s="5" t="str">
-        <f aca="false">IF($A79="","",$D79+$E79+$F79-$G79)</f>
-        <v/>
-      </c>
-      <c r="I79" s="4"/>
+      <c r="J79" s="5" t="str">
+        <f aca="false">IF($A79="","",$D79+$E79-$F79-$G79-$H79+$I79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4"/>
@@ -2613,18 +3228,26 @@
         <v/>
       </c>
       <c r="F80" s="5" t="str">
+        <f aca="false">IF($A80="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A80,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G80" s="5" t="str">
+        <f aca="false">IF($A80="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A80,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H80" s="5" t="str">
+        <f aca="false">IF($A80="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A80,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I80" s="5" t="str">
         <f aca="false">IF($A80="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A80,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G80" s="5" t="str">
-        <f aca="false">IF($A80="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A80))</f>
-        <v/>
-      </c>
-      <c r="H80" s="5" t="str">
-        <f aca="false">IF($A80="","",$D80+$E80+$F80-$G80)</f>
-        <v/>
-      </c>
-      <c r="I80" s="4"/>
+      <c r="J80" s="5" t="str">
+        <f aca="false">IF($A80="","",$D80+$E80-$F80-$G80-$H80+$I80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4"/>
@@ -2636,18 +3259,26 @@
         <v/>
       </c>
       <c r="F81" s="5" t="str">
+        <f aca="false">IF($A81="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A81,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G81" s="5" t="str">
+        <f aca="false">IF($A81="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A81,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H81" s="5" t="str">
+        <f aca="false">IF($A81="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A81,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I81" s="5" t="str">
         <f aca="false">IF($A81="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A81,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G81" s="5" t="str">
-        <f aca="false">IF($A81="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A81))</f>
-        <v/>
-      </c>
-      <c r="H81" s="5" t="str">
-        <f aca="false">IF($A81="","",$D81+$E81+$F81-$G81)</f>
-        <v/>
-      </c>
-      <c r="I81" s="4"/>
+      <c r="J81" s="5" t="str">
+        <f aca="false">IF($A81="","",$D81+$E81-$F81-$G81-$H81+$I81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4"/>
@@ -2659,18 +3290,26 @@
         <v/>
       </c>
       <c r="F82" s="5" t="str">
+        <f aca="false">IF($A82="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A82,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G82" s="5" t="str">
+        <f aca="false">IF($A82="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A82,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H82" s="5" t="str">
+        <f aca="false">IF($A82="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A82,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I82" s="5" t="str">
         <f aca="false">IF($A82="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A82,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G82" s="5" t="str">
-        <f aca="false">IF($A82="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A82))</f>
-        <v/>
-      </c>
-      <c r="H82" s="5" t="str">
-        <f aca="false">IF($A82="","",$D82+$E82+$F82-$G82)</f>
-        <v/>
-      </c>
-      <c r="I82" s="4"/>
+      <c r="J82" s="5" t="str">
+        <f aca="false">IF($A82="","",$D82+$E82-$F82-$G82-$H82+$I82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4"/>
@@ -2682,18 +3321,26 @@
         <v/>
       </c>
       <c r="F83" s="5" t="str">
+        <f aca="false">IF($A83="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A83,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G83" s="5" t="str">
+        <f aca="false">IF($A83="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A83,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H83" s="5" t="str">
+        <f aca="false">IF($A83="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A83,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I83" s="5" t="str">
         <f aca="false">IF($A83="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A83,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G83" s="5" t="str">
-        <f aca="false">IF($A83="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A83))</f>
-        <v/>
-      </c>
-      <c r="H83" s="5" t="str">
-        <f aca="false">IF($A83="","",$D83+$E83+$F83-$G83)</f>
-        <v/>
-      </c>
-      <c r="I83" s="4"/>
+      <c r="J83" s="5" t="str">
+        <f aca="false">IF($A83="","",$D83+$E83-$F83-$G83-$H83+$I83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4"/>
@@ -2705,18 +3352,26 @@
         <v/>
       </c>
       <c r="F84" s="5" t="str">
+        <f aca="false">IF($A84="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A84,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G84" s="5" t="str">
+        <f aca="false">IF($A84="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A84,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H84" s="5" t="str">
+        <f aca="false">IF($A84="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A84,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I84" s="5" t="str">
         <f aca="false">IF($A84="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A84,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G84" s="5" t="str">
-        <f aca="false">IF($A84="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A84))</f>
-        <v/>
-      </c>
-      <c r="H84" s="5" t="str">
-        <f aca="false">IF($A84="","",$D84+$E84+$F84-$G84)</f>
-        <v/>
-      </c>
-      <c r="I84" s="4"/>
+      <c r="J84" s="5" t="str">
+        <f aca="false">IF($A84="","",$D84+$E84-$F84-$G84-$H84+$I84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4"/>
@@ -2728,18 +3383,26 @@
         <v/>
       </c>
       <c r="F85" s="5" t="str">
+        <f aca="false">IF($A85="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A85,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G85" s="5" t="str">
+        <f aca="false">IF($A85="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A85,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H85" s="5" t="str">
+        <f aca="false">IF($A85="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A85,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I85" s="5" t="str">
         <f aca="false">IF($A85="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A85,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G85" s="5" t="str">
-        <f aca="false">IF($A85="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A85))</f>
-        <v/>
-      </c>
-      <c r="H85" s="5" t="str">
-        <f aca="false">IF($A85="","",$D85+$E85+$F85-$G85)</f>
-        <v/>
-      </c>
-      <c r="I85" s="4"/>
+      <c r="J85" s="5" t="str">
+        <f aca="false">IF($A85="","",$D85+$E85-$F85-$G85-$H85+$I85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4"/>
@@ -2751,18 +3414,26 @@
         <v/>
       </c>
       <c r="F86" s="5" t="str">
+        <f aca="false">IF($A86="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A86,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G86" s="5" t="str">
+        <f aca="false">IF($A86="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A86,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H86" s="5" t="str">
+        <f aca="false">IF($A86="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A86,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I86" s="5" t="str">
         <f aca="false">IF($A86="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A86,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G86" s="5" t="str">
-        <f aca="false">IF($A86="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A86))</f>
-        <v/>
-      </c>
-      <c r="H86" s="5" t="str">
-        <f aca="false">IF($A86="","",$D86+$E86+$F86-$G86)</f>
-        <v/>
-      </c>
-      <c r="I86" s="4"/>
+      <c r="J86" s="5" t="str">
+        <f aca="false">IF($A86="","",$D86+$E86-$F86-$G86-$H86+$I86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4"/>
@@ -2774,18 +3445,26 @@
         <v/>
       </c>
       <c r="F87" s="5" t="str">
+        <f aca="false">IF($A87="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A87,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G87" s="5" t="str">
+        <f aca="false">IF($A87="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A87,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H87" s="5" t="str">
+        <f aca="false">IF($A87="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A87,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I87" s="5" t="str">
         <f aca="false">IF($A87="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A87,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G87" s="5" t="str">
-        <f aca="false">IF($A87="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A87))</f>
-        <v/>
-      </c>
-      <c r="H87" s="5" t="str">
-        <f aca="false">IF($A87="","",$D87+$E87+$F87-$G87)</f>
-        <v/>
-      </c>
-      <c r="I87" s="4"/>
+      <c r="J87" s="5" t="str">
+        <f aca="false">IF($A87="","",$D87+$E87-$F87-$G87-$H87+$I87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4"/>
@@ -2797,18 +3476,26 @@
         <v/>
       </c>
       <c r="F88" s="5" t="str">
+        <f aca="false">IF($A88="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A88,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G88" s="5" t="str">
+        <f aca="false">IF($A88="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A88,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H88" s="5" t="str">
+        <f aca="false">IF($A88="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A88,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I88" s="5" t="str">
         <f aca="false">IF($A88="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A88,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G88" s="5" t="str">
-        <f aca="false">IF($A88="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A88))</f>
-        <v/>
-      </c>
-      <c r="H88" s="5" t="str">
-        <f aca="false">IF($A88="","",$D88+$E88+$F88-$G88)</f>
-        <v/>
-      </c>
-      <c r="I88" s="4"/>
+      <c r="J88" s="5" t="str">
+        <f aca="false">IF($A88="","",$D88+$E88-$F88-$G88-$H88+$I88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4"/>
@@ -2820,18 +3507,26 @@
         <v/>
       </c>
       <c r="F89" s="5" t="str">
+        <f aca="false">IF($A89="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A89,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G89" s="5" t="str">
+        <f aca="false">IF($A89="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A89,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H89" s="5" t="str">
+        <f aca="false">IF($A89="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A89,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I89" s="5" t="str">
         <f aca="false">IF($A89="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A89,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G89" s="5" t="str">
-        <f aca="false">IF($A89="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A89))</f>
-        <v/>
-      </c>
-      <c r="H89" s="5" t="str">
-        <f aca="false">IF($A89="","",$D89+$E89+$F89-$G89)</f>
-        <v/>
-      </c>
-      <c r="I89" s="4"/>
+      <c r="J89" s="5" t="str">
+        <f aca="false">IF($A89="","",$D89+$E89-$F89-$G89-$H89+$I89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4"/>
@@ -2843,18 +3538,26 @@
         <v/>
       </c>
       <c r="F90" s="5" t="str">
+        <f aca="false">IF($A90="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A90,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G90" s="5" t="str">
+        <f aca="false">IF($A90="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A90,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H90" s="5" t="str">
+        <f aca="false">IF($A90="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A90,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I90" s="5" t="str">
         <f aca="false">IF($A90="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A90,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G90" s="5" t="str">
-        <f aca="false">IF($A90="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A90))</f>
-        <v/>
-      </c>
-      <c r="H90" s="5" t="str">
-        <f aca="false">IF($A90="","",$D90+$E90+$F90-$G90)</f>
-        <v/>
-      </c>
-      <c r="I90" s="4"/>
+      <c r="J90" s="5" t="str">
+        <f aca="false">IF($A90="","",$D90+$E90-$F90-$G90-$H90+$I90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4"/>
@@ -2866,18 +3569,26 @@
         <v/>
       </c>
       <c r="F91" s="5" t="str">
+        <f aca="false">IF($A91="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A91,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G91" s="5" t="str">
+        <f aca="false">IF($A91="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A91,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H91" s="5" t="str">
+        <f aca="false">IF($A91="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A91,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I91" s="5" t="str">
         <f aca="false">IF($A91="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A91,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G91" s="5" t="str">
-        <f aca="false">IF($A91="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A91))</f>
-        <v/>
-      </c>
-      <c r="H91" s="5" t="str">
-        <f aca="false">IF($A91="","",$D91+$E91+$F91-$G91)</f>
-        <v/>
-      </c>
-      <c r="I91" s="4"/>
+      <c r="J91" s="5" t="str">
+        <f aca="false">IF($A91="","",$D91+$E91-$F91-$G91-$H91+$I91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4"/>
@@ -2889,18 +3600,26 @@
         <v/>
       </c>
       <c r="F92" s="5" t="str">
+        <f aca="false">IF($A92="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A92,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G92" s="5" t="str">
+        <f aca="false">IF($A92="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A92,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H92" s="5" t="str">
+        <f aca="false">IF($A92="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A92,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I92" s="5" t="str">
         <f aca="false">IF($A92="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A92,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G92" s="5" t="str">
-        <f aca="false">IF($A92="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A92))</f>
-        <v/>
-      </c>
-      <c r="H92" s="5" t="str">
-        <f aca="false">IF($A92="","",$D92+$E92+$F92-$G92)</f>
-        <v/>
-      </c>
-      <c r="I92" s="4"/>
+      <c r="J92" s="5" t="str">
+        <f aca="false">IF($A92="","",$D92+$E92-$F92-$G92-$H92+$I92)</f>
+        <v/>
+      </c>
+      <c r="K92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4"/>
@@ -2912,18 +3631,26 @@
         <v/>
       </c>
       <c r="F93" s="5" t="str">
+        <f aca="false">IF($A93="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A93,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G93" s="5" t="str">
+        <f aca="false">IF($A93="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A93,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H93" s="5" t="str">
+        <f aca="false">IF($A93="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A93,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I93" s="5" t="str">
         <f aca="false">IF($A93="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A93,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G93" s="5" t="str">
-        <f aca="false">IF($A93="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A93))</f>
-        <v/>
-      </c>
-      <c r="H93" s="5" t="str">
-        <f aca="false">IF($A93="","",$D93+$E93+$F93-$G93)</f>
-        <v/>
-      </c>
-      <c r="I93" s="4"/>
+      <c r="J93" s="5" t="str">
+        <f aca="false">IF($A93="","",$D93+$E93-$F93-$G93-$H93+$I93)</f>
+        <v/>
+      </c>
+      <c r="K93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4"/>
@@ -2935,18 +3662,26 @@
         <v/>
       </c>
       <c r="F94" s="5" t="str">
+        <f aca="false">IF($A94="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A94,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G94" s="5" t="str">
+        <f aca="false">IF($A94="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A94,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H94" s="5" t="str">
+        <f aca="false">IF($A94="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A94,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I94" s="5" t="str">
         <f aca="false">IF($A94="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A94,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G94" s="5" t="str">
-        <f aca="false">IF($A94="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A94))</f>
-        <v/>
-      </c>
-      <c r="H94" s="5" t="str">
-        <f aca="false">IF($A94="","",$D94+$E94+$F94-$G94)</f>
-        <v/>
-      </c>
-      <c r="I94" s="4"/>
+      <c r="J94" s="5" t="str">
+        <f aca="false">IF($A94="","",$D94+$E94-$F94-$G94-$H94+$I94)</f>
+        <v/>
+      </c>
+      <c r="K94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4"/>
@@ -2958,18 +3693,26 @@
         <v/>
       </c>
       <c r="F95" s="5" t="str">
+        <f aca="false">IF($A95="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A95,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G95" s="5" t="str">
+        <f aca="false">IF($A95="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A95,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H95" s="5" t="str">
+        <f aca="false">IF($A95="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A95,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I95" s="5" t="str">
         <f aca="false">IF($A95="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A95,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G95" s="5" t="str">
-        <f aca="false">IF($A95="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A95))</f>
-        <v/>
-      </c>
-      <c r="H95" s="5" t="str">
-        <f aca="false">IF($A95="","",$D95+$E95+$F95-$G95)</f>
-        <v/>
-      </c>
-      <c r="I95" s="4"/>
+      <c r="J95" s="5" t="str">
+        <f aca="false">IF($A95="","",$D95+$E95-$F95-$G95-$H95+$I95)</f>
+        <v/>
+      </c>
+      <c r="K95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4"/>
@@ -2981,18 +3724,26 @@
         <v/>
       </c>
       <c r="F96" s="5" t="str">
+        <f aca="false">IF($A96="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A96,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G96" s="5" t="str">
+        <f aca="false">IF($A96="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A96,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H96" s="5" t="str">
+        <f aca="false">IF($A96="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A96,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I96" s="5" t="str">
         <f aca="false">IF($A96="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A96,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G96" s="5" t="str">
-        <f aca="false">IF($A96="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A96))</f>
-        <v/>
-      </c>
-      <c r="H96" s="5" t="str">
-        <f aca="false">IF($A96="","",$D96+$E96+$F96-$G96)</f>
-        <v/>
-      </c>
-      <c r="I96" s="4"/>
+      <c r="J96" s="5" t="str">
+        <f aca="false">IF($A96="","",$D96+$E96-$F96-$G96-$H96+$I96)</f>
+        <v/>
+      </c>
+      <c r="K96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4"/>
@@ -3004,18 +3755,26 @@
         <v/>
       </c>
       <c r="F97" s="5" t="str">
+        <f aca="false">IF($A97="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A97,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G97" s="5" t="str">
+        <f aca="false">IF($A97="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A97,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H97" s="5" t="str">
+        <f aca="false">IF($A97="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A97,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I97" s="5" t="str">
         <f aca="false">IF($A97="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A97,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G97" s="5" t="str">
-        <f aca="false">IF($A97="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A97))</f>
-        <v/>
-      </c>
-      <c r="H97" s="5" t="str">
-        <f aca="false">IF($A97="","",$D97+$E97+$F97-$G97)</f>
-        <v/>
-      </c>
-      <c r="I97" s="4"/>
+      <c r="J97" s="5" t="str">
+        <f aca="false">IF($A97="","",$D97+$E97-$F97-$G97-$H97+$I97)</f>
+        <v/>
+      </c>
+      <c r="K97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4"/>
@@ -3027,18 +3786,26 @@
         <v/>
       </c>
       <c r="F98" s="5" t="str">
+        <f aca="false">IF($A98="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A98,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G98" s="5" t="str">
+        <f aca="false">IF($A98="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A98,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H98" s="5" t="str">
+        <f aca="false">IF($A98="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A98,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I98" s="5" t="str">
         <f aca="false">IF($A98="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A98,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G98" s="5" t="str">
-        <f aca="false">IF($A98="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A98))</f>
-        <v/>
-      </c>
-      <c r="H98" s="5" t="str">
-        <f aca="false">IF($A98="","",$D98+$E98+$F98-$G98)</f>
-        <v/>
-      </c>
-      <c r="I98" s="4"/>
+      <c r="J98" s="5" t="str">
+        <f aca="false">IF($A98="","",$D98+$E98-$F98-$G98-$H98+$I98)</f>
+        <v/>
+      </c>
+      <c r="K98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4"/>
@@ -3050,18 +3817,26 @@
         <v/>
       </c>
       <c r="F99" s="5" t="str">
+        <f aca="false">IF($A99="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A99,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G99" s="5" t="str">
+        <f aca="false">IF($A99="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A99,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H99" s="5" t="str">
+        <f aca="false">IF($A99="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A99,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I99" s="5" t="str">
         <f aca="false">IF($A99="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A99,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G99" s="5" t="str">
-        <f aca="false">IF($A99="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A99))</f>
-        <v/>
-      </c>
-      <c r="H99" s="5" t="str">
-        <f aca="false">IF($A99="","",$D99+$E99+$F99-$G99)</f>
-        <v/>
-      </c>
-      <c r="I99" s="4"/>
+      <c r="J99" s="5" t="str">
+        <f aca="false">IF($A99="","",$D99+$E99-$F99-$G99-$H99+$I99)</f>
+        <v/>
+      </c>
+      <c r="K99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4"/>
@@ -3073,18 +3848,26 @@
         <v/>
       </c>
       <c r="F100" s="5" t="str">
+        <f aca="false">IF($A100="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A100,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G100" s="5" t="str">
+        <f aca="false">IF($A100="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A100,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H100" s="5" t="str">
+        <f aca="false">IF($A100="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A100,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I100" s="5" t="str">
         <f aca="false">IF($A100="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A100,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G100" s="5" t="str">
-        <f aca="false">IF($A100="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A100))</f>
-        <v/>
-      </c>
-      <c r="H100" s="5" t="str">
-        <f aca="false">IF($A100="","",$D100+$E100+$F100-$G100)</f>
-        <v/>
-      </c>
-      <c r="I100" s="4"/>
+      <c r="J100" s="5" t="str">
+        <f aca="false">IF($A100="","",$D100+$E100-$F100-$G100-$H100+$I100)</f>
+        <v/>
+      </c>
+      <c r="K100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4"/>
@@ -3096,18 +3879,26 @@
         <v/>
       </c>
       <c r="F101" s="5" t="str">
+        <f aca="false">IF($A101="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A101,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G101" s="5" t="str">
+        <f aca="false">IF($A101="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A101,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H101" s="5" t="str">
+        <f aca="false">IF($A101="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A101,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I101" s="5" t="str">
         <f aca="false">IF($A101="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A101,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G101" s="5" t="str">
-        <f aca="false">IF($A101="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A101))</f>
-        <v/>
-      </c>
-      <c r="H101" s="5" t="str">
-        <f aca="false">IF($A101="","",$D101+$E101+$F101-$G101)</f>
-        <v/>
-      </c>
-      <c r="I101" s="4"/>
+      <c r="J101" s="5" t="str">
+        <f aca="false">IF($A101="","",$D101+$E101-$F101-$G101-$H101+$I101)</f>
+        <v/>
+      </c>
+      <c r="K101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4"/>
@@ -3119,18 +3910,26 @@
         <v/>
       </c>
       <c r="F102" s="5" t="str">
+        <f aca="false">IF($A102="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A102,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G102" s="5" t="str">
+        <f aca="false">IF($A102="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A102,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H102" s="5" t="str">
+        <f aca="false">IF($A102="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A102,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I102" s="5" t="str">
         <f aca="false">IF($A102="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A102,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G102" s="5" t="str">
-        <f aca="false">IF($A102="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A102))</f>
-        <v/>
-      </c>
-      <c r="H102" s="5" t="str">
-        <f aca="false">IF($A102="","",$D102+$E102+$F102-$G102)</f>
-        <v/>
-      </c>
-      <c r="I102" s="4"/>
+      <c r="J102" s="5" t="str">
+        <f aca="false">IF($A102="","",$D102+$E102-$F102-$G102-$H102+$I102)</f>
+        <v/>
+      </c>
+      <c r="K102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4"/>
@@ -3142,18 +3941,26 @@
         <v/>
       </c>
       <c r="F103" s="5" t="str">
+        <f aca="false">IF($A103="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A103,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G103" s="5" t="str">
+        <f aca="false">IF($A103="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A103,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H103" s="5" t="str">
+        <f aca="false">IF($A103="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A103,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I103" s="5" t="str">
         <f aca="false">IF($A103="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A103,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G103" s="5" t="str">
-        <f aca="false">IF($A103="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A103))</f>
-        <v/>
-      </c>
-      <c r="H103" s="5" t="str">
-        <f aca="false">IF($A103="","",$D103+$E103+$F103-$G103)</f>
-        <v/>
-      </c>
-      <c r="I103" s="4"/>
+      <c r="J103" s="5" t="str">
+        <f aca="false">IF($A103="","",$D103+$E103-$F103-$G103-$H103+$I103)</f>
+        <v/>
+      </c>
+      <c r="K103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4"/>
@@ -3165,18 +3972,26 @@
         <v/>
       </c>
       <c r="F104" s="5" t="str">
+        <f aca="false">IF($A104="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A104,Movements!$B$5:$B$304,"Sell"))</f>
+        <v/>
+      </c>
+      <c r="G104" s="5" t="str">
+        <f aca="false">IF($A104="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A104,Recipes!$B$5:$B$104,"B"))</f>
+        <v/>
+      </c>
+      <c r="H104" s="5" t="str">
+        <f aca="false">IF($A104="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A104,Recipes!$B$5:$B$104,"C"))</f>
+        <v/>
+      </c>
+      <c r="I104" s="5" t="str">
         <f aca="false">IF($A104="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A104,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="G104" s="5" t="str">
-        <f aca="false">IF($A104="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A104))</f>
-        <v/>
-      </c>
-      <c r="H104" s="5" t="str">
-        <f aca="false">IF($A104="","",$D104+$E104+$F104-$G104)</f>
-        <v/>
-      </c>
-      <c r="I104" s="4"/>
+      <c r="J104" s="5" t="str">
+        <f aca="false">IF($A104="","",$D104+$E104-$F104-$G104-$H104+$I104)</f>
+        <v/>
+      </c>
+      <c r="K104" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3213,12 +4028,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3229,42 +4044,42 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Build"))</f>
@@ -3303,15 +4118,15 @@
         <v>2</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Build"))</f>
@@ -3353,10 +4168,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Build"))</f>
@@ -7405,12 +8220,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7418,42 +8233,42 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>899</v>
@@ -7479,18 +8294,18 @@
         <v>Shares parts with other kits</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>1299</v>
@@ -10199,70 +11014,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>30</v>
@@ -10284,15 +11099,15 @@
         <v>660</v>
       </c>
       <c r="I5" s="6" t="n">
-        <f aca="false">IF($B5&lt;&gt;"B","",IFERROR(IF($D5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$D5,1)),0))</f>
+        <f aca="false">IF($B5&lt;&gt;"B","",IFERROR(IF($D5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$D5,1)),0))</f>
         <v>19</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
+        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
         <v/>
       </c>
       <c r="K5" s="6" t="str">
-        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
+        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
         <v/>
       </c>
       <c r="L5" s="6" t="str">
@@ -10314,13 +11129,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
@@ -10342,15 +11157,15 @@
         <v>22</v>
       </c>
       <c r="I6" s="6" t="n">
-        <f aca="false">IF($B6&lt;&gt;"B","",IFERROR(IF($D6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$D6,1)),0))</f>
+        <f aca="false">IF($B6&lt;&gt;"B","",IFERROR(IF($D6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$D6,1)),0))</f>
         <v>38</v>
       </c>
       <c r="J6" s="6" t="str">
-        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
+        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
         <v/>
       </c>
       <c r="K6" s="6" t="str">
-        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
+        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
         <v/>
       </c>
       <c r="L6" s="6" t="str">
@@ -10372,13 +11187,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1</v>
@@ -10400,15 +11215,15 @@
         <v>22</v>
       </c>
       <c r="I7" s="6" t="n">
-        <f aca="false">IF($B7&lt;&gt;"B","",IFERROR(IF($D7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$D7,1)),0))</f>
+        <f aca="false">IF($B7&lt;&gt;"B","",IFERROR(IF($D7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$D7,1)),0))</f>
         <v>178</v>
       </c>
       <c r="J7" s="6" t="str">
-        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
+        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
         <v/>
       </c>
       <c r="K7" s="6" t="str">
-        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
+        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
         <v/>
       </c>
       <c r="L7" s="6" t="str">
@@ -10430,13 +11245,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>1</v>
@@ -10458,15 +11273,15 @@
         <v>12</v>
       </c>
       <c r="I8" s="6" t="n">
-        <f aca="false">IF($B8&lt;&gt;"B","",IFERROR(IF($D8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$D8,1)),0))</f>
+        <f aca="false">IF($B8&lt;&gt;"B","",IFERROR(IF($D8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$D8,1)),0))</f>
         <v>138</v>
       </c>
       <c r="J8" s="6" t="str">
-        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
+        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
         <v/>
       </c>
       <c r="K8" s="6" t="str">
-        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
+        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
         <v/>
       </c>
       <c r="L8" s="6" t="str">
@@ -10488,13 +11303,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>10</v>
@@ -10516,15 +11331,15 @@
         <v>120</v>
       </c>
       <c r="I9" s="6" t="n">
-        <f aca="false">IF($B9&lt;&gt;"B","",IFERROR(IF($D9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$D9,1)),0))</f>
+        <f aca="false">IF($B9&lt;&gt;"B","",IFERROR(IF($D9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$D9,1)),0))</f>
         <v>58</v>
       </c>
       <c r="J9" s="6" t="str">
-        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
+        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
         <v/>
       </c>
       <c r="K9" s="6" t="str">
-        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
+        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
         <v/>
       </c>
       <c r="L9" s="6" t="str">
@@ -10546,13 +11361,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1</v>
@@ -10574,15 +11389,15 @@
         <v>17</v>
       </c>
       <c r="I10" s="6" t="n">
-        <f aca="false">IF($B10&lt;&gt;"B","",IFERROR(IF($D10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$D10,1)),0))</f>
+        <f aca="false">IF($B10&lt;&gt;"B","",IFERROR(IF($D10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$D10,1)),0))</f>
         <v>63</v>
       </c>
       <c r="J10" s="6" t="str">
-        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
+        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
         <v/>
       </c>
       <c r="K10" s="6" t="str">
-        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
+        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
         <v/>
       </c>
       <c r="L10" s="6" t="str">
@@ -10604,13 +11419,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>1</v>
@@ -10632,15 +11447,15 @@
         <v>12</v>
       </c>
       <c r="I11" s="6" t="str">
-        <f aca="false">IF($B11&lt;&gt;"B","",IFERROR(IF($D11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$D11,1)),0))</f>
+        <f aca="false">IF($B11&lt;&gt;"B","",IFERROR(IF($D11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$D11,1)),0))</f>
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
+        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
+        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
         <v>19</v>
       </c>
       <c r="L11" s="6" t="str">
@@ -10662,13 +11477,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>1</v>
@@ -10690,15 +11505,15 @@
         <v>12</v>
       </c>
       <c r="I12" s="6" t="str">
-        <f aca="false">IF($B12&lt;&gt;"B","",IFERROR(IF($D12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$D12,1)),0))</f>
+        <f aca="false">IF($B12&lt;&gt;"B","",IFERROR(IF($D12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$D12,1)),0))</f>
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
+        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
-        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
+        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
         <v>58</v>
       </c>
       <c r="L12" s="6" t="str">
@@ -10720,13 +11535,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1</v>
@@ -10748,15 +11563,15 @@
         <v>12</v>
       </c>
       <c r="I13" s="6" t="str">
-        <f aca="false">IF($B13&lt;&gt;"B","",IFERROR(IF($D13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$D13,1)),0))</f>
+        <f aca="false">IF($B13&lt;&gt;"B","",IFERROR(IF($D13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$D13,1)),0))</f>
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
+        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
+        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
         <v>63</v>
       </c>
       <c r="L13" s="6" t="str">
@@ -10778,13 +11593,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>10</v>
@@ -10806,15 +11621,15 @@
         <v>120</v>
       </c>
       <c r="I14" s="6" t="str">
-        <f aca="false">IF($B14&lt;&gt;"B","",IFERROR(IF($D14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$D14,1)),0))</f>
+        <f aca="false">IF($B14&lt;&gt;"B","",IFERROR(IF($D14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$D14,1)),0))</f>
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
+        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
         <v>11</v>
       </c>
       <c r="K14" s="6" t="n">
-        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
+        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
         <v>11</v>
       </c>
       <c r="L14" s="6" t="str">
@@ -10836,13 +11651,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>2</v>
@@ -10864,15 +11679,15 @@
         <v>10</v>
       </c>
       <c r="I15" s="6" t="str">
-        <f aca="false">IF($B15&lt;&gt;"B","",IFERROR(IF($D15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$D15,1)),0))</f>
+        <f aca="false">IF($B15&lt;&gt;"B","",IFERROR(IF($D15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$D15,1)),0))</f>
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
+        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
+        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
         <v>9</v>
       </c>
       <c r="L15" s="6" t="str">
@@ -10894,13 +11709,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1</v>
@@ -10922,15 +11737,15 @@
         <v>5</v>
       </c>
       <c r="I16" s="6" t="str">
-        <f aca="false">IF($B16&lt;&gt;"B","",IFERROR(IF($D16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$D16,1)),0))</f>
+        <f aca="false">IF($B16&lt;&gt;"B","",IFERROR(IF($D16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$D16,1)),0))</f>
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
+        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
+        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
         <v>63</v>
       </c>
       <c r="L16" s="6" t="str">
@@ -10972,15 +11787,15 @@
         <v/>
       </c>
       <c r="I17" s="6" t="str">
-        <f aca="false">IF($B17&lt;&gt;"B","",IFERROR(IF($D17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$D17,1)),0))</f>
+        <f aca="false">IF($B17&lt;&gt;"B","",IFERROR(IF($D17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$D17,1)),0))</f>
         <v/>
       </c>
       <c r="J17" s="6" t="str">
-        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
+        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
         <v/>
       </c>
       <c r="K17" s="6" t="str">
-        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
+        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
         <v/>
       </c>
       <c r="L17" s="6" t="str">
@@ -11022,15 +11837,15 @@
         <v/>
       </c>
       <c r="I18" s="6" t="str">
-        <f aca="false">IF($B18&lt;&gt;"B","",IFERROR(IF($D18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$D18,1)),0))</f>
+        <f aca="false">IF($B18&lt;&gt;"B","",IFERROR(IF($D18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$D18,1)),0))</f>
         <v/>
       </c>
       <c r="J18" s="6" t="str">
-        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
+        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
         <v/>
       </c>
       <c r="K18" s="6" t="str">
-        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
+        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
         <v/>
       </c>
       <c r="L18" s="6" t="str">
@@ -11072,15 +11887,15 @@
         <v/>
       </c>
       <c r="I19" s="6" t="str">
-        <f aca="false">IF($B19&lt;&gt;"B","",IFERROR(IF($D19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$D19,1)),0))</f>
+        <f aca="false">IF($B19&lt;&gt;"B","",IFERROR(IF($D19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$D19,1)),0))</f>
         <v/>
       </c>
       <c r="J19" s="6" t="str">
-        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
+        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
         <v/>
       </c>
       <c r="K19" s="6" t="str">
-        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
+        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
         <v/>
       </c>
       <c r="L19" s="6" t="str">
@@ -11122,15 +11937,15 @@
         <v/>
       </c>
       <c r="I20" s="6" t="str">
-        <f aca="false">IF($B20&lt;&gt;"B","",IFERROR(IF($D20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$D20,1)),0))</f>
+        <f aca="false">IF($B20&lt;&gt;"B","",IFERROR(IF($D20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$D20,1)),0))</f>
         <v/>
       </c>
       <c r="J20" s="6" t="str">
-        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
+        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
         <v/>
       </c>
       <c r="K20" s="6" t="str">
-        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
+        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
         <v/>
       </c>
       <c r="L20" s="6" t="str">
@@ -11172,15 +11987,15 @@
         <v/>
       </c>
       <c r="I21" s="6" t="str">
-        <f aca="false">IF($B21&lt;&gt;"B","",IFERROR(IF($D21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$D21,1)),0))</f>
+        <f aca="false">IF($B21&lt;&gt;"B","",IFERROR(IF($D21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$D21,1)),0))</f>
         <v/>
       </c>
       <c r="J21" s="6" t="str">
-        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
+        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
         <v/>
       </c>
       <c r="K21" s="6" t="str">
-        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
+        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
         <v/>
       </c>
       <c r="L21" s="6" t="str">
@@ -11222,15 +12037,15 @@
         <v/>
       </c>
       <c r="I22" s="6" t="str">
-        <f aca="false">IF($B22&lt;&gt;"B","",IFERROR(IF($D22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$D22,1)),0))</f>
+        <f aca="false">IF($B22&lt;&gt;"B","",IFERROR(IF($D22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$D22,1)),0))</f>
         <v/>
       </c>
       <c r="J22" s="6" t="str">
-        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
+        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
         <v/>
       </c>
       <c r="K22" s="6" t="str">
-        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
+        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
         <v/>
       </c>
       <c r="L22" s="6" t="str">
@@ -11272,15 +12087,15 @@
         <v/>
       </c>
       <c r="I23" s="6" t="str">
-        <f aca="false">IF($B23&lt;&gt;"B","",IFERROR(IF($D23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$D23,1)),0))</f>
+        <f aca="false">IF($B23&lt;&gt;"B","",IFERROR(IF($D23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$D23,1)),0))</f>
         <v/>
       </c>
       <c r="J23" s="6" t="str">
-        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
+        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
         <v/>
       </c>
       <c r="K23" s="6" t="str">
-        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
+        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
         <v/>
       </c>
       <c r="L23" s="6" t="str">
@@ -11322,15 +12137,15 @@
         <v/>
       </c>
       <c r="I24" s="6" t="str">
-        <f aca="false">IF($B24&lt;&gt;"B","",IFERROR(IF($D24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$D24,1)),0))</f>
+        <f aca="false">IF($B24&lt;&gt;"B","",IFERROR(IF($D24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$D24,1)),0))</f>
         <v/>
       </c>
       <c r="J24" s="6" t="str">
-        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
+        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
         <v/>
       </c>
       <c r="K24" s="6" t="str">
-        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
+        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
         <v/>
       </c>
       <c r="L24" s="6" t="str">
@@ -11372,15 +12187,15 @@
         <v/>
       </c>
       <c r="I25" s="6" t="str">
-        <f aca="false">IF($B25&lt;&gt;"B","",IFERROR(IF($D25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$D25,1)),0))</f>
+        <f aca="false">IF($B25&lt;&gt;"B","",IFERROR(IF($D25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$D25,1)),0))</f>
         <v/>
       </c>
       <c r="J25" s="6" t="str">
-        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
+        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
         <v/>
       </c>
       <c r="K25" s="6" t="str">
-        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
+        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
         <v/>
       </c>
       <c r="L25" s="6" t="str">
@@ -11422,15 +12237,15 @@
         <v/>
       </c>
       <c r="I26" s="6" t="str">
-        <f aca="false">IF($B26&lt;&gt;"B","",IFERROR(IF($D26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$D26,1)),0))</f>
+        <f aca="false">IF($B26&lt;&gt;"B","",IFERROR(IF($D26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$D26,1)),0))</f>
         <v/>
       </c>
       <c r="J26" s="6" t="str">
-        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
+        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
         <v/>
       </c>
       <c r="K26" s="6" t="str">
-        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
+        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
         <v/>
       </c>
       <c r="L26" s="6" t="str">
@@ -11472,15 +12287,15 @@
         <v/>
       </c>
       <c r="I27" s="6" t="str">
-        <f aca="false">IF($B27&lt;&gt;"B","",IFERROR(IF($D27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$D27,1)),0))</f>
+        <f aca="false">IF($B27&lt;&gt;"B","",IFERROR(IF($D27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$D27,1)),0))</f>
         <v/>
       </c>
       <c r="J27" s="6" t="str">
-        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
+        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
         <v/>
       </c>
       <c r="K27" s="6" t="str">
-        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
+        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
         <v/>
       </c>
       <c r="L27" s="6" t="str">
@@ -11522,15 +12337,15 @@
         <v/>
       </c>
       <c r="I28" s="6" t="str">
-        <f aca="false">IF($B28&lt;&gt;"B","",IFERROR(IF($D28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$D28,1)),0))</f>
+        <f aca="false">IF($B28&lt;&gt;"B","",IFERROR(IF($D28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$D28,1)),0))</f>
         <v/>
       </c>
       <c r="J28" s="6" t="str">
-        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
+        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
         <v/>
       </c>
       <c r="K28" s="6" t="str">
-        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
+        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
         <v/>
       </c>
       <c r="L28" s="6" t="str">
@@ -11572,15 +12387,15 @@
         <v/>
       </c>
       <c r="I29" s="6" t="str">
-        <f aca="false">IF($B29&lt;&gt;"B","",IFERROR(IF($D29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$D29,1)),0))</f>
+        <f aca="false">IF($B29&lt;&gt;"B","",IFERROR(IF($D29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$D29,1)),0))</f>
         <v/>
       </c>
       <c r="J29" s="6" t="str">
-        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
+        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
         <v/>
       </c>
       <c r="K29" s="6" t="str">
-        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
+        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
         <v/>
       </c>
       <c r="L29" s="6" t="str">
@@ -11622,15 +12437,15 @@
         <v/>
       </c>
       <c r="I30" s="6" t="str">
-        <f aca="false">IF($B30&lt;&gt;"B","",IFERROR(IF($D30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$D30,1)),0))</f>
+        <f aca="false">IF($B30&lt;&gt;"B","",IFERROR(IF($D30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$D30,1)),0))</f>
         <v/>
       </c>
       <c r="J30" s="6" t="str">
-        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
+        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
         <v/>
       </c>
       <c r="K30" s="6" t="str">
-        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
+        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
         <v/>
       </c>
       <c r="L30" s="6" t="str">
@@ -11672,15 +12487,15 @@
         <v/>
       </c>
       <c r="I31" s="6" t="str">
-        <f aca="false">IF($B31&lt;&gt;"B","",IFERROR(IF($D31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$D31,1)),0))</f>
+        <f aca="false">IF($B31&lt;&gt;"B","",IFERROR(IF($D31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$D31,1)),0))</f>
         <v/>
       </c>
       <c r="J31" s="6" t="str">
-        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
+        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
         <v/>
       </c>
       <c r="K31" s="6" t="str">
-        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
+        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
         <v/>
       </c>
       <c r="L31" s="6" t="str">
@@ -11722,15 +12537,15 @@
         <v/>
       </c>
       <c r="I32" s="6" t="str">
-        <f aca="false">IF($B32&lt;&gt;"B","",IFERROR(IF($D32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$D32,1)),0))</f>
+        <f aca="false">IF($B32&lt;&gt;"B","",IFERROR(IF($D32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$D32,1)),0))</f>
         <v/>
       </c>
       <c r="J32" s="6" t="str">
-        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
+        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
         <v/>
       </c>
       <c r="K32" s="6" t="str">
-        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
+        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
         <v/>
       </c>
       <c r="L32" s="6" t="str">
@@ -11772,15 +12587,15 @@
         <v/>
       </c>
       <c r="I33" s="6" t="str">
-        <f aca="false">IF($B33&lt;&gt;"B","",IFERROR(IF($D33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$D33,1)),0))</f>
+        <f aca="false">IF($B33&lt;&gt;"B","",IFERROR(IF($D33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$D33,1)),0))</f>
         <v/>
       </c>
       <c r="J33" s="6" t="str">
-        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
+        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
         <v/>
       </c>
       <c r="K33" s="6" t="str">
-        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
+        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
         <v/>
       </c>
       <c r="L33" s="6" t="str">
@@ -11822,15 +12637,15 @@
         <v/>
       </c>
       <c r="I34" s="6" t="str">
-        <f aca="false">IF($B34&lt;&gt;"B","",IFERROR(IF($D34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$D34,1)),0))</f>
+        <f aca="false">IF($B34&lt;&gt;"B","",IFERROR(IF($D34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$D34,1)),0))</f>
         <v/>
       </c>
       <c r="J34" s="6" t="str">
-        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
+        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
         <v/>
       </c>
       <c r="K34" s="6" t="str">
-        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
+        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
         <v/>
       </c>
       <c r="L34" s="6" t="str">
@@ -11872,15 +12687,15 @@
         <v/>
       </c>
       <c r="I35" s="6" t="str">
-        <f aca="false">IF($B35&lt;&gt;"B","",IFERROR(IF($D35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$D35,1)),0))</f>
+        <f aca="false">IF($B35&lt;&gt;"B","",IFERROR(IF($D35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$D35,1)),0))</f>
         <v/>
       </c>
       <c r="J35" s="6" t="str">
-        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
+        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
         <v/>
       </c>
       <c r="K35" s="6" t="str">
-        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
+        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
         <v/>
       </c>
       <c r="L35" s="6" t="str">
@@ -11922,15 +12737,15 @@
         <v/>
       </c>
       <c r="I36" s="6" t="str">
-        <f aca="false">IF($B36&lt;&gt;"B","",IFERROR(IF($D36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$D36,1)),0))</f>
+        <f aca="false">IF($B36&lt;&gt;"B","",IFERROR(IF($D36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$D36,1)),0))</f>
         <v/>
       </c>
       <c r="J36" s="6" t="str">
-        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
+        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
         <v/>
       </c>
       <c r="K36" s="6" t="str">
-        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
+        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
         <v/>
       </c>
       <c r="L36" s="6" t="str">
@@ -11972,15 +12787,15 @@
         <v/>
       </c>
       <c r="I37" s="6" t="str">
-        <f aca="false">IF($B37&lt;&gt;"B","",IFERROR(IF($D37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$D37,1)),0))</f>
+        <f aca="false">IF($B37&lt;&gt;"B","",IFERROR(IF($D37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$D37,1)),0))</f>
         <v/>
       </c>
       <c r="J37" s="6" t="str">
-        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
+        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
         <v/>
       </c>
       <c r="K37" s="6" t="str">
-        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
+        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
         <v/>
       </c>
       <c r="L37" s="6" t="str">
@@ -12022,15 +12837,15 @@
         <v/>
       </c>
       <c r="I38" s="6" t="str">
-        <f aca="false">IF($B38&lt;&gt;"B","",IFERROR(IF($D38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$D38,1)),0))</f>
+        <f aca="false">IF($B38&lt;&gt;"B","",IFERROR(IF($D38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$D38,1)),0))</f>
         <v/>
       </c>
       <c r="J38" s="6" t="str">
-        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
+        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
         <v/>
       </c>
       <c r="K38" s="6" t="str">
-        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
+        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
         <v/>
       </c>
       <c r="L38" s="6" t="str">
@@ -12072,15 +12887,15 @@
         <v/>
       </c>
       <c r="I39" s="6" t="str">
-        <f aca="false">IF($B39&lt;&gt;"B","",IFERROR(IF($D39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$D39,1)),0))</f>
+        <f aca="false">IF($B39&lt;&gt;"B","",IFERROR(IF($D39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$D39,1)),0))</f>
         <v/>
       </c>
       <c r="J39" s="6" t="str">
-        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
+        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
         <v/>
       </c>
       <c r="K39" s="6" t="str">
-        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
+        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
         <v/>
       </c>
       <c r="L39" s="6" t="str">
@@ -12122,15 +12937,15 @@
         <v/>
       </c>
       <c r="I40" s="6" t="str">
-        <f aca="false">IF($B40&lt;&gt;"B","",IFERROR(IF($D40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$D40,1)),0))</f>
+        <f aca="false">IF($B40&lt;&gt;"B","",IFERROR(IF($D40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$D40,1)),0))</f>
         <v/>
       </c>
       <c r="J40" s="6" t="str">
-        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
+        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
         <v/>
       </c>
       <c r="K40" s="6" t="str">
-        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
+        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
         <v/>
       </c>
       <c r="L40" s="6" t="str">
@@ -12172,15 +12987,15 @@
         <v/>
       </c>
       <c r="I41" s="6" t="str">
-        <f aca="false">IF($B41&lt;&gt;"B","",IFERROR(IF($D41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$D41,1)),0))</f>
+        <f aca="false">IF($B41&lt;&gt;"B","",IFERROR(IF($D41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$D41,1)),0))</f>
         <v/>
       </c>
       <c r="J41" s="6" t="str">
-        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
+        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
         <v/>
       </c>
       <c r="K41" s="6" t="str">
-        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
+        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
         <v/>
       </c>
       <c r="L41" s="6" t="str">
@@ -12222,15 +13037,15 @@
         <v/>
       </c>
       <c r="I42" s="6" t="str">
-        <f aca="false">IF($B42&lt;&gt;"B","",IFERROR(IF($D42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$D42,1)),0))</f>
+        <f aca="false">IF($B42&lt;&gt;"B","",IFERROR(IF($D42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$D42,1)),0))</f>
         <v/>
       </c>
       <c r="J42" s="6" t="str">
-        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
+        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
         <v/>
       </c>
       <c r="K42" s="6" t="str">
-        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
+        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
         <v/>
       </c>
       <c r="L42" s="6" t="str">
@@ -12272,15 +13087,15 @@
         <v/>
       </c>
       <c r="I43" s="6" t="str">
-        <f aca="false">IF($B43&lt;&gt;"B","",IFERROR(IF($D43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$D43,1)),0))</f>
+        <f aca="false">IF($B43&lt;&gt;"B","",IFERROR(IF($D43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$D43,1)),0))</f>
         <v/>
       </c>
       <c r="J43" s="6" t="str">
-        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
+        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
         <v/>
       </c>
       <c r="K43" s="6" t="str">
-        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
+        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
         <v/>
       </c>
       <c r="L43" s="6" t="str">
@@ -12322,15 +13137,15 @@
         <v/>
       </c>
       <c r="I44" s="6" t="str">
-        <f aca="false">IF($B44&lt;&gt;"B","",IFERROR(IF($D44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$D44,1)),0))</f>
+        <f aca="false">IF($B44&lt;&gt;"B","",IFERROR(IF($D44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$D44,1)),0))</f>
         <v/>
       </c>
       <c r="J44" s="6" t="str">
-        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
+        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
         <v/>
       </c>
       <c r="K44" s="6" t="str">
-        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
+        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
         <v/>
       </c>
       <c r="L44" s="6" t="str">
@@ -12372,15 +13187,15 @@
         <v/>
       </c>
       <c r="I45" s="6" t="str">
-        <f aca="false">IF($B45&lt;&gt;"B","",IFERROR(IF($D45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$D45,1)),0))</f>
+        <f aca="false">IF($B45&lt;&gt;"B","",IFERROR(IF($D45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$D45,1)),0))</f>
         <v/>
       </c>
       <c r="J45" s="6" t="str">
-        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
+        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
         <v/>
       </c>
       <c r="K45" s="6" t="str">
-        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
+        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
         <v/>
       </c>
       <c r="L45" s="6" t="str">
@@ -12422,15 +13237,15 @@
         <v/>
       </c>
       <c r="I46" s="6" t="str">
-        <f aca="false">IF($B46&lt;&gt;"B","",IFERROR(IF($D46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$D46,1)),0))</f>
+        <f aca="false">IF($B46&lt;&gt;"B","",IFERROR(IF($D46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$D46,1)),0))</f>
         <v/>
       </c>
       <c r="J46" s="6" t="str">
-        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
+        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
         <v/>
       </c>
       <c r="K46" s="6" t="str">
-        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
+        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
         <v/>
       </c>
       <c r="L46" s="6" t="str">
@@ -12472,15 +13287,15 @@
         <v/>
       </c>
       <c r="I47" s="6" t="str">
-        <f aca="false">IF($B47&lt;&gt;"B","",IFERROR(IF($D47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$D47,1)),0))</f>
+        <f aca="false">IF($B47&lt;&gt;"B","",IFERROR(IF($D47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$D47,1)),0))</f>
         <v/>
       </c>
       <c r="J47" s="6" t="str">
-        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
+        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
         <v/>
       </c>
       <c r="K47" s="6" t="str">
-        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
+        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
         <v/>
       </c>
       <c r="L47" s="6" t="str">
@@ -12522,15 +13337,15 @@
         <v/>
       </c>
       <c r="I48" s="6" t="str">
-        <f aca="false">IF($B48&lt;&gt;"B","",IFERROR(IF($D48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$D48,1)),0))</f>
+        <f aca="false">IF($B48&lt;&gt;"B","",IFERROR(IF($D48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$D48,1)),0))</f>
         <v/>
       </c>
       <c r="J48" s="6" t="str">
-        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
+        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
         <v/>
       </c>
       <c r="K48" s="6" t="str">
-        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
+        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
         <v/>
       </c>
       <c r="L48" s="6" t="str">
@@ -12572,15 +13387,15 @@
         <v/>
       </c>
       <c r="I49" s="6" t="str">
-        <f aca="false">IF($B49&lt;&gt;"B","",IFERROR(IF($D49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$D49,1)),0))</f>
+        <f aca="false">IF($B49&lt;&gt;"B","",IFERROR(IF($D49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$D49,1)),0))</f>
         <v/>
       </c>
       <c r="J49" s="6" t="str">
-        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
+        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
         <v/>
       </c>
       <c r="K49" s="6" t="str">
-        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
+        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
         <v/>
       </c>
       <c r="L49" s="6" t="str">
@@ -12622,15 +13437,15 @@
         <v/>
       </c>
       <c r="I50" s="6" t="str">
-        <f aca="false">IF($B50&lt;&gt;"B","",IFERROR(IF($D50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$D50,1)),0))</f>
+        <f aca="false">IF($B50&lt;&gt;"B","",IFERROR(IF($D50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$D50,1)),0))</f>
         <v/>
       </c>
       <c r="J50" s="6" t="str">
-        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
+        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
         <v/>
       </c>
       <c r="K50" s="6" t="str">
-        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
+        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
         <v/>
       </c>
       <c r="L50" s="6" t="str">
@@ -12672,15 +13487,15 @@
         <v/>
       </c>
       <c r="I51" s="6" t="str">
-        <f aca="false">IF($B51&lt;&gt;"B","",IFERROR(IF($D51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$D51,1)),0))</f>
+        <f aca="false">IF($B51&lt;&gt;"B","",IFERROR(IF($D51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$D51,1)),0))</f>
         <v/>
       </c>
       <c r="J51" s="6" t="str">
-        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
+        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
         <v/>
       </c>
       <c r="K51" s="6" t="str">
-        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
+        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
         <v/>
       </c>
       <c r="L51" s="6" t="str">
@@ -12722,15 +13537,15 @@
         <v/>
       </c>
       <c r="I52" s="6" t="str">
-        <f aca="false">IF($B52&lt;&gt;"B","",IFERROR(IF($D52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$D52,1)),0))</f>
+        <f aca="false">IF($B52&lt;&gt;"B","",IFERROR(IF($D52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$D52,1)),0))</f>
         <v/>
       </c>
       <c r="J52" s="6" t="str">
-        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
+        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
         <v/>
       </c>
       <c r="K52" s="6" t="str">
-        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
+        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
         <v/>
       </c>
       <c r="L52" s="6" t="str">
@@ -12772,15 +13587,15 @@
         <v/>
       </c>
       <c r="I53" s="6" t="str">
-        <f aca="false">IF($B53&lt;&gt;"B","",IFERROR(IF($D53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$D53,1)),0))</f>
+        <f aca="false">IF($B53&lt;&gt;"B","",IFERROR(IF($D53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$D53,1)),0))</f>
         <v/>
       </c>
       <c r="J53" s="6" t="str">
-        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
+        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
         <v/>
       </c>
       <c r="K53" s="6" t="str">
-        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
+        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
         <v/>
       </c>
       <c r="L53" s="6" t="str">
@@ -12822,15 +13637,15 @@
         <v/>
       </c>
       <c r="I54" s="6" t="str">
-        <f aca="false">IF($B54&lt;&gt;"B","",IFERROR(IF($D54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$D54,1)),0))</f>
+        <f aca="false">IF($B54&lt;&gt;"B","",IFERROR(IF($D54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$D54,1)),0))</f>
         <v/>
       </c>
       <c r="J54" s="6" t="str">
-        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
+        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
         <v/>
       </c>
       <c r="K54" s="6" t="str">
-        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
+        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
         <v/>
       </c>
       <c r="L54" s="6" t="str">
@@ -12872,15 +13687,15 @@
         <v/>
       </c>
       <c r="I55" s="6" t="str">
-        <f aca="false">IF($B55&lt;&gt;"B","",IFERROR(IF($D55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$D55,1)),0))</f>
+        <f aca="false">IF($B55&lt;&gt;"B","",IFERROR(IF($D55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$D55,1)),0))</f>
         <v/>
       </c>
       <c r="J55" s="6" t="str">
-        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
+        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
         <v/>
       </c>
       <c r="K55" s="6" t="str">
-        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
+        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
         <v/>
       </c>
       <c r="L55" s="6" t="str">
@@ -12922,15 +13737,15 @@
         <v/>
       </c>
       <c r="I56" s="6" t="str">
-        <f aca="false">IF($B56&lt;&gt;"B","",IFERROR(IF($D56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$D56,1)),0))</f>
+        <f aca="false">IF($B56&lt;&gt;"B","",IFERROR(IF($D56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$D56,1)),0))</f>
         <v/>
       </c>
       <c r="J56" s="6" t="str">
-        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
+        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
         <v/>
       </c>
       <c r="K56" s="6" t="str">
-        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
+        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
         <v/>
       </c>
       <c r="L56" s="6" t="str">
@@ -12972,15 +13787,15 @@
         <v/>
       </c>
       <c r="I57" s="6" t="str">
-        <f aca="false">IF($B57&lt;&gt;"B","",IFERROR(IF($D57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$D57,1)),0))</f>
+        <f aca="false">IF($B57&lt;&gt;"B","",IFERROR(IF($D57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$D57,1)),0))</f>
         <v/>
       </c>
       <c r="J57" s="6" t="str">
-        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
+        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
         <v/>
       </c>
       <c r="K57" s="6" t="str">
-        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
+        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
         <v/>
       </c>
       <c r="L57" s="6" t="str">
@@ -13022,15 +13837,15 @@
         <v/>
       </c>
       <c r="I58" s="6" t="str">
-        <f aca="false">IF($B58&lt;&gt;"B","",IFERROR(IF($D58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$D58,1)),0))</f>
+        <f aca="false">IF($B58&lt;&gt;"B","",IFERROR(IF($D58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$D58,1)),0))</f>
         <v/>
       </c>
       <c r="J58" s="6" t="str">
-        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
+        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
         <v/>
       </c>
       <c r="K58" s="6" t="str">
-        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
+        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
         <v/>
       </c>
       <c r="L58" s="6" t="str">
@@ -13072,15 +13887,15 @@
         <v/>
       </c>
       <c r="I59" s="6" t="str">
-        <f aca="false">IF($B59&lt;&gt;"B","",IFERROR(IF($D59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$D59,1)),0))</f>
+        <f aca="false">IF($B59&lt;&gt;"B","",IFERROR(IF($D59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$D59,1)),0))</f>
         <v/>
       </c>
       <c r="J59" s="6" t="str">
-        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
+        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
         <v/>
       </c>
       <c r="K59" s="6" t="str">
-        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
+        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
         <v/>
       </c>
       <c r="L59" s="6" t="str">
@@ -13122,15 +13937,15 @@
         <v/>
       </c>
       <c r="I60" s="6" t="str">
-        <f aca="false">IF($B60&lt;&gt;"B","",IFERROR(IF($D60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$D60,1)),0))</f>
+        <f aca="false">IF($B60&lt;&gt;"B","",IFERROR(IF($D60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$D60,1)),0))</f>
         <v/>
       </c>
       <c r="J60" s="6" t="str">
-        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
+        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
         <v/>
       </c>
       <c r="K60" s="6" t="str">
-        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
+        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
         <v/>
       </c>
       <c r="L60" s="6" t="str">
@@ -13172,15 +13987,15 @@
         <v/>
       </c>
       <c r="I61" s="6" t="str">
-        <f aca="false">IF($B61&lt;&gt;"B","",IFERROR(IF($D61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$D61,1)),0))</f>
+        <f aca="false">IF($B61&lt;&gt;"B","",IFERROR(IF($D61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$D61,1)),0))</f>
         <v/>
       </c>
       <c r="J61" s="6" t="str">
-        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
+        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
         <v/>
       </c>
       <c r="K61" s="6" t="str">
-        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
+        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
         <v/>
       </c>
       <c r="L61" s="6" t="str">
@@ -13222,15 +14037,15 @@
         <v/>
       </c>
       <c r="I62" s="6" t="str">
-        <f aca="false">IF($B62&lt;&gt;"B","",IFERROR(IF($D62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$D62,1)),0))</f>
+        <f aca="false">IF($B62&lt;&gt;"B","",IFERROR(IF($D62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$D62,1)),0))</f>
         <v/>
       </c>
       <c r="J62" s="6" t="str">
-        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
+        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
         <v/>
       </c>
       <c r="K62" s="6" t="str">
-        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
+        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
         <v/>
       </c>
       <c r="L62" s="6" t="str">
@@ -13272,15 +14087,15 @@
         <v/>
       </c>
       <c r="I63" s="6" t="str">
-        <f aca="false">IF($B63&lt;&gt;"B","",IFERROR(IF($D63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$D63,1)),0))</f>
+        <f aca="false">IF($B63&lt;&gt;"B","",IFERROR(IF($D63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$D63,1)),0))</f>
         <v/>
       </c>
       <c r="J63" s="6" t="str">
-        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
+        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
         <v/>
       </c>
       <c r="K63" s="6" t="str">
-        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
+        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
         <v/>
       </c>
       <c r="L63" s="6" t="str">
@@ -13322,15 +14137,15 @@
         <v/>
       </c>
       <c r="I64" s="6" t="str">
-        <f aca="false">IF($B64&lt;&gt;"B","",IFERROR(IF($D64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$D64,1)),0))</f>
+        <f aca="false">IF($B64&lt;&gt;"B","",IFERROR(IF($D64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$D64,1)),0))</f>
         <v/>
       </c>
       <c r="J64" s="6" t="str">
-        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
+        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
         <v/>
       </c>
       <c r="K64" s="6" t="str">
-        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
+        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
         <v/>
       </c>
       <c r="L64" s="6" t="str">
@@ -13372,15 +14187,15 @@
         <v/>
       </c>
       <c r="I65" s="6" t="str">
-        <f aca="false">IF($B65&lt;&gt;"B","",IFERROR(IF($D65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$D65,1)),0))</f>
+        <f aca="false">IF($B65&lt;&gt;"B","",IFERROR(IF($D65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$D65,1)),0))</f>
         <v/>
       </c>
       <c r="J65" s="6" t="str">
-        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
+        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
         <v/>
       </c>
       <c r="K65" s="6" t="str">
-        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
+        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
         <v/>
       </c>
       <c r="L65" s="6" t="str">
@@ -13422,15 +14237,15 @@
         <v/>
       </c>
       <c r="I66" s="6" t="str">
-        <f aca="false">IF($B66&lt;&gt;"B","",IFERROR(IF($D66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$D66,1)),0))</f>
+        <f aca="false">IF($B66&lt;&gt;"B","",IFERROR(IF($D66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$D66,1)),0))</f>
         <v/>
       </c>
       <c r="J66" s="6" t="str">
-        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
+        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
         <v/>
       </c>
       <c r="K66" s="6" t="str">
-        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
+        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
         <v/>
       </c>
       <c r="L66" s="6" t="str">
@@ -13472,15 +14287,15 @@
         <v/>
       </c>
       <c r="I67" s="6" t="str">
-        <f aca="false">IF($B67&lt;&gt;"B","",IFERROR(IF($D67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$D67,1)),0))</f>
+        <f aca="false">IF($B67&lt;&gt;"B","",IFERROR(IF($D67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$D67,1)),0))</f>
         <v/>
       </c>
       <c r="J67" s="6" t="str">
-        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
+        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
         <v/>
       </c>
       <c r="K67" s="6" t="str">
-        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
+        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
         <v/>
       </c>
       <c r="L67" s="6" t="str">
@@ -13522,15 +14337,15 @@
         <v/>
       </c>
       <c r="I68" s="6" t="str">
-        <f aca="false">IF($B68&lt;&gt;"B","",IFERROR(IF($D68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$D68,1)),0))</f>
+        <f aca="false">IF($B68&lt;&gt;"B","",IFERROR(IF($D68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$D68,1)),0))</f>
         <v/>
       </c>
       <c r="J68" s="6" t="str">
-        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
+        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
         <v/>
       </c>
       <c r="K68" s="6" t="str">
-        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
+        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
         <v/>
       </c>
       <c r="L68" s="6" t="str">
@@ -13572,15 +14387,15 @@
         <v/>
       </c>
       <c r="I69" s="6" t="str">
-        <f aca="false">IF($B69&lt;&gt;"B","",IFERROR(IF($D69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$D69,1)),0))</f>
+        <f aca="false">IF($B69&lt;&gt;"B","",IFERROR(IF($D69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$D69,1)),0))</f>
         <v/>
       </c>
       <c r="J69" s="6" t="str">
-        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
+        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
         <v/>
       </c>
       <c r="K69" s="6" t="str">
-        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
+        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
         <v/>
       </c>
       <c r="L69" s="6" t="str">
@@ -13622,15 +14437,15 @@
         <v/>
       </c>
       <c r="I70" s="6" t="str">
-        <f aca="false">IF($B70&lt;&gt;"B","",IFERROR(IF($D70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$D70,1)),0))</f>
+        <f aca="false">IF($B70&lt;&gt;"B","",IFERROR(IF($D70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$D70,1)),0))</f>
         <v/>
       </c>
       <c r="J70" s="6" t="str">
-        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
+        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
         <v/>
       </c>
       <c r="K70" s="6" t="str">
-        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
+        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
         <v/>
       </c>
       <c r="L70" s="6" t="str">
@@ -13672,15 +14487,15 @@
         <v/>
       </c>
       <c r="I71" s="6" t="str">
-        <f aca="false">IF($B71&lt;&gt;"B","",IFERROR(IF($D71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$D71,1)),0))</f>
+        <f aca="false">IF($B71&lt;&gt;"B","",IFERROR(IF($D71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$D71,1)),0))</f>
         <v/>
       </c>
       <c r="J71" s="6" t="str">
-        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
+        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
         <v/>
       </c>
       <c r="K71" s="6" t="str">
-        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
+        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
         <v/>
       </c>
       <c r="L71" s="6" t="str">
@@ -13722,15 +14537,15 @@
         <v/>
       </c>
       <c r="I72" s="6" t="str">
-        <f aca="false">IF($B72&lt;&gt;"B","",IFERROR(IF($D72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$D72,1)),0))</f>
+        <f aca="false">IF($B72&lt;&gt;"B","",IFERROR(IF($D72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$D72,1)),0))</f>
         <v/>
       </c>
       <c r="J72" s="6" t="str">
-        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
+        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
         <v/>
       </c>
       <c r="K72" s="6" t="str">
-        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
+        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
         <v/>
       </c>
       <c r="L72" s="6" t="str">
@@ -13772,15 +14587,15 @@
         <v/>
       </c>
       <c r="I73" s="6" t="str">
-        <f aca="false">IF($B73&lt;&gt;"B","",IFERROR(IF($D73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$D73,1)),0))</f>
+        <f aca="false">IF($B73&lt;&gt;"B","",IFERROR(IF($D73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$D73,1)),0))</f>
         <v/>
       </c>
       <c r="J73" s="6" t="str">
-        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
+        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
         <v/>
       </c>
       <c r="K73" s="6" t="str">
-        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
+        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
         <v/>
       </c>
       <c r="L73" s="6" t="str">
@@ -13822,15 +14637,15 @@
         <v/>
       </c>
       <c r="I74" s="6" t="str">
-        <f aca="false">IF($B74&lt;&gt;"B","",IFERROR(IF($D74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$D74,1)),0))</f>
+        <f aca="false">IF($B74&lt;&gt;"B","",IFERROR(IF($D74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$D74,1)),0))</f>
         <v/>
       </c>
       <c r="J74" s="6" t="str">
-        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
+        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
         <v/>
       </c>
       <c r="K74" s="6" t="str">
-        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
+        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
         <v/>
       </c>
       <c r="L74" s="6" t="str">
@@ -13872,15 +14687,15 @@
         <v/>
       </c>
       <c r="I75" s="6" t="str">
-        <f aca="false">IF($B75&lt;&gt;"B","",IFERROR(IF($D75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$D75,1)),0))</f>
+        <f aca="false">IF($B75&lt;&gt;"B","",IFERROR(IF($D75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$D75,1)),0))</f>
         <v/>
       </c>
       <c r="J75" s="6" t="str">
-        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
+        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
         <v/>
       </c>
       <c r="K75" s="6" t="str">
-        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
+        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
         <v/>
       </c>
       <c r="L75" s="6" t="str">
@@ -13922,15 +14737,15 @@
         <v/>
       </c>
       <c r="I76" s="6" t="str">
-        <f aca="false">IF($B76&lt;&gt;"B","",IFERROR(IF($D76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$D76,1)),0))</f>
+        <f aca="false">IF($B76&lt;&gt;"B","",IFERROR(IF($D76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$D76,1)),0))</f>
         <v/>
       </c>
       <c r="J76" s="6" t="str">
-        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
+        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
         <v/>
       </c>
       <c r="K76" s="6" t="str">
-        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
+        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
         <v/>
       </c>
       <c r="L76" s="6" t="str">
@@ -13972,15 +14787,15 @@
         <v/>
       </c>
       <c r="I77" s="6" t="str">
-        <f aca="false">IF($B77&lt;&gt;"B","",IFERROR(IF($D77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$D77,1)),0))</f>
+        <f aca="false">IF($B77&lt;&gt;"B","",IFERROR(IF($D77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$D77,1)),0))</f>
         <v/>
       </c>
       <c r="J77" s="6" t="str">
-        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
+        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
         <v/>
       </c>
       <c r="K77" s="6" t="str">
-        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
+        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
         <v/>
       </c>
       <c r="L77" s="6" t="str">
@@ -14022,15 +14837,15 @@
         <v/>
       </c>
       <c r="I78" s="6" t="str">
-        <f aca="false">IF($B78&lt;&gt;"B","",IFERROR(IF($D78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$D78,1)),0))</f>
+        <f aca="false">IF($B78&lt;&gt;"B","",IFERROR(IF($D78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$D78,1)),0))</f>
         <v/>
       </c>
       <c r="J78" s="6" t="str">
-        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
+        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
         <v/>
       </c>
       <c r="K78" s="6" t="str">
-        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
+        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
         <v/>
       </c>
       <c r="L78" s="6" t="str">
@@ -14072,15 +14887,15 @@
         <v/>
       </c>
       <c r="I79" s="6" t="str">
-        <f aca="false">IF($B79&lt;&gt;"B","",IFERROR(IF($D79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$D79,1)),0))</f>
+        <f aca="false">IF($B79&lt;&gt;"B","",IFERROR(IF($D79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$D79,1)),0))</f>
         <v/>
       </c>
       <c r="J79" s="6" t="str">
-        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
+        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
         <v/>
       </c>
       <c r="K79" s="6" t="str">
-        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
+        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
         <v/>
       </c>
       <c r="L79" s="6" t="str">
@@ -14122,15 +14937,15 @@
         <v/>
       </c>
       <c r="I80" s="6" t="str">
-        <f aca="false">IF($B80&lt;&gt;"B","",IFERROR(IF($D80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$D80,1)),0))</f>
+        <f aca="false">IF($B80&lt;&gt;"B","",IFERROR(IF($D80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$D80,1)),0))</f>
         <v/>
       </c>
       <c r="J80" s="6" t="str">
-        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
+        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
         <v/>
       </c>
       <c r="K80" s="6" t="str">
-        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
+        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
         <v/>
       </c>
       <c r="L80" s="6" t="str">
@@ -14172,15 +14987,15 @@
         <v/>
       </c>
       <c r="I81" s="6" t="str">
-        <f aca="false">IF($B81&lt;&gt;"B","",IFERROR(IF($D81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$D81,1)),0))</f>
+        <f aca="false">IF($B81&lt;&gt;"B","",IFERROR(IF($D81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$D81,1)),0))</f>
         <v/>
       </c>
       <c r="J81" s="6" t="str">
-        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
+        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
         <v/>
       </c>
       <c r="K81" s="6" t="str">
-        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
+        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
         <v/>
       </c>
       <c r="L81" s="6" t="str">
@@ -14222,15 +15037,15 @@
         <v/>
       </c>
       <c r="I82" s="6" t="str">
-        <f aca="false">IF($B82&lt;&gt;"B","",IFERROR(IF($D82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$D82,1)),0))</f>
+        <f aca="false">IF($B82&lt;&gt;"B","",IFERROR(IF($D82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$D82,1)),0))</f>
         <v/>
       </c>
       <c r="J82" s="6" t="str">
-        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
+        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
         <v/>
       </c>
       <c r="K82" s="6" t="str">
-        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
+        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
         <v/>
       </c>
       <c r="L82" s="6" t="str">
@@ -14272,15 +15087,15 @@
         <v/>
       </c>
       <c r="I83" s="6" t="str">
-        <f aca="false">IF($B83&lt;&gt;"B","",IFERROR(IF($D83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$D83,1)),0))</f>
+        <f aca="false">IF($B83&lt;&gt;"B","",IFERROR(IF($D83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$D83,1)),0))</f>
         <v/>
       </c>
       <c r="J83" s="6" t="str">
-        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
+        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
         <v/>
       </c>
       <c r="K83" s="6" t="str">
-        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
+        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
         <v/>
       </c>
       <c r="L83" s="6" t="str">
@@ -14322,15 +15137,15 @@
         <v/>
       </c>
       <c r="I84" s="6" t="str">
-        <f aca="false">IF($B84&lt;&gt;"B","",IFERROR(IF($D84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$D84,1)),0))</f>
+        <f aca="false">IF($B84&lt;&gt;"B","",IFERROR(IF($D84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$D84,1)),0))</f>
         <v/>
       </c>
       <c r="J84" s="6" t="str">
-        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
+        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
         <v/>
       </c>
       <c r="K84" s="6" t="str">
-        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
+        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
         <v/>
       </c>
       <c r="L84" s="6" t="str">
@@ -14372,15 +15187,15 @@
         <v/>
       </c>
       <c r="I85" s="6" t="str">
-        <f aca="false">IF($B85&lt;&gt;"B","",IFERROR(IF($D85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$D85,1)),0))</f>
+        <f aca="false">IF($B85&lt;&gt;"B","",IFERROR(IF($D85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$D85,1)),0))</f>
         <v/>
       </c>
       <c r="J85" s="6" t="str">
-        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
+        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
         <v/>
       </c>
       <c r="K85" s="6" t="str">
-        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
+        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
         <v/>
       </c>
       <c r="L85" s="6" t="str">
@@ -14422,15 +15237,15 @@
         <v/>
       </c>
       <c r="I86" s="6" t="str">
-        <f aca="false">IF($B86&lt;&gt;"B","",IFERROR(IF($D86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$D86,1)),0))</f>
+        <f aca="false">IF($B86&lt;&gt;"B","",IFERROR(IF($D86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$D86,1)),0))</f>
         <v/>
       </c>
       <c r="J86" s="6" t="str">
-        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
+        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
         <v/>
       </c>
       <c r="K86" s="6" t="str">
-        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
+        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
         <v/>
       </c>
       <c r="L86" s="6" t="str">
@@ -14472,15 +15287,15 @@
         <v/>
       </c>
       <c r="I87" s="6" t="str">
-        <f aca="false">IF($B87&lt;&gt;"B","",IFERROR(IF($D87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$D87,1)),0))</f>
+        <f aca="false">IF($B87&lt;&gt;"B","",IFERROR(IF($D87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$D87,1)),0))</f>
         <v/>
       </c>
       <c r="J87" s="6" t="str">
-        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
+        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
         <v/>
       </c>
       <c r="K87" s="6" t="str">
-        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
+        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
         <v/>
       </c>
       <c r="L87" s="6" t="str">
@@ -14522,15 +15337,15 @@
         <v/>
       </c>
       <c r="I88" s="6" t="str">
-        <f aca="false">IF($B88&lt;&gt;"B","",IFERROR(IF($D88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$D88,1)),0))</f>
+        <f aca="false">IF($B88&lt;&gt;"B","",IFERROR(IF($D88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$D88,1)),0))</f>
         <v/>
       </c>
       <c r="J88" s="6" t="str">
-        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
+        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
         <v/>
       </c>
       <c r="K88" s="6" t="str">
-        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
+        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
         <v/>
       </c>
       <c r="L88" s="6" t="str">
@@ -14572,15 +15387,15 @@
         <v/>
       </c>
       <c r="I89" s="6" t="str">
-        <f aca="false">IF($B89&lt;&gt;"B","",IFERROR(IF($D89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$D89,1)),0))</f>
+        <f aca="false">IF($B89&lt;&gt;"B","",IFERROR(IF($D89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$D89,1)),0))</f>
         <v/>
       </c>
       <c r="J89" s="6" t="str">
-        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
+        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
         <v/>
       </c>
       <c r="K89" s="6" t="str">
-        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
+        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
         <v/>
       </c>
       <c r="L89" s="6" t="str">
@@ -14622,15 +15437,15 @@
         <v/>
       </c>
       <c r="I90" s="6" t="str">
-        <f aca="false">IF($B90&lt;&gt;"B","",IFERROR(IF($D90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$D90,1)),0))</f>
+        <f aca="false">IF($B90&lt;&gt;"B","",IFERROR(IF($D90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$D90,1)),0))</f>
         <v/>
       </c>
       <c r="J90" s="6" t="str">
-        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
+        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
         <v/>
       </c>
       <c r="K90" s="6" t="str">
-        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
+        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
         <v/>
       </c>
       <c r="L90" s="6" t="str">
@@ -14672,15 +15487,15 @@
         <v/>
       </c>
       <c r="I91" s="6" t="str">
-        <f aca="false">IF($B91&lt;&gt;"B","",IFERROR(IF($D91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$D91,1)),0))</f>
+        <f aca="false">IF($B91&lt;&gt;"B","",IFERROR(IF($D91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$D91,1)),0))</f>
         <v/>
       </c>
       <c r="J91" s="6" t="str">
-        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
+        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
         <v/>
       </c>
       <c r="K91" s="6" t="str">
-        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
+        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
         <v/>
       </c>
       <c r="L91" s="6" t="str">
@@ -14722,15 +15537,15 @@
         <v/>
       </c>
       <c r="I92" s="6" t="str">
-        <f aca="false">IF($B92&lt;&gt;"B","",IFERROR(IF($D92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$D92,1)),0))</f>
+        <f aca="false">IF($B92&lt;&gt;"B","",IFERROR(IF($D92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$D92,1)),0))</f>
         <v/>
       </c>
       <c r="J92" s="6" t="str">
-        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
+        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
         <v/>
       </c>
       <c r="K92" s="6" t="str">
-        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
+        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
         <v/>
       </c>
       <c r="L92" s="6" t="str">
@@ -14772,15 +15587,15 @@
         <v/>
       </c>
       <c r="I93" s="6" t="str">
-        <f aca="false">IF($B93&lt;&gt;"B","",IFERROR(IF($D93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$D93,1)),0))</f>
+        <f aca="false">IF($B93&lt;&gt;"B","",IFERROR(IF($D93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$D93,1)),0))</f>
         <v/>
       </c>
       <c r="J93" s="6" t="str">
-        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
+        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
         <v/>
       </c>
       <c r="K93" s="6" t="str">
-        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
+        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
         <v/>
       </c>
       <c r="L93" s="6" t="str">
@@ -14822,15 +15637,15 @@
         <v/>
       </c>
       <c r="I94" s="6" t="str">
-        <f aca="false">IF($B94&lt;&gt;"B","",IFERROR(IF($D94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$D94,1)),0))</f>
+        <f aca="false">IF($B94&lt;&gt;"B","",IFERROR(IF($D94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$D94,1)),0))</f>
         <v/>
       </c>
       <c r="J94" s="6" t="str">
-        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
+        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
         <v/>
       </c>
       <c r="K94" s="6" t="str">
-        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
+        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
         <v/>
       </c>
       <c r="L94" s="6" t="str">
@@ -14872,15 +15687,15 @@
         <v/>
       </c>
       <c r="I95" s="6" t="str">
-        <f aca="false">IF($B95&lt;&gt;"B","",IFERROR(IF($D95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$D95,1)),0))</f>
+        <f aca="false">IF($B95&lt;&gt;"B","",IFERROR(IF($D95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$D95,1)),0))</f>
         <v/>
       </c>
       <c r="J95" s="6" t="str">
-        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
+        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
         <v/>
       </c>
       <c r="K95" s="6" t="str">
-        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
+        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
         <v/>
       </c>
       <c r="L95" s="6" t="str">
@@ -14922,15 +15737,15 @@
         <v/>
       </c>
       <c r="I96" s="6" t="str">
-        <f aca="false">IF($B96&lt;&gt;"B","",IFERROR(IF($D96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$D96,1)),0))</f>
+        <f aca="false">IF($B96&lt;&gt;"B","",IFERROR(IF($D96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$D96,1)),0))</f>
         <v/>
       </c>
       <c r="J96" s="6" t="str">
-        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
+        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
         <v/>
       </c>
       <c r="K96" s="6" t="str">
-        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
+        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
@@ -14972,15 +15787,15 @@
         <v/>
       </c>
       <c r="I97" s="6" t="str">
-        <f aca="false">IF($B97&lt;&gt;"B","",IFERROR(IF($D97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$D97,1)),0))</f>
+        <f aca="false">IF($B97&lt;&gt;"B","",IFERROR(IF($D97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$D97,1)),0))</f>
         <v/>
       </c>
       <c r="J97" s="6" t="str">
-        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
+        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
         <v/>
       </c>
       <c r="K97" s="6" t="str">
-        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
+        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
@@ -15022,15 +15837,15 @@
         <v/>
       </c>
       <c r="I98" s="6" t="str">
-        <f aca="false">IF($B98&lt;&gt;"B","",IFERROR(IF($D98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$D98,1)),0))</f>
+        <f aca="false">IF($B98&lt;&gt;"B","",IFERROR(IF($D98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$D98,1)),0))</f>
         <v/>
       </c>
       <c r="J98" s="6" t="str">
-        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
+        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
         <v/>
       </c>
       <c r="K98" s="6" t="str">
-        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
+        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
         <v/>
       </c>
       <c r="L98" s="6" t="str">
@@ -15072,15 +15887,15 @@
         <v/>
       </c>
       <c r="I99" s="6" t="str">
-        <f aca="false">IF($B99&lt;&gt;"B","",IFERROR(IF($D99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$D99,1)),0))</f>
+        <f aca="false">IF($B99&lt;&gt;"B","",IFERROR(IF($D99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$D99,1)),0))</f>
         <v/>
       </c>
       <c r="J99" s="6" t="str">
-        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
+        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
         <v/>
       </c>
       <c r="K99" s="6" t="str">
-        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
+        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
         <v/>
       </c>
       <c r="L99" s="6" t="str">
@@ -15122,15 +15937,15 @@
         <v/>
       </c>
       <c r="I100" s="6" t="str">
-        <f aca="false">IF($B100&lt;&gt;"B","",IFERROR(IF($D100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$D100,1)),0))</f>
+        <f aca="false">IF($B100&lt;&gt;"B","",IFERROR(IF($D100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$D100,1)),0))</f>
         <v/>
       </c>
       <c r="J100" s="6" t="str">
-        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
+        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
         <v/>
       </c>
       <c r="K100" s="6" t="str">
-        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
+        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
         <v/>
       </c>
       <c r="L100" s="6" t="str">
@@ -15172,15 +15987,15 @@
         <v/>
       </c>
       <c r="I101" s="6" t="str">
-        <f aca="false">IF($B101&lt;&gt;"B","",IFERROR(IF($D101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$D101,1)),0))</f>
+        <f aca="false">IF($B101&lt;&gt;"B","",IFERROR(IF($D101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$D101,1)),0))</f>
         <v/>
       </c>
       <c r="J101" s="6" t="str">
-        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
+        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
         <v/>
       </c>
       <c r="K101" s="6" t="str">
-        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
+        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
         <v/>
       </c>
       <c r="L101" s="6" t="str">
@@ -15222,15 +16037,15 @@
         <v/>
       </c>
       <c r="I102" s="6" t="str">
-        <f aca="false">IF($B102&lt;&gt;"B","",IFERROR(IF($D102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$D102,1)),0))</f>
+        <f aca="false">IF($B102&lt;&gt;"B","",IFERROR(IF($D102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$D102,1)),0))</f>
         <v/>
       </c>
       <c r="J102" s="6" t="str">
-        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
+        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
         <v/>
       </c>
       <c r="K102" s="6" t="str">
-        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
+        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
         <v/>
       </c>
       <c r="L102" s="6" t="str">
@@ -15272,15 +16087,15 @@
         <v/>
       </c>
       <c r="I103" s="6" t="str">
-        <f aca="false">IF($B103&lt;&gt;"B","",IFERROR(IF($D103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$D103,1)),0))</f>
+        <f aca="false">IF($B103&lt;&gt;"B","",IFERROR(IF($D103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$D103,1)),0))</f>
         <v/>
       </c>
       <c r="J103" s="6" t="str">
-        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
+        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
         <v/>
       </c>
       <c r="K103" s="6" t="str">
-        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
+        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
         <v/>
       </c>
       <c r="L103" s="6" t="str">
@@ -15322,15 +16137,15 @@
         <v/>
       </c>
       <c r="I104" s="6" t="str">
-        <f aca="false">IF($B104&lt;&gt;"B","",IFERROR(IF($D104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$D104,1)),0))</f>
+        <f aca="false">IF($B104&lt;&gt;"B","",IFERROR(IF($D104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$D104,1)),0))</f>
         <v/>
       </c>
       <c r="J104" s="6" t="str">
-        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
+        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
         <v/>
       </c>
       <c r="K104" s="6" t="str">
-        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$H$5:$H$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
+        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
         <v/>
       </c>
       <c r="L104" s="6" t="str">
@@ -15383,29 +16198,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15413,16 +16228,16 @@
         <v>46235</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15430,16 +16245,16 @@
         <v>46239</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15447,16 +16262,16 @@
         <v>46254</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15464,16 +16279,16 @@
         <v>46256</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15481,16 +16296,16 @@
         <v>46259</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>-20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17592,48 +18407,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">IF($D5="","",IF($B$3="Can pack now",INDEX('C Kits'!$F$5:$F$104,MATCH($A5,'C Kits'!$C$5:$C$104,0)),INDEX('C Kits'!$G$5:$G$104,MATCH($A5,'C Kits'!$C$5:$C$104,0))))</f>
@@ -17658,7 +18473,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">IF($D6="","",IF($B$3="Can pack now",INDEX('C Kits'!$F$5:$F$104,MATCH($A6,'C Kits'!$C$5:$C$104,0)),INDEX('C Kits'!$G$5:$G$104,MATCH($A6,'C Kits'!$C$5:$C$104,0))))</f>
@@ -17683,7 +18498,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B7" s="5" t="str">
         <f aca="false">IF($D7="","",IF($B$3="Can pack now",INDEX('C Kits'!$F$5:$F$104,MATCH($A7,'C Kits'!$C$5:$C$104,0)),INDEX('C Kits'!$G$5:$G$104,MATCH($A7,'C Kits'!$C$5:$C$104,0))))</f>

--- a/uploads/warehouse-stock-template.xlsx
+++ b/uploads/warehouse-stock-template.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="103">
   <si>
     <t xml:space="preserve">A — Loose Items (what you count on the shelf)</t>
   </si>
   <si>
-    <t xml:space="preserve">Type in the amber columns only; grey columns work themselves out. Opening Qty is your starting count — everything after it comes from the Movements tab. The three Sold columns say where the stock went: sold loose on its own, gone into a B item, or gone straight into a kit. Opening + Received - the three Sold columns + Adjusted = Stock in Hand.</t>
+    <t xml:space="preserve">Type in the amber columns only; grey columns work themselves out. Opening Qty is your starting count — everything after it comes from the Movements tab. Unit is a fixed list; Pcs per Pack only opens up on a unit that holds pieces (Box, Pack, Set, Bundle, Dozen, Roll). The three Sold columns say where the stock went: sold loose on its own, gone into a B item, or gone straight into a kit. Opening + Received - the three Sold columns + Adjusted = Stock in Hand.</t>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pcs per Pack</t>
   </si>
   <si>
     <t xml:space="preserve">Opening Qty</t>
@@ -72,7 +75,7 @@
     <t xml:space="preserve">White Balloon</t>
   </si>
   <si>
-    <t xml:space="preserve">pcs</t>
+    <t xml:space="preserve">Box</t>
   </si>
   <si>
     <t xml:space="preserve">EXAMPLE ROWS - delete rows 5-9 and put your own items in</t>
@@ -82,6 +85,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gold Foil Number 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pcs</t>
   </si>
   <si>
     <t xml:space="preserve">BOX-SM</t>
@@ -437,13 +443,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8E8E8"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -550,6 +556,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -585,8 +600,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FFE8E8E8"/>
-      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -793,17 +808,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -850,3150 +866,3272 @@
       <c r="K4" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="L4" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Receive"))</f>
         <v>500</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Sell"))</f>
         <v>0</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A5,Recipes!$B$5:$B$104,"B"))</f>
         <v>780</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A5,Recipes!$B$5:$B$104,"C"))</f>
         <v>120</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>-20</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <f aca="false">IF($A5="","",$D5+$E5-$F5-$G5-$H5+$I5)</f>
+      <c r="K5" s="5" t="n">
+        <f aca="false">IF($A5="","",$E5+$F5-$G5-$H5-$I5+$J5)</f>
         <v>580</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>16</v>
+      <c r="L5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Receive"))</f>
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Sell"))</f>
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A6,Recipes!$B$5:$B$104,"B"))</f>
         <v>22</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A6,Recipes!$B$5:$B$104,"C"))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <f aca="false">IF($A6="","",$D6+$E6-$F6-$G6-$H6+$I6)</f>
+      <c r="K6" s="5" t="n">
+        <f aca="false">IF($A6="","",$E6+$F6-$G6-$H6-$I6+$J6)</f>
         <v>38</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Receive"))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Sell"))</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A7,Recipes!$B$5:$B$104,"B"))</f>
         <v>22</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A7,Recipes!$B$5:$B$104,"C"))</f>
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <f aca="false">IF($A7="","",$D7+$E7-$F7-$G7-$H7+$I7)</f>
+      <c r="K7" s="5" t="n">
+        <f aca="false">IF($A7="","",$E7+$F7-$G7-$H7-$I7+$J7)</f>
         <v>178</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <f aca="false">IF($A8="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A8,Movements!$B$5:$B$304,"Receive"))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <f aca="false">IF($A8="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A8,Movements!$B$5:$B$304,"Sell"))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <f aca="false">IF($A8="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A8,Recipes!$B$5:$B$104,"B"))</f>
         <v>12</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <f aca="false">IF($A8="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A8,Recipes!$B$5:$B$104,"C"))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <f aca="false">IF($A8="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A8,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <f aca="false">IF($A8="","",$D8+$E8-$F8-$G8-$H8+$I8)</f>
+      <c r="K8" s="5" t="n">
+        <f aca="false">IF($A8="","",$E8+$F8-$G8-$H8-$I8+$J8)</f>
         <v>138</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <f aca="false">IF($A9="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A9,Movements!$B$5:$B$304,"Receive"))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <f aca="false">IF($A9="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A9,Movements!$B$5:$B$304,"Sell"))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <f aca="false">IF($A9="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A9,Recipes!$B$5:$B$104,"B"))</f>
         <v>17</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <f aca="false">IF($A9="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A9,Recipes!$B$5:$B$104,"C"))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <f aca="false">IF($A9="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A9,Movements!$B$5:$B$304,"Adjust"))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <f aca="false">IF($A9="","",$D9+$E9-$F9-$G9-$H9+$I9)</f>
+      <c r="K9" s="5" t="n">
+        <f aca="false">IF($A9="","",$E9+$F9-$G9-$H9-$I9+$J9)</f>
         <v>63</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="5" t="str">
+      <c r="E10" s="4"/>
+      <c r="F10" s="5" t="str">
         <f aca="false">IF($A10="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A10,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F10" s="5" t="str">
+      <c r="G10" s="5" t="str">
         <f aca="false">IF($A10="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A10,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G10" s="5" t="str">
+      <c r="H10" s="5" t="str">
         <f aca="false">IF($A10="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A10,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H10" s="5" t="str">
+      <c r="I10" s="5" t="str">
         <f aca="false">IF($A10="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A10,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I10" s="5" t="str">
+      <c r="J10" s="5" t="str">
         <f aca="false">IF($A10="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A10,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J10" s="5" t="str">
-        <f aca="false">IF($A10="","",$D10+$E10-$F10-$G10-$H10+$I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="5" t="str">
+        <f aca="false">IF($A10="","",$E10+$F10-$G10-$H10-$I10+$J10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="5" t="str">
+      <c r="E11" s="4"/>
+      <c r="F11" s="5" t="str">
         <f aca="false">IF($A11="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A11,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F11" s="5" t="str">
+      <c r="G11" s="5" t="str">
         <f aca="false">IF($A11="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A11,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G11" s="5" t="str">
+      <c r="H11" s="5" t="str">
         <f aca="false">IF($A11="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A11,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H11" s="5" t="str">
+      <c r="I11" s="5" t="str">
         <f aca="false">IF($A11="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A11,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I11" s="5" t="str">
+      <c r="J11" s="5" t="str">
         <f aca="false">IF($A11="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A11,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J11" s="5" t="str">
-        <f aca="false">IF($A11="","",$D11+$E11-$F11-$G11-$H11+$I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="5" t="str">
+        <f aca="false">IF($A11="","",$E11+$F11-$G11-$H11-$I11+$J11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5" t="str">
+      <c r="E12" s="4"/>
+      <c r="F12" s="5" t="str">
         <f aca="false">IF($A12="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A12,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F12" s="5" t="str">
+      <c r="G12" s="5" t="str">
         <f aca="false">IF($A12="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A12,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G12" s="5" t="str">
+      <c r="H12" s="5" t="str">
         <f aca="false">IF($A12="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A12,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H12" s="5" t="str">
+      <c r="I12" s="5" t="str">
         <f aca="false">IF($A12="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A12,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I12" s="5" t="str">
+      <c r="J12" s="5" t="str">
         <f aca="false">IF($A12="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A12,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J12" s="5" t="str">
-        <f aca="false">IF($A12="","",$D12+$E12-$F12-$G12-$H12+$I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="5" t="str">
+        <f aca="false">IF($A12="","",$E12+$F12-$G12-$H12-$I12+$J12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="5" t="str">
+      <c r="E13" s="4"/>
+      <c r="F13" s="5" t="str">
         <f aca="false">IF($A13="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A13,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F13" s="5" t="str">
+      <c r="G13" s="5" t="str">
         <f aca="false">IF($A13="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A13,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G13" s="5" t="str">
+      <c r="H13" s="5" t="str">
         <f aca="false">IF($A13="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A13,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H13" s="5" t="str">
+      <c r="I13" s="5" t="str">
         <f aca="false">IF($A13="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A13,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I13" s="5" t="str">
+      <c r="J13" s="5" t="str">
         <f aca="false">IF($A13="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A13,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J13" s="5" t="str">
-        <f aca="false">IF($A13="","",$D13+$E13-$F13-$G13-$H13+$I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="5" t="str">
+        <f aca="false">IF($A13="","",$E13+$F13-$G13-$H13-$I13+$J13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="5" t="str">
+      <c r="E14" s="4"/>
+      <c r="F14" s="5" t="str">
         <f aca="false">IF($A14="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A14,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F14" s="5" t="str">
+      <c r="G14" s="5" t="str">
         <f aca="false">IF($A14="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A14,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G14" s="5" t="str">
+      <c r="H14" s="5" t="str">
         <f aca="false">IF($A14="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A14,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H14" s="5" t="str">
+      <c r="I14" s="5" t="str">
         <f aca="false">IF($A14="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A14,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I14" s="5" t="str">
+      <c r="J14" s="5" t="str">
         <f aca="false">IF($A14="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A14,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J14" s="5" t="str">
-        <f aca="false">IF($A14="","",$D14+$E14-$F14-$G14-$H14+$I14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="5" t="str">
+        <f aca="false">IF($A14="","",$E14+$F14-$G14-$H14-$I14+$J14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="5" t="str">
+      <c r="E15" s="4"/>
+      <c r="F15" s="5" t="str">
         <f aca="false">IF($A15="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A15,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F15" s="5" t="str">
+      <c r="G15" s="5" t="str">
         <f aca="false">IF($A15="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A15,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G15" s="5" t="str">
+      <c r="H15" s="5" t="str">
         <f aca="false">IF($A15="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A15,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H15" s="5" t="str">
+      <c r="I15" s="5" t="str">
         <f aca="false">IF($A15="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A15,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I15" s="5" t="str">
+      <c r="J15" s="5" t="str">
         <f aca="false">IF($A15="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A15,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J15" s="5" t="str">
-        <f aca="false">IF($A15="","",$D15+$E15-$F15-$G15-$H15+$I15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="4"/>
+      <c r="K15" s="5" t="str">
+        <f aca="false">IF($A15="","",$E15+$F15-$G15-$H15-$I15+$J15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="5" t="str">
+      <c r="E16" s="4"/>
+      <c r="F16" s="5" t="str">
         <f aca="false">IF($A16="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A16,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F16" s="5" t="str">
+      <c r="G16" s="5" t="str">
         <f aca="false">IF($A16="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A16,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G16" s="5" t="str">
+      <c r="H16" s="5" t="str">
         <f aca="false">IF($A16="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A16,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H16" s="5" t="str">
+      <c r="I16" s="5" t="str">
         <f aca="false">IF($A16="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A16,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I16" s="5" t="str">
+      <c r="J16" s="5" t="str">
         <f aca="false">IF($A16="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A16,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J16" s="5" t="str">
-        <f aca="false">IF($A16="","",$D16+$E16-$F16-$G16-$H16+$I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="4"/>
+      <c r="K16" s="5" t="str">
+        <f aca="false">IF($A16="","",$E16+$F16-$G16-$H16-$I16+$J16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="5" t="str">
+      <c r="E17" s="4"/>
+      <c r="F17" s="5" t="str">
         <f aca="false">IF($A17="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A17,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F17" s="5" t="str">
+      <c r="G17" s="5" t="str">
         <f aca="false">IF($A17="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A17,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G17" s="5" t="str">
+      <c r="H17" s="5" t="str">
         <f aca="false">IF($A17="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A17,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H17" s="5" t="str">
+      <c r="I17" s="5" t="str">
         <f aca="false">IF($A17="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A17,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I17" s="5" t="str">
+      <c r="J17" s="5" t="str">
         <f aca="false">IF($A17="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A17,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J17" s="5" t="str">
-        <f aca="false">IF($A17="","",$D17+$E17-$F17-$G17-$H17+$I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="4"/>
+      <c r="K17" s="5" t="str">
+        <f aca="false">IF($A17="","",$E17+$F17-$G17-$H17-$I17+$J17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="5" t="str">
+      <c r="E18" s="4"/>
+      <c r="F18" s="5" t="str">
         <f aca="false">IF($A18="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A18,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F18" s="5" t="str">
+      <c r="G18" s="5" t="str">
         <f aca="false">IF($A18="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A18,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G18" s="5" t="str">
+      <c r="H18" s="5" t="str">
         <f aca="false">IF($A18="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A18,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H18" s="5" t="str">
+      <c r="I18" s="5" t="str">
         <f aca="false">IF($A18="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A18,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I18" s="5" t="str">
+      <c r="J18" s="5" t="str">
         <f aca="false">IF($A18="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A18,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J18" s="5" t="str">
-        <f aca="false">IF($A18="","",$D18+$E18-$F18-$G18-$H18+$I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="4"/>
+      <c r="K18" s="5" t="str">
+        <f aca="false">IF($A18="","",$E18+$F18-$G18-$H18-$I18+$J18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="5" t="str">
+      <c r="E19" s="4"/>
+      <c r="F19" s="5" t="str">
         <f aca="false">IF($A19="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A19,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F19" s="5" t="str">
+      <c r="G19" s="5" t="str">
         <f aca="false">IF($A19="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A19,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G19" s="5" t="str">
+      <c r="H19" s="5" t="str">
         <f aca="false">IF($A19="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A19,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H19" s="5" t="str">
+      <c r="I19" s="5" t="str">
         <f aca="false">IF($A19="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A19,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I19" s="5" t="str">
+      <c r="J19" s="5" t="str">
         <f aca="false">IF($A19="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A19,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J19" s="5" t="str">
-        <f aca="false">IF($A19="","",$D19+$E19-$F19-$G19-$H19+$I19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="4"/>
+      <c r="K19" s="5" t="str">
+        <f aca="false">IF($A19="","",$E19+$F19-$G19-$H19-$I19+$J19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="5" t="str">
+      <c r="E20" s="4"/>
+      <c r="F20" s="5" t="str">
         <f aca="false">IF($A20="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A20,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F20" s="5" t="str">
+      <c r="G20" s="5" t="str">
         <f aca="false">IF($A20="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A20,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G20" s="5" t="str">
+      <c r="H20" s="5" t="str">
         <f aca="false">IF($A20="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A20,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H20" s="5" t="str">
+      <c r="I20" s="5" t="str">
         <f aca="false">IF($A20="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A20,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I20" s="5" t="str">
+      <c r="J20" s="5" t="str">
         <f aca="false">IF($A20="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A20,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J20" s="5" t="str">
-        <f aca="false">IF($A20="","",$D20+$E20-$F20-$G20-$H20+$I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="4"/>
+      <c r="K20" s="5" t="str">
+        <f aca="false">IF($A20="","",$E20+$F20-$G20-$H20-$I20+$J20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="5" t="str">
+      <c r="E21" s="4"/>
+      <c r="F21" s="5" t="str">
         <f aca="false">IF($A21="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A21,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F21" s="5" t="str">
+      <c r="G21" s="5" t="str">
         <f aca="false">IF($A21="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A21,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G21" s="5" t="str">
+      <c r="H21" s="5" t="str">
         <f aca="false">IF($A21="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A21,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H21" s="5" t="str">
+      <c r="I21" s="5" t="str">
         <f aca="false">IF($A21="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A21,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I21" s="5" t="str">
+      <c r="J21" s="5" t="str">
         <f aca="false">IF($A21="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A21,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J21" s="5" t="str">
-        <f aca="false">IF($A21="","",$D21+$E21-$F21-$G21-$H21+$I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="4"/>
+      <c r="K21" s="5" t="str">
+        <f aca="false">IF($A21="","",$E21+$F21-$G21-$H21-$I21+$J21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="5" t="str">
+      <c r="E22" s="4"/>
+      <c r="F22" s="5" t="str">
         <f aca="false">IF($A22="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A22,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F22" s="5" t="str">
+      <c r="G22" s="5" t="str">
         <f aca="false">IF($A22="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A22,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G22" s="5" t="str">
+      <c r="H22" s="5" t="str">
         <f aca="false">IF($A22="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A22,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H22" s="5" t="str">
+      <c r="I22" s="5" t="str">
         <f aca="false">IF($A22="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A22,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I22" s="5" t="str">
+      <c r="J22" s="5" t="str">
         <f aca="false">IF($A22="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A22,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J22" s="5" t="str">
-        <f aca="false">IF($A22="","",$D22+$E22-$F22-$G22-$H22+$I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="4"/>
+      <c r="K22" s="5" t="str">
+        <f aca="false">IF($A22="","",$E22+$F22-$G22-$H22-$I22+$J22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="5" t="str">
+      <c r="E23" s="4"/>
+      <c r="F23" s="5" t="str">
         <f aca="false">IF($A23="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A23,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F23" s="5" t="str">
+      <c r="G23" s="5" t="str">
         <f aca="false">IF($A23="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A23,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G23" s="5" t="str">
+      <c r="H23" s="5" t="str">
         <f aca="false">IF($A23="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A23,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H23" s="5" t="str">
+      <c r="I23" s="5" t="str">
         <f aca="false">IF($A23="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A23,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I23" s="5" t="str">
+      <c r="J23" s="5" t="str">
         <f aca="false">IF($A23="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A23,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J23" s="5" t="str">
-        <f aca="false">IF($A23="","",$D23+$E23-$F23-$G23-$H23+$I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="4"/>
+      <c r="K23" s="5" t="str">
+        <f aca="false">IF($A23="","",$E23+$F23-$G23-$H23-$I23+$J23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="5" t="str">
+      <c r="E24" s="4"/>
+      <c r="F24" s="5" t="str">
         <f aca="false">IF($A24="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A24,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F24" s="5" t="str">
+      <c r="G24" s="5" t="str">
         <f aca="false">IF($A24="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A24,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G24" s="5" t="str">
+      <c r="H24" s="5" t="str">
         <f aca="false">IF($A24="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A24,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H24" s="5" t="str">
+      <c r="I24" s="5" t="str">
         <f aca="false">IF($A24="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A24,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I24" s="5" t="str">
+      <c r="J24" s="5" t="str">
         <f aca="false">IF($A24="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A24,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J24" s="5" t="str">
-        <f aca="false">IF($A24="","",$D24+$E24-$F24-$G24-$H24+$I24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="4"/>
+      <c r="K24" s="5" t="str">
+        <f aca="false">IF($A24="","",$E24+$F24-$G24-$H24-$I24+$J24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="5" t="str">
+      <c r="E25" s="4"/>
+      <c r="F25" s="5" t="str">
         <f aca="false">IF($A25="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A25,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F25" s="5" t="str">
+      <c r="G25" s="5" t="str">
         <f aca="false">IF($A25="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A25,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G25" s="5" t="str">
+      <c r="H25" s="5" t="str">
         <f aca="false">IF($A25="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A25,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H25" s="5" t="str">
+      <c r="I25" s="5" t="str">
         <f aca="false">IF($A25="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A25,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I25" s="5" t="str">
+      <c r="J25" s="5" t="str">
         <f aca="false">IF($A25="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A25,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J25" s="5" t="str">
-        <f aca="false">IF($A25="","",$D25+$E25-$F25-$G25-$H25+$I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="4"/>
+      <c r="K25" s="5" t="str">
+        <f aca="false">IF($A25="","",$E25+$F25-$G25-$H25-$I25+$J25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="5" t="str">
+      <c r="E26" s="4"/>
+      <c r="F26" s="5" t="str">
         <f aca="false">IF($A26="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A26,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F26" s="5" t="str">
+      <c r="G26" s="5" t="str">
         <f aca="false">IF($A26="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A26,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G26" s="5" t="str">
+      <c r="H26" s="5" t="str">
         <f aca="false">IF($A26="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A26,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H26" s="5" t="str">
+      <c r="I26" s="5" t="str">
         <f aca="false">IF($A26="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A26,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I26" s="5" t="str">
+      <c r="J26" s="5" t="str">
         <f aca="false">IF($A26="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A26,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J26" s="5" t="str">
-        <f aca="false">IF($A26="","",$D26+$E26-$F26-$G26-$H26+$I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="4"/>
+      <c r="K26" s="5" t="str">
+        <f aca="false">IF($A26="","",$E26+$F26-$G26-$H26-$I26+$J26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="5" t="str">
+      <c r="E27" s="4"/>
+      <c r="F27" s="5" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A27,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F27" s="5" t="str">
+      <c r="G27" s="5" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A27,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G27" s="5" t="str">
+      <c r="H27" s="5" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A27,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H27" s="5" t="str">
+      <c r="I27" s="5" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A27,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I27" s="5" t="str">
+      <c r="J27" s="5" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A27,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J27" s="5" t="str">
-        <f aca="false">IF($A27="","",$D27+$E27-$F27-$G27-$H27+$I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="4"/>
+      <c r="K27" s="5" t="str">
+        <f aca="false">IF($A27="","",$E27+$F27-$G27-$H27-$I27+$J27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="5" t="str">
+      <c r="E28" s="4"/>
+      <c r="F28" s="5" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A28,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F28" s="5" t="str">
+      <c r="G28" s="5" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A28,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G28" s="5" t="str">
+      <c r="H28" s="5" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A28,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H28" s="5" t="str">
+      <c r="I28" s="5" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A28,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I28" s="5" t="str">
+      <c r="J28" s="5" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A28,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J28" s="5" t="str">
-        <f aca="false">IF($A28="","",$D28+$E28-$F28-$G28-$H28+$I28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="4"/>
+      <c r="K28" s="5" t="str">
+        <f aca="false">IF($A28="","",$E28+$F28-$G28-$H28-$I28+$J28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="5" t="str">
+      <c r="E29" s="4"/>
+      <c r="F29" s="5" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A29,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F29" s="5" t="str">
+      <c r="G29" s="5" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A29,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G29" s="5" t="str">
+      <c r="H29" s="5" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A29,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H29" s="5" t="str">
+      <c r="I29" s="5" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A29,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I29" s="5" t="str">
+      <c r="J29" s="5" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A29,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J29" s="5" t="str">
-        <f aca="false">IF($A29="","",$D29+$E29-$F29-$G29-$H29+$I29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="4"/>
+      <c r="K29" s="5" t="str">
+        <f aca="false">IF($A29="","",$E29+$F29-$G29-$H29-$I29+$J29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="5" t="str">
+      <c r="E30" s="4"/>
+      <c r="F30" s="5" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A30,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F30" s="5" t="str">
+      <c r="G30" s="5" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A30,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G30" s="5" t="str">
+      <c r="H30" s="5" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A30,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H30" s="5" t="str">
+      <c r="I30" s="5" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A30,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I30" s="5" t="str">
+      <c r="J30" s="5" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A30,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J30" s="5" t="str">
-        <f aca="false">IF($A30="","",$D30+$E30-$F30-$G30-$H30+$I30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="4"/>
+      <c r="K30" s="5" t="str">
+        <f aca="false">IF($A30="","",$E30+$F30-$G30-$H30-$I30+$J30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="5" t="str">
+      <c r="E31" s="4"/>
+      <c r="F31" s="5" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A31,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F31" s="5" t="str">
+      <c r="G31" s="5" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A31,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G31" s="5" t="str">
+      <c r="H31" s="5" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A31,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H31" s="5" t="str">
+      <c r="I31" s="5" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A31,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I31" s="5" t="str">
+      <c r="J31" s="5" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A31,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J31" s="5" t="str">
-        <f aca="false">IF($A31="","",$D31+$E31-$F31-$G31-$H31+$I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="4"/>
+      <c r="K31" s="5" t="str">
+        <f aca="false">IF($A31="","",$E31+$F31-$G31-$H31-$I31+$J31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="5" t="str">
+      <c r="E32" s="4"/>
+      <c r="F32" s="5" t="str">
         <f aca="false">IF($A32="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A32,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F32" s="5" t="str">
+      <c r="G32" s="5" t="str">
         <f aca="false">IF($A32="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A32,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G32" s="5" t="str">
+      <c r="H32" s="5" t="str">
         <f aca="false">IF($A32="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A32,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H32" s="5" t="str">
+      <c r="I32" s="5" t="str">
         <f aca="false">IF($A32="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A32,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I32" s="5" t="str">
+      <c r="J32" s="5" t="str">
         <f aca="false">IF($A32="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A32,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J32" s="5" t="str">
-        <f aca="false">IF($A32="","",$D32+$E32-$F32-$G32-$H32+$I32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="4"/>
+      <c r="K32" s="5" t="str">
+        <f aca="false">IF($A32="","",$E32+$F32-$G32-$H32-$I32+$J32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="5" t="str">
+      <c r="E33" s="4"/>
+      <c r="F33" s="5" t="str">
         <f aca="false">IF($A33="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A33,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F33" s="5" t="str">
+      <c r="G33" s="5" t="str">
         <f aca="false">IF($A33="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A33,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G33" s="5" t="str">
+      <c r="H33" s="5" t="str">
         <f aca="false">IF($A33="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A33,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H33" s="5" t="str">
+      <c r="I33" s="5" t="str">
         <f aca="false">IF($A33="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A33,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I33" s="5" t="str">
+      <c r="J33" s="5" t="str">
         <f aca="false">IF($A33="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A33,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J33" s="5" t="str">
-        <f aca="false">IF($A33="","",$D33+$E33-$F33-$G33-$H33+$I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="4"/>
+      <c r="K33" s="5" t="str">
+        <f aca="false">IF($A33="","",$E33+$F33-$G33-$H33-$I33+$J33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="5" t="str">
+      <c r="E34" s="4"/>
+      <c r="F34" s="5" t="str">
         <f aca="false">IF($A34="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A34,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F34" s="5" t="str">
+      <c r="G34" s="5" t="str">
         <f aca="false">IF($A34="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A34,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G34" s="5" t="str">
+      <c r="H34" s="5" t="str">
         <f aca="false">IF($A34="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A34,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H34" s="5" t="str">
+      <c r="I34" s="5" t="str">
         <f aca="false">IF($A34="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A34,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I34" s="5" t="str">
+      <c r="J34" s="5" t="str">
         <f aca="false">IF($A34="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A34,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J34" s="5" t="str">
-        <f aca="false">IF($A34="","",$D34+$E34-$F34-$G34-$H34+$I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="4"/>
+      <c r="K34" s="5" t="str">
+        <f aca="false">IF($A34="","",$E34+$F34-$G34-$H34-$I34+$J34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="5" t="str">
+      <c r="E35" s="4"/>
+      <c r="F35" s="5" t="str">
         <f aca="false">IF($A35="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A35,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F35" s="5" t="str">
+      <c r="G35" s="5" t="str">
         <f aca="false">IF($A35="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A35,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G35" s="5" t="str">
+      <c r="H35" s="5" t="str">
         <f aca="false">IF($A35="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A35,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H35" s="5" t="str">
+      <c r="I35" s="5" t="str">
         <f aca="false">IF($A35="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A35,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I35" s="5" t="str">
+      <c r="J35" s="5" t="str">
         <f aca="false">IF($A35="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A35,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J35" s="5" t="str">
-        <f aca="false">IF($A35="","",$D35+$E35-$F35-$G35-$H35+$I35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="4"/>
+      <c r="K35" s="5" t="str">
+        <f aca="false">IF($A35="","",$E35+$F35-$G35-$H35-$I35+$J35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="5" t="str">
+      <c r="E36" s="4"/>
+      <c r="F36" s="5" t="str">
         <f aca="false">IF($A36="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A36,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F36" s="5" t="str">
+      <c r="G36" s="5" t="str">
         <f aca="false">IF($A36="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A36,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G36" s="5" t="str">
+      <c r="H36" s="5" t="str">
         <f aca="false">IF($A36="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A36,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H36" s="5" t="str">
+      <c r="I36" s="5" t="str">
         <f aca="false">IF($A36="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A36,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I36" s="5" t="str">
+      <c r="J36" s="5" t="str">
         <f aca="false">IF($A36="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A36,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J36" s="5" t="str">
-        <f aca="false">IF($A36="","",$D36+$E36-$F36-$G36-$H36+$I36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="4"/>
+      <c r="K36" s="5" t="str">
+        <f aca="false">IF($A36="","",$E36+$F36-$G36-$H36-$I36+$J36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="5" t="str">
+      <c r="E37" s="4"/>
+      <c r="F37" s="5" t="str">
         <f aca="false">IF($A37="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A37,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F37" s="5" t="str">
+      <c r="G37" s="5" t="str">
         <f aca="false">IF($A37="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A37,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G37" s="5" t="str">
+      <c r="H37" s="5" t="str">
         <f aca="false">IF($A37="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A37,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H37" s="5" t="str">
+      <c r="I37" s="5" t="str">
         <f aca="false">IF($A37="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A37,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I37" s="5" t="str">
+      <c r="J37" s="5" t="str">
         <f aca="false">IF($A37="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A37,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J37" s="5" t="str">
-        <f aca="false">IF($A37="","",$D37+$E37-$F37-$G37-$H37+$I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="4"/>
+      <c r="K37" s="5" t="str">
+        <f aca="false">IF($A37="","",$E37+$F37-$G37-$H37-$I37+$J37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="5" t="str">
+      <c r="E38" s="4"/>
+      <c r="F38" s="5" t="str">
         <f aca="false">IF($A38="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A38,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F38" s="5" t="str">
+      <c r="G38" s="5" t="str">
         <f aca="false">IF($A38="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A38,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G38" s="5" t="str">
+      <c r="H38" s="5" t="str">
         <f aca="false">IF($A38="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A38,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H38" s="5" t="str">
+      <c r="I38" s="5" t="str">
         <f aca="false">IF($A38="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A38,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I38" s="5" t="str">
+      <c r="J38" s="5" t="str">
         <f aca="false">IF($A38="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A38,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J38" s="5" t="str">
-        <f aca="false">IF($A38="","",$D38+$E38-$F38-$G38-$H38+$I38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="4"/>
+      <c r="K38" s="5" t="str">
+        <f aca="false">IF($A38="","",$E38+$F38-$G38-$H38-$I38+$J38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="5" t="str">
+      <c r="E39" s="4"/>
+      <c r="F39" s="5" t="str">
         <f aca="false">IF($A39="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A39,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F39" s="5" t="str">
+      <c r="G39" s="5" t="str">
         <f aca="false">IF($A39="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A39,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G39" s="5" t="str">
+      <c r="H39" s="5" t="str">
         <f aca="false">IF($A39="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A39,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H39" s="5" t="str">
+      <c r="I39" s="5" t="str">
         <f aca="false">IF($A39="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A39,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I39" s="5" t="str">
+      <c r="J39" s="5" t="str">
         <f aca="false">IF($A39="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A39,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J39" s="5" t="str">
-        <f aca="false">IF($A39="","",$D39+$E39-$F39-$G39-$H39+$I39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="4"/>
+      <c r="K39" s="5" t="str">
+        <f aca="false">IF($A39="","",$E39+$F39-$G39-$H39-$I39+$J39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="5" t="str">
+      <c r="E40" s="4"/>
+      <c r="F40" s="5" t="str">
         <f aca="false">IF($A40="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A40,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F40" s="5" t="str">
+      <c r="G40" s="5" t="str">
         <f aca="false">IF($A40="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A40,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G40" s="5" t="str">
+      <c r="H40" s="5" t="str">
         <f aca="false">IF($A40="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A40,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H40" s="5" t="str">
+      <c r="I40" s="5" t="str">
         <f aca="false">IF($A40="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A40,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I40" s="5" t="str">
+      <c r="J40" s="5" t="str">
         <f aca="false">IF($A40="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A40,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J40" s="5" t="str">
-        <f aca="false">IF($A40="","",$D40+$E40-$F40-$G40-$H40+$I40)</f>
-        <v/>
-      </c>
-      <c r="K40" s="4"/>
+      <c r="K40" s="5" t="str">
+        <f aca="false">IF($A40="","",$E40+$F40-$G40-$H40-$I40+$J40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="5" t="str">
+      <c r="E41" s="4"/>
+      <c r="F41" s="5" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A41,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F41" s="5" t="str">
+      <c r="G41" s="5" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A41,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G41" s="5" t="str">
+      <c r="H41" s="5" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A41,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H41" s="5" t="str">
+      <c r="I41" s="5" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A41,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I41" s="5" t="str">
+      <c r="J41" s="5" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A41,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J41" s="5" t="str">
-        <f aca="false">IF($A41="","",$D41+$E41-$F41-$G41-$H41+$I41)</f>
-        <v/>
-      </c>
-      <c r="K41" s="4"/>
+      <c r="K41" s="5" t="str">
+        <f aca="false">IF($A41="","",$E41+$F41-$G41-$H41-$I41+$J41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="5" t="str">
+      <c r="E42" s="4"/>
+      <c r="F42" s="5" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A42,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F42" s="5" t="str">
+      <c r="G42" s="5" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A42,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G42" s="5" t="str">
+      <c r="H42" s="5" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A42,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H42" s="5" t="str">
+      <c r="I42" s="5" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A42,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I42" s="5" t="str">
+      <c r="J42" s="5" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A42,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J42" s="5" t="str">
-        <f aca="false">IF($A42="","",$D42+$E42-$F42-$G42-$H42+$I42)</f>
-        <v/>
-      </c>
-      <c r="K42" s="4"/>
+      <c r="K42" s="5" t="str">
+        <f aca="false">IF($A42="","",$E42+$F42-$G42-$H42-$I42+$J42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
-      <c r="E43" s="5" t="str">
+      <c r="E43" s="4"/>
+      <c r="F43" s="5" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A43,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F43" s="5" t="str">
+      <c r="G43" s="5" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A43,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G43" s="5" t="str">
+      <c r="H43" s="5" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A43,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H43" s="5" t="str">
+      <c r="I43" s="5" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A43,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I43" s="5" t="str">
+      <c r="J43" s="5" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A43,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J43" s="5" t="str">
-        <f aca="false">IF($A43="","",$D43+$E43-$F43-$G43-$H43+$I43)</f>
-        <v/>
-      </c>
-      <c r="K43" s="4"/>
+      <c r="K43" s="5" t="str">
+        <f aca="false">IF($A43="","",$E43+$F43-$G43-$H43-$I43+$J43)</f>
+        <v/>
+      </c>
+      <c r="L43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
-      <c r="E44" s="5" t="str">
+      <c r="E44" s="4"/>
+      <c r="F44" s="5" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A44,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F44" s="5" t="str">
+      <c r="G44" s="5" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A44,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G44" s="5" t="str">
+      <c r="H44" s="5" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A44,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H44" s="5" t="str">
+      <c r="I44" s="5" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A44,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I44" s="5" t="str">
+      <c r="J44" s="5" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A44,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J44" s="5" t="str">
-        <f aca="false">IF($A44="","",$D44+$E44-$F44-$G44-$H44+$I44)</f>
-        <v/>
-      </c>
-      <c r="K44" s="4"/>
+      <c r="K44" s="5" t="str">
+        <f aca="false">IF($A44="","",$E44+$F44-$G44-$H44-$I44+$J44)</f>
+        <v/>
+      </c>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="5" t="str">
+      <c r="E45" s="4"/>
+      <c r="F45" s="5" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A45,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F45" s="5" t="str">
+      <c r="G45" s="5" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A45,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G45" s="5" t="str">
+      <c r="H45" s="5" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A45,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H45" s="5" t="str">
+      <c r="I45" s="5" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A45,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I45" s="5" t="str">
+      <c r="J45" s="5" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A45,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J45" s="5" t="str">
-        <f aca="false">IF($A45="","",$D45+$E45-$F45-$G45-$H45+$I45)</f>
-        <v/>
-      </c>
-      <c r="K45" s="4"/>
+      <c r="K45" s="5" t="str">
+        <f aca="false">IF($A45="","",$E45+$F45-$G45-$H45-$I45+$J45)</f>
+        <v/>
+      </c>
+      <c r="L45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="5" t="str">
+      <c r="E46" s="4"/>
+      <c r="F46" s="5" t="str">
         <f aca="false">IF($A46="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A46,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F46" s="5" t="str">
+      <c r="G46" s="5" t="str">
         <f aca="false">IF($A46="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A46,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G46" s="5" t="str">
+      <c r="H46" s="5" t="str">
         <f aca="false">IF($A46="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A46,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H46" s="5" t="str">
+      <c r="I46" s="5" t="str">
         <f aca="false">IF($A46="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A46,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I46" s="5" t="str">
+      <c r="J46" s="5" t="str">
         <f aca="false">IF($A46="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A46,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J46" s="5" t="str">
-        <f aca="false">IF($A46="","",$D46+$E46-$F46-$G46-$H46+$I46)</f>
-        <v/>
-      </c>
-      <c r="K46" s="4"/>
+      <c r="K46" s="5" t="str">
+        <f aca="false">IF($A46="","",$E46+$F46-$G46-$H46-$I46+$J46)</f>
+        <v/>
+      </c>
+      <c r="L46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="5" t="str">
+      <c r="E47" s="4"/>
+      <c r="F47" s="5" t="str">
         <f aca="false">IF($A47="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A47,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F47" s="5" t="str">
+      <c r="G47" s="5" t="str">
         <f aca="false">IF($A47="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A47,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G47" s="5" t="str">
+      <c r="H47" s="5" t="str">
         <f aca="false">IF($A47="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A47,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H47" s="5" t="str">
+      <c r="I47" s="5" t="str">
         <f aca="false">IF($A47="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A47,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I47" s="5" t="str">
+      <c r="J47" s="5" t="str">
         <f aca="false">IF($A47="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A47,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J47" s="5" t="str">
-        <f aca="false">IF($A47="","",$D47+$E47-$F47-$G47-$H47+$I47)</f>
-        <v/>
-      </c>
-      <c r="K47" s="4"/>
+      <c r="K47" s="5" t="str">
+        <f aca="false">IF($A47="","",$E47+$F47-$G47-$H47-$I47+$J47)</f>
+        <v/>
+      </c>
+      <c r="L47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="5" t="str">
+      <c r="E48" s="4"/>
+      <c r="F48" s="5" t="str">
         <f aca="false">IF($A48="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A48,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F48" s="5" t="str">
+      <c r="G48" s="5" t="str">
         <f aca="false">IF($A48="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A48,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G48" s="5" t="str">
+      <c r="H48" s="5" t="str">
         <f aca="false">IF($A48="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A48,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H48" s="5" t="str">
+      <c r="I48" s="5" t="str">
         <f aca="false">IF($A48="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A48,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I48" s="5" t="str">
+      <c r="J48" s="5" t="str">
         <f aca="false">IF($A48="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A48,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J48" s="5" t="str">
-        <f aca="false">IF($A48="","",$D48+$E48-$F48-$G48-$H48+$I48)</f>
-        <v/>
-      </c>
-      <c r="K48" s="4"/>
+      <c r="K48" s="5" t="str">
+        <f aca="false">IF($A48="","",$E48+$F48-$G48-$H48-$I48+$J48)</f>
+        <v/>
+      </c>
+      <c r="L48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="5" t="str">
+      <c r="E49" s="4"/>
+      <c r="F49" s="5" t="str">
         <f aca="false">IF($A49="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A49,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F49" s="5" t="str">
+      <c r="G49" s="5" t="str">
         <f aca="false">IF($A49="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A49,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G49" s="5" t="str">
+      <c r="H49" s="5" t="str">
         <f aca="false">IF($A49="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A49,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H49" s="5" t="str">
+      <c r="I49" s="5" t="str">
         <f aca="false">IF($A49="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A49,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I49" s="5" t="str">
+      <c r="J49" s="5" t="str">
         <f aca="false">IF($A49="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A49,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J49" s="5" t="str">
-        <f aca="false">IF($A49="","",$D49+$E49-$F49-$G49-$H49+$I49)</f>
-        <v/>
-      </c>
-      <c r="K49" s="4"/>
+      <c r="K49" s="5" t="str">
+        <f aca="false">IF($A49="","",$E49+$F49-$G49-$H49-$I49+$J49)</f>
+        <v/>
+      </c>
+      <c r="L49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="5" t="str">
+      <c r="E50" s="4"/>
+      <c r="F50" s="5" t="str">
         <f aca="false">IF($A50="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A50,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F50" s="5" t="str">
+      <c r="G50" s="5" t="str">
         <f aca="false">IF($A50="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A50,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G50" s="5" t="str">
+      <c r="H50" s="5" t="str">
         <f aca="false">IF($A50="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A50,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H50" s="5" t="str">
+      <c r="I50" s="5" t="str">
         <f aca="false">IF($A50="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A50,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I50" s="5" t="str">
+      <c r="J50" s="5" t="str">
         <f aca="false">IF($A50="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A50,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J50" s="5" t="str">
-        <f aca="false">IF($A50="","",$D50+$E50-$F50-$G50-$H50+$I50)</f>
-        <v/>
-      </c>
-      <c r="K50" s="4"/>
+      <c r="K50" s="5" t="str">
+        <f aca="false">IF($A50="","",$E50+$F50-$G50-$H50-$I50+$J50)</f>
+        <v/>
+      </c>
+      <c r="L50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="5" t="str">
+      <c r="E51" s="4"/>
+      <c r="F51" s="5" t="str">
         <f aca="false">IF($A51="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A51,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F51" s="5" t="str">
+      <c r="G51" s="5" t="str">
         <f aca="false">IF($A51="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A51,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G51" s="5" t="str">
+      <c r="H51" s="5" t="str">
         <f aca="false">IF($A51="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A51,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H51" s="5" t="str">
+      <c r="I51" s="5" t="str">
         <f aca="false">IF($A51="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A51,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I51" s="5" t="str">
+      <c r="J51" s="5" t="str">
         <f aca="false">IF($A51="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A51,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J51" s="5" t="str">
-        <f aca="false">IF($A51="","",$D51+$E51-$F51-$G51-$H51+$I51)</f>
-        <v/>
-      </c>
-      <c r="K51" s="4"/>
+      <c r="K51" s="5" t="str">
+        <f aca="false">IF($A51="","",$E51+$F51-$G51-$H51-$I51+$J51)</f>
+        <v/>
+      </c>
+      <c r="L51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="5" t="str">
+      <c r="E52" s="4"/>
+      <c r="F52" s="5" t="str">
         <f aca="false">IF($A52="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A52,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F52" s="5" t="str">
+      <c r="G52" s="5" t="str">
         <f aca="false">IF($A52="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A52,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G52" s="5" t="str">
+      <c r="H52" s="5" t="str">
         <f aca="false">IF($A52="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A52,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H52" s="5" t="str">
+      <c r="I52" s="5" t="str">
         <f aca="false">IF($A52="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A52,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I52" s="5" t="str">
+      <c r="J52" s="5" t="str">
         <f aca="false">IF($A52="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A52,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J52" s="5" t="str">
-        <f aca="false">IF($A52="","",$D52+$E52-$F52-$G52-$H52+$I52)</f>
-        <v/>
-      </c>
-      <c r="K52" s="4"/>
+      <c r="K52" s="5" t="str">
+        <f aca="false">IF($A52="","",$E52+$F52-$G52-$H52-$I52+$J52)</f>
+        <v/>
+      </c>
+      <c r="L52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="5" t="str">
+      <c r="E53" s="4"/>
+      <c r="F53" s="5" t="str">
         <f aca="false">IF($A53="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A53,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F53" s="5" t="str">
+      <c r="G53" s="5" t="str">
         <f aca="false">IF($A53="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A53,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G53" s="5" t="str">
+      <c r="H53" s="5" t="str">
         <f aca="false">IF($A53="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A53,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H53" s="5" t="str">
+      <c r="I53" s="5" t="str">
         <f aca="false">IF($A53="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A53,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I53" s="5" t="str">
+      <c r="J53" s="5" t="str">
         <f aca="false">IF($A53="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A53,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J53" s="5" t="str">
-        <f aca="false">IF($A53="","",$D53+$E53-$F53-$G53-$H53+$I53)</f>
-        <v/>
-      </c>
-      <c r="K53" s="4"/>
+      <c r="K53" s="5" t="str">
+        <f aca="false">IF($A53="","",$E53+$F53-$G53-$H53-$I53+$J53)</f>
+        <v/>
+      </c>
+      <c r="L53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="5" t="str">
+      <c r="E54" s="4"/>
+      <c r="F54" s="5" t="str">
         <f aca="false">IF($A54="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A54,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F54" s="5" t="str">
+      <c r="G54" s="5" t="str">
         <f aca="false">IF($A54="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A54,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G54" s="5" t="str">
+      <c r="H54" s="5" t="str">
         <f aca="false">IF($A54="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A54,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H54" s="5" t="str">
+      <c r="I54" s="5" t="str">
         <f aca="false">IF($A54="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A54,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I54" s="5" t="str">
+      <c r="J54" s="5" t="str">
         <f aca="false">IF($A54="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A54,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J54" s="5" t="str">
-        <f aca="false">IF($A54="","",$D54+$E54-$F54-$G54-$H54+$I54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="4"/>
+      <c r="K54" s="5" t="str">
+        <f aca="false">IF($A54="","",$E54+$F54-$G54-$H54-$I54+$J54)</f>
+        <v/>
+      </c>
+      <c r="L54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="5" t="str">
+      <c r="E55" s="4"/>
+      <c r="F55" s="5" t="str">
         <f aca="false">IF($A55="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A55,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F55" s="5" t="str">
+      <c r="G55" s="5" t="str">
         <f aca="false">IF($A55="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A55,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G55" s="5" t="str">
+      <c r="H55" s="5" t="str">
         <f aca="false">IF($A55="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A55,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H55" s="5" t="str">
+      <c r="I55" s="5" t="str">
         <f aca="false">IF($A55="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A55,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I55" s="5" t="str">
+      <c r="J55" s="5" t="str">
         <f aca="false">IF($A55="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A55,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J55" s="5" t="str">
-        <f aca="false">IF($A55="","",$D55+$E55-$F55-$G55-$H55+$I55)</f>
-        <v/>
-      </c>
-      <c r="K55" s="4"/>
+      <c r="K55" s="5" t="str">
+        <f aca="false">IF($A55="","",$E55+$F55-$G55-$H55-$I55+$J55)</f>
+        <v/>
+      </c>
+      <c r="L55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="5" t="str">
+      <c r="E56" s="4"/>
+      <c r="F56" s="5" t="str">
         <f aca="false">IF($A56="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A56,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F56" s="5" t="str">
+      <c r="G56" s="5" t="str">
         <f aca="false">IF($A56="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A56,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G56" s="5" t="str">
+      <c r="H56" s="5" t="str">
         <f aca="false">IF($A56="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A56,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H56" s="5" t="str">
+      <c r="I56" s="5" t="str">
         <f aca="false">IF($A56="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A56,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I56" s="5" t="str">
+      <c r="J56" s="5" t="str">
         <f aca="false">IF($A56="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A56,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J56" s="5" t="str">
-        <f aca="false">IF($A56="","",$D56+$E56-$F56-$G56-$H56+$I56)</f>
-        <v/>
-      </c>
-      <c r="K56" s="4"/>
+      <c r="K56" s="5" t="str">
+        <f aca="false">IF($A56="","",$E56+$F56-$G56-$H56-$I56+$J56)</f>
+        <v/>
+      </c>
+      <c r="L56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="5" t="str">
+      <c r="E57" s="4"/>
+      <c r="F57" s="5" t="str">
         <f aca="false">IF($A57="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A57,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F57" s="5" t="str">
+      <c r="G57" s="5" t="str">
         <f aca="false">IF($A57="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A57,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G57" s="5" t="str">
+      <c r="H57" s="5" t="str">
         <f aca="false">IF($A57="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A57,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H57" s="5" t="str">
+      <c r="I57" s="5" t="str">
         <f aca="false">IF($A57="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A57,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I57" s="5" t="str">
+      <c r="J57" s="5" t="str">
         <f aca="false">IF($A57="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A57,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J57" s="5" t="str">
-        <f aca="false">IF($A57="","",$D57+$E57-$F57-$G57-$H57+$I57)</f>
-        <v/>
-      </c>
-      <c r="K57" s="4"/>
+      <c r="K57" s="5" t="str">
+        <f aca="false">IF($A57="","",$E57+$F57-$G57-$H57-$I57+$J57)</f>
+        <v/>
+      </c>
+      <c r="L57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
-      <c r="E58" s="5" t="str">
+      <c r="E58" s="4"/>
+      <c r="F58" s="5" t="str">
         <f aca="false">IF($A58="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A58,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F58" s="5" t="str">
+      <c r="G58" s="5" t="str">
         <f aca="false">IF($A58="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A58,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G58" s="5" t="str">
+      <c r="H58" s="5" t="str">
         <f aca="false">IF($A58="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A58,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H58" s="5" t="str">
+      <c r="I58" s="5" t="str">
         <f aca="false">IF($A58="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A58,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I58" s="5" t="str">
+      <c r="J58" s="5" t="str">
         <f aca="false">IF($A58="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A58,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J58" s="5" t="str">
-        <f aca="false">IF($A58="","",$D58+$E58-$F58-$G58-$H58+$I58)</f>
-        <v/>
-      </c>
-      <c r="K58" s="4"/>
+      <c r="K58" s="5" t="str">
+        <f aca="false">IF($A58="","",$E58+$F58-$G58-$H58-$I58+$J58)</f>
+        <v/>
+      </c>
+      <c r="L58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="5" t="str">
+      <c r="E59" s="4"/>
+      <c r="F59" s="5" t="str">
         <f aca="false">IF($A59="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A59,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F59" s="5" t="str">
+      <c r="G59" s="5" t="str">
         <f aca="false">IF($A59="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A59,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G59" s="5" t="str">
+      <c r="H59" s="5" t="str">
         <f aca="false">IF($A59="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A59,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H59" s="5" t="str">
+      <c r="I59" s="5" t="str">
         <f aca="false">IF($A59="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A59,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I59" s="5" t="str">
+      <c r="J59" s="5" t="str">
         <f aca="false">IF($A59="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A59,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J59" s="5" t="str">
-        <f aca="false">IF($A59="","",$D59+$E59-$F59-$G59-$H59+$I59)</f>
-        <v/>
-      </c>
-      <c r="K59" s="4"/>
+      <c r="K59" s="5" t="str">
+        <f aca="false">IF($A59="","",$E59+$F59-$G59-$H59-$I59+$J59)</f>
+        <v/>
+      </c>
+      <c r="L59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="5" t="str">
+      <c r="E60" s="4"/>
+      <c r="F60" s="5" t="str">
         <f aca="false">IF($A60="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A60,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F60" s="5" t="str">
+      <c r="G60" s="5" t="str">
         <f aca="false">IF($A60="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A60,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G60" s="5" t="str">
+      <c r="H60" s="5" t="str">
         <f aca="false">IF($A60="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A60,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H60" s="5" t="str">
+      <c r="I60" s="5" t="str">
         <f aca="false">IF($A60="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A60,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I60" s="5" t="str">
+      <c r="J60" s="5" t="str">
         <f aca="false">IF($A60="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A60,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J60" s="5" t="str">
-        <f aca="false">IF($A60="","",$D60+$E60-$F60-$G60-$H60+$I60)</f>
-        <v/>
-      </c>
-      <c r="K60" s="4"/>
+      <c r="K60" s="5" t="str">
+        <f aca="false">IF($A60="","",$E60+$F60-$G60-$H60-$I60+$J60)</f>
+        <v/>
+      </c>
+      <c r="L60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="5" t="str">
+      <c r="E61" s="4"/>
+      <c r="F61" s="5" t="str">
         <f aca="false">IF($A61="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A61,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F61" s="5" t="str">
+      <c r="G61" s="5" t="str">
         <f aca="false">IF($A61="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A61,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G61" s="5" t="str">
+      <c r="H61" s="5" t="str">
         <f aca="false">IF($A61="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A61,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H61" s="5" t="str">
+      <c r="I61" s="5" t="str">
         <f aca="false">IF($A61="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A61,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I61" s="5" t="str">
+      <c r="J61" s="5" t="str">
         <f aca="false">IF($A61="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A61,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J61" s="5" t="str">
-        <f aca="false">IF($A61="","",$D61+$E61-$F61-$G61-$H61+$I61)</f>
-        <v/>
-      </c>
-      <c r="K61" s="4"/>
+      <c r="K61" s="5" t="str">
+        <f aca="false">IF($A61="","",$E61+$F61-$G61-$H61-$I61+$J61)</f>
+        <v/>
+      </c>
+      <c r="L61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="5" t="str">
+      <c r="E62" s="4"/>
+      <c r="F62" s="5" t="str">
         <f aca="false">IF($A62="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A62,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F62" s="5" t="str">
+      <c r="G62" s="5" t="str">
         <f aca="false">IF($A62="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A62,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G62" s="5" t="str">
+      <c r="H62" s="5" t="str">
         <f aca="false">IF($A62="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A62,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H62" s="5" t="str">
+      <c r="I62" s="5" t="str">
         <f aca="false">IF($A62="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A62,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I62" s="5" t="str">
+      <c r="J62" s="5" t="str">
         <f aca="false">IF($A62="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A62,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J62" s="5" t="str">
-        <f aca="false">IF($A62="","",$D62+$E62-$F62-$G62-$H62+$I62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="4"/>
+      <c r="K62" s="5" t="str">
+        <f aca="false">IF($A62="","",$E62+$F62-$G62-$H62-$I62+$J62)</f>
+        <v/>
+      </c>
+      <c r="L62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="5" t="str">
+      <c r="E63" s="4"/>
+      <c r="F63" s="5" t="str">
         <f aca="false">IF($A63="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A63,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F63" s="5" t="str">
+      <c r="G63" s="5" t="str">
         <f aca="false">IF($A63="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A63,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G63" s="5" t="str">
+      <c r="H63" s="5" t="str">
         <f aca="false">IF($A63="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A63,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H63" s="5" t="str">
+      <c r="I63" s="5" t="str">
         <f aca="false">IF($A63="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A63,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I63" s="5" t="str">
+      <c r="J63" s="5" t="str">
         <f aca="false">IF($A63="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A63,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J63" s="5" t="str">
-        <f aca="false">IF($A63="","",$D63+$E63-$F63-$G63-$H63+$I63)</f>
-        <v/>
-      </c>
-      <c r="K63" s="4"/>
+      <c r="K63" s="5" t="str">
+        <f aca="false">IF($A63="","",$E63+$F63-$G63-$H63-$I63+$J63)</f>
+        <v/>
+      </c>
+      <c r="L63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="5" t="str">
+      <c r="E64" s="4"/>
+      <c r="F64" s="5" t="str">
         <f aca="false">IF($A64="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A64,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F64" s="5" t="str">
+      <c r="G64" s="5" t="str">
         <f aca="false">IF($A64="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A64,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G64" s="5" t="str">
+      <c r="H64" s="5" t="str">
         <f aca="false">IF($A64="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A64,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H64" s="5" t="str">
+      <c r="I64" s="5" t="str">
         <f aca="false">IF($A64="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A64,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I64" s="5" t="str">
+      <c r="J64" s="5" t="str">
         <f aca="false">IF($A64="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A64,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J64" s="5" t="str">
-        <f aca="false">IF($A64="","",$D64+$E64-$F64-$G64-$H64+$I64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="4"/>
+      <c r="K64" s="5" t="str">
+        <f aca="false">IF($A64="","",$E64+$F64-$G64-$H64-$I64+$J64)</f>
+        <v/>
+      </c>
+      <c r="L64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="5" t="str">
+      <c r="E65" s="4"/>
+      <c r="F65" s="5" t="str">
         <f aca="false">IF($A65="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A65,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F65" s="5" t="str">
+      <c r="G65" s="5" t="str">
         <f aca="false">IF($A65="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A65,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G65" s="5" t="str">
+      <c r="H65" s="5" t="str">
         <f aca="false">IF($A65="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A65,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H65" s="5" t="str">
+      <c r="I65" s="5" t="str">
         <f aca="false">IF($A65="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A65,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I65" s="5" t="str">
+      <c r="J65" s="5" t="str">
         <f aca="false">IF($A65="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A65,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J65" s="5" t="str">
-        <f aca="false">IF($A65="","",$D65+$E65-$F65-$G65-$H65+$I65)</f>
-        <v/>
-      </c>
-      <c r="K65" s="4"/>
+      <c r="K65" s="5" t="str">
+        <f aca="false">IF($A65="","",$E65+$F65-$G65-$H65-$I65+$J65)</f>
+        <v/>
+      </c>
+      <c r="L65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="5" t="str">
+      <c r="E66" s="4"/>
+      <c r="F66" s="5" t="str">
         <f aca="false">IF($A66="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A66,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F66" s="5" t="str">
+      <c r="G66" s="5" t="str">
         <f aca="false">IF($A66="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A66,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G66" s="5" t="str">
+      <c r="H66" s="5" t="str">
         <f aca="false">IF($A66="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A66,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H66" s="5" t="str">
+      <c r="I66" s="5" t="str">
         <f aca="false">IF($A66="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A66,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I66" s="5" t="str">
+      <c r="J66" s="5" t="str">
         <f aca="false">IF($A66="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A66,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J66" s="5" t="str">
-        <f aca="false">IF($A66="","",$D66+$E66-$F66-$G66-$H66+$I66)</f>
-        <v/>
-      </c>
-      <c r="K66" s="4"/>
+      <c r="K66" s="5" t="str">
+        <f aca="false">IF($A66="","",$E66+$F66-$G66-$H66-$I66+$J66)</f>
+        <v/>
+      </c>
+      <c r="L66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="5" t="str">
+      <c r="E67" s="4"/>
+      <c r="F67" s="5" t="str">
         <f aca="false">IF($A67="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A67,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F67" s="5" t="str">
+      <c r="G67" s="5" t="str">
         <f aca="false">IF($A67="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A67,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G67" s="5" t="str">
+      <c r="H67" s="5" t="str">
         <f aca="false">IF($A67="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A67,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H67" s="5" t="str">
+      <c r="I67" s="5" t="str">
         <f aca="false">IF($A67="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A67,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I67" s="5" t="str">
+      <c r="J67" s="5" t="str">
         <f aca="false">IF($A67="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A67,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J67" s="5" t="str">
-        <f aca="false">IF($A67="","",$D67+$E67-$F67-$G67-$H67+$I67)</f>
-        <v/>
-      </c>
-      <c r="K67" s="4"/>
+      <c r="K67" s="5" t="str">
+        <f aca="false">IF($A67="","",$E67+$F67-$G67-$H67-$I67+$J67)</f>
+        <v/>
+      </c>
+      <c r="L67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="5" t="str">
+      <c r="E68" s="4"/>
+      <c r="F68" s="5" t="str">
         <f aca="false">IF($A68="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A68,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F68" s="5" t="str">
+      <c r="G68" s="5" t="str">
         <f aca="false">IF($A68="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A68,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G68" s="5" t="str">
+      <c r="H68" s="5" t="str">
         <f aca="false">IF($A68="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A68,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H68" s="5" t="str">
+      <c r="I68" s="5" t="str">
         <f aca="false">IF($A68="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A68,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I68" s="5" t="str">
+      <c r="J68" s="5" t="str">
         <f aca="false">IF($A68="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A68,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J68" s="5" t="str">
-        <f aca="false">IF($A68="","",$D68+$E68-$F68-$G68-$H68+$I68)</f>
-        <v/>
-      </c>
-      <c r="K68" s="4"/>
+      <c r="K68" s="5" t="str">
+        <f aca="false">IF($A68="","",$E68+$F68-$G68-$H68-$I68+$J68)</f>
+        <v/>
+      </c>
+      <c r="L68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="5" t="str">
+      <c r="E69" s="4"/>
+      <c r="F69" s="5" t="str">
         <f aca="false">IF($A69="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A69,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F69" s="5" t="str">
+      <c r="G69" s="5" t="str">
         <f aca="false">IF($A69="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A69,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G69" s="5" t="str">
+      <c r="H69" s="5" t="str">
         <f aca="false">IF($A69="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A69,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H69" s="5" t="str">
+      <c r="I69" s="5" t="str">
         <f aca="false">IF($A69="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A69,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I69" s="5" t="str">
+      <c r="J69" s="5" t="str">
         <f aca="false">IF($A69="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A69,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J69" s="5" t="str">
-        <f aca="false">IF($A69="","",$D69+$E69-$F69-$G69-$H69+$I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="4"/>
+      <c r="K69" s="5" t="str">
+        <f aca="false">IF($A69="","",$E69+$F69-$G69-$H69-$I69+$J69)</f>
+        <v/>
+      </c>
+      <c r="L69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="5" t="str">
+      <c r="E70" s="4"/>
+      <c r="F70" s="5" t="str">
         <f aca="false">IF($A70="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A70,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F70" s="5" t="str">
+      <c r="G70" s="5" t="str">
         <f aca="false">IF($A70="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A70,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G70" s="5" t="str">
+      <c r="H70" s="5" t="str">
         <f aca="false">IF($A70="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A70,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H70" s="5" t="str">
+      <c r="I70" s="5" t="str">
         <f aca="false">IF($A70="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A70,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I70" s="5" t="str">
+      <c r="J70" s="5" t="str">
         <f aca="false">IF($A70="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A70,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J70" s="5" t="str">
-        <f aca="false">IF($A70="","",$D70+$E70-$F70-$G70-$H70+$I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="4"/>
+      <c r="K70" s="5" t="str">
+        <f aca="false">IF($A70="","",$E70+$F70-$G70-$H70-$I70+$J70)</f>
+        <v/>
+      </c>
+      <c r="L70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="5" t="str">
+      <c r="E71" s="4"/>
+      <c r="F71" s="5" t="str">
         <f aca="false">IF($A71="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A71,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F71" s="5" t="str">
+      <c r="G71" s="5" t="str">
         <f aca="false">IF($A71="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A71,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G71" s="5" t="str">
+      <c r="H71" s="5" t="str">
         <f aca="false">IF($A71="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A71,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H71" s="5" t="str">
+      <c r="I71" s="5" t="str">
         <f aca="false">IF($A71="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A71,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I71" s="5" t="str">
+      <c r="J71" s="5" t="str">
         <f aca="false">IF($A71="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A71,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J71" s="5" t="str">
-        <f aca="false">IF($A71="","",$D71+$E71-$F71-$G71-$H71+$I71)</f>
-        <v/>
-      </c>
-      <c r="K71" s="4"/>
+      <c r="K71" s="5" t="str">
+        <f aca="false">IF($A71="","",$E71+$F71-$G71-$H71-$I71+$J71)</f>
+        <v/>
+      </c>
+      <c r="L71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="5" t="str">
+      <c r="E72" s="4"/>
+      <c r="F72" s="5" t="str">
         <f aca="false">IF($A72="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A72,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F72" s="5" t="str">
+      <c r="G72" s="5" t="str">
         <f aca="false">IF($A72="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A72,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G72" s="5" t="str">
+      <c r="H72" s="5" t="str">
         <f aca="false">IF($A72="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A72,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H72" s="5" t="str">
+      <c r="I72" s="5" t="str">
         <f aca="false">IF($A72="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A72,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I72" s="5" t="str">
+      <c r="J72" s="5" t="str">
         <f aca="false">IF($A72="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A72,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J72" s="5" t="str">
-        <f aca="false">IF($A72="","",$D72+$E72-$F72-$G72-$H72+$I72)</f>
-        <v/>
-      </c>
-      <c r="K72" s="4"/>
+      <c r="K72" s="5" t="str">
+        <f aca="false">IF($A72="","",$E72+$F72-$G72-$H72-$I72+$J72)</f>
+        <v/>
+      </c>
+      <c r="L72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="5" t="str">
+      <c r="E73" s="4"/>
+      <c r="F73" s="5" t="str">
         <f aca="false">IF($A73="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A73,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F73" s="5" t="str">
+      <c r="G73" s="5" t="str">
         <f aca="false">IF($A73="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A73,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G73" s="5" t="str">
+      <c r="H73" s="5" t="str">
         <f aca="false">IF($A73="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A73,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H73" s="5" t="str">
+      <c r="I73" s="5" t="str">
         <f aca="false">IF($A73="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A73,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I73" s="5" t="str">
+      <c r="J73" s="5" t="str">
         <f aca="false">IF($A73="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A73,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J73" s="5" t="str">
-        <f aca="false">IF($A73="","",$D73+$E73-$F73-$G73-$H73+$I73)</f>
-        <v/>
-      </c>
-      <c r="K73" s="4"/>
+      <c r="K73" s="5" t="str">
+        <f aca="false">IF($A73="","",$E73+$F73-$G73-$H73-$I73+$J73)</f>
+        <v/>
+      </c>
+      <c r="L73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="5" t="str">
+      <c r="E74" s="4"/>
+      <c r="F74" s="5" t="str">
         <f aca="false">IF($A74="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A74,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F74" s="5" t="str">
+      <c r="G74" s="5" t="str">
         <f aca="false">IF($A74="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A74,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G74" s="5" t="str">
+      <c r="H74" s="5" t="str">
         <f aca="false">IF($A74="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A74,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H74" s="5" t="str">
+      <c r="I74" s="5" t="str">
         <f aca="false">IF($A74="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A74,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I74" s="5" t="str">
+      <c r="J74" s="5" t="str">
         <f aca="false">IF($A74="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A74,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J74" s="5" t="str">
-        <f aca="false">IF($A74="","",$D74+$E74-$F74-$G74-$H74+$I74)</f>
-        <v/>
-      </c>
-      <c r="K74" s="4"/>
+      <c r="K74" s="5" t="str">
+        <f aca="false">IF($A74="","",$E74+$F74-$G74-$H74-$I74+$J74)</f>
+        <v/>
+      </c>
+      <c r="L74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="5" t="str">
+      <c r="E75" s="4"/>
+      <c r="F75" s="5" t="str">
         <f aca="false">IF($A75="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A75,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F75" s="5" t="str">
+      <c r="G75" s="5" t="str">
         <f aca="false">IF($A75="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A75,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G75" s="5" t="str">
+      <c r="H75" s="5" t="str">
         <f aca="false">IF($A75="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A75,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H75" s="5" t="str">
+      <c r="I75" s="5" t="str">
         <f aca="false">IF($A75="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A75,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I75" s="5" t="str">
+      <c r="J75" s="5" t="str">
         <f aca="false">IF($A75="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A75,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J75" s="5" t="str">
-        <f aca="false">IF($A75="","",$D75+$E75-$F75-$G75-$H75+$I75)</f>
-        <v/>
-      </c>
-      <c r="K75" s="4"/>
+      <c r="K75" s="5" t="str">
+        <f aca="false">IF($A75="","",$E75+$F75-$G75-$H75-$I75+$J75)</f>
+        <v/>
+      </c>
+      <c r="L75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="5" t="str">
+      <c r="E76" s="4"/>
+      <c r="F76" s="5" t="str">
         <f aca="false">IF($A76="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A76,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F76" s="5" t="str">
+      <c r="G76" s="5" t="str">
         <f aca="false">IF($A76="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A76,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G76" s="5" t="str">
+      <c r="H76" s="5" t="str">
         <f aca="false">IF($A76="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A76,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H76" s="5" t="str">
+      <c r="I76" s="5" t="str">
         <f aca="false">IF($A76="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A76,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I76" s="5" t="str">
+      <c r="J76" s="5" t="str">
         <f aca="false">IF($A76="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A76,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J76" s="5" t="str">
-        <f aca="false">IF($A76="","",$D76+$E76-$F76-$G76-$H76+$I76)</f>
-        <v/>
-      </c>
-      <c r="K76" s="4"/>
+      <c r="K76" s="5" t="str">
+        <f aca="false">IF($A76="","",$E76+$F76-$G76-$H76-$I76+$J76)</f>
+        <v/>
+      </c>
+      <c r="L76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="5" t="str">
+      <c r="E77" s="4"/>
+      <c r="F77" s="5" t="str">
         <f aca="false">IF($A77="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A77,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F77" s="5" t="str">
+      <c r="G77" s="5" t="str">
         <f aca="false">IF($A77="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A77,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G77" s="5" t="str">
+      <c r="H77" s="5" t="str">
         <f aca="false">IF($A77="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A77,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H77" s="5" t="str">
+      <c r="I77" s="5" t="str">
         <f aca="false">IF($A77="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A77,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I77" s="5" t="str">
+      <c r="J77" s="5" t="str">
         <f aca="false">IF($A77="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A77,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J77" s="5" t="str">
-        <f aca="false">IF($A77="","",$D77+$E77-$F77-$G77-$H77+$I77)</f>
-        <v/>
-      </c>
-      <c r="K77" s="4"/>
+      <c r="K77" s="5" t="str">
+        <f aca="false">IF($A77="","",$E77+$F77-$G77-$H77-$I77+$J77)</f>
+        <v/>
+      </c>
+      <c r="L77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="5" t="str">
+      <c r="E78" s="4"/>
+      <c r="F78" s="5" t="str">
         <f aca="false">IF($A78="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A78,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F78" s="5" t="str">
+      <c r="G78" s="5" t="str">
         <f aca="false">IF($A78="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A78,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G78" s="5" t="str">
+      <c r="H78" s="5" t="str">
         <f aca="false">IF($A78="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A78,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H78" s="5" t="str">
+      <c r="I78" s="5" t="str">
         <f aca="false">IF($A78="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A78,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I78" s="5" t="str">
+      <c r="J78" s="5" t="str">
         <f aca="false">IF($A78="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A78,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J78" s="5" t="str">
-        <f aca="false">IF($A78="","",$D78+$E78-$F78-$G78-$H78+$I78)</f>
-        <v/>
-      </c>
-      <c r="K78" s="4"/>
+      <c r="K78" s="5" t="str">
+        <f aca="false">IF($A78="","",$E78+$F78-$G78-$H78-$I78+$J78)</f>
+        <v/>
+      </c>
+      <c r="L78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="5" t="str">
+      <c r="E79" s="4"/>
+      <c r="F79" s="5" t="str">
         <f aca="false">IF($A79="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A79,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F79" s="5" t="str">
+      <c r="G79" s="5" t="str">
         <f aca="false">IF($A79="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A79,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G79" s="5" t="str">
+      <c r="H79" s="5" t="str">
         <f aca="false">IF($A79="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A79,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H79" s="5" t="str">
+      <c r="I79" s="5" t="str">
         <f aca="false">IF($A79="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A79,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I79" s="5" t="str">
+      <c r="J79" s="5" t="str">
         <f aca="false">IF($A79="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A79,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J79" s="5" t="str">
-        <f aca="false">IF($A79="","",$D79+$E79-$F79-$G79-$H79+$I79)</f>
-        <v/>
-      </c>
-      <c r="K79" s="4"/>
+      <c r="K79" s="5" t="str">
+        <f aca="false">IF($A79="","",$E79+$F79-$G79-$H79-$I79+$J79)</f>
+        <v/>
+      </c>
+      <c r="L79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="5" t="str">
+      <c r="E80" s="4"/>
+      <c r="F80" s="5" t="str">
         <f aca="false">IF($A80="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A80,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F80" s="5" t="str">
+      <c r="G80" s="5" t="str">
         <f aca="false">IF($A80="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A80,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G80" s="5" t="str">
+      <c r="H80" s="5" t="str">
         <f aca="false">IF($A80="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A80,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H80" s="5" t="str">
+      <c r="I80" s="5" t="str">
         <f aca="false">IF($A80="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A80,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I80" s="5" t="str">
+      <c r="J80" s="5" t="str">
         <f aca="false">IF($A80="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A80,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J80" s="5" t="str">
-        <f aca="false">IF($A80="","",$D80+$E80-$F80-$G80-$H80+$I80)</f>
-        <v/>
-      </c>
-      <c r="K80" s="4"/>
+      <c r="K80" s="5" t="str">
+        <f aca="false">IF($A80="","",$E80+$F80-$G80-$H80-$I80+$J80)</f>
+        <v/>
+      </c>
+      <c r="L80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="5" t="str">
+      <c r="E81" s="4"/>
+      <c r="F81" s="5" t="str">
         <f aca="false">IF($A81="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A81,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F81" s="5" t="str">
+      <c r="G81" s="5" t="str">
         <f aca="false">IF($A81="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A81,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G81" s="5" t="str">
+      <c r="H81" s="5" t="str">
         <f aca="false">IF($A81="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A81,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H81" s="5" t="str">
+      <c r="I81" s="5" t="str">
         <f aca="false">IF($A81="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A81,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I81" s="5" t="str">
+      <c r="J81" s="5" t="str">
         <f aca="false">IF($A81="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A81,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J81" s="5" t="str">
-        <f aca="false">IF($A81="","",$D81+$E81-$F81-$G81-$H81+$I81)</f>
-        <v/>
-      </c>
-      <c r="K81" s="4"/>
+      <c r="K81" s="5" t="str">
+        <f aca="false">IF($A81="","",$E81+$F81-$G81-$H81-$I81+$J81)</f>
+        <v/>
+      </c>
+      <c r="L81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="5" t="str">
+      <c r="E82" s="4"/>
+      <c r="F82" s="5" t="str">
         <f aca="false">IF($A82="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A82,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F82" s="5" t="str">
+      <c r="G82" s="5" t="str">
         <f aca="false">IF($A82="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A82,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G82" s="5" t="str">
+      <c r="H82" s="5" t="str">
         <f aca="false">IF($A82="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A82,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H82" s="5" t="str">
+      <c r="I82" s="5" t="str">
         <f aca="false">IF($A82="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A82,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I82" s="5" t="str">
+      <c r="J82" s="5" t="str">
         <f aca="false">IF($A82="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A82,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J82" s="5" t="str">
-        <f aca="false">IF($A82="","",$D82+$E82-$F82-$G82-$H82+$I82)</f>
-        <v/>
-      </c>
-      <c r="K82" s="4"/>
+      <c r="K82" s="5" t="str">
+        <f aca="false">IF($A82="","",$E82+$F82-$G82-$H82-$I82+$J82)</f>
+        <v/>
+      </c>
+      <c r="L82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="5" t="str">
+      <c r="E83" s="4"/>
+      <c r="F83" s="5" t="str">
         <f aca="false">IF($A83="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A83,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F83" s="5" t="str">
+      <c r="G83" s="5" t="str">
         <f aca="false">IF($A83="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A83,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G83" s="5" t="str">
+      <c r="H83" s="5" t="str">
         <f aca="false">IF($A83="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A83,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H83" s="5" t="str">
+      <c r="I83" s="5" t="str">
         <f aca="false">IF($A83="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A83,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I83" s="5" t="str">
+      <c r="J83" s="5" t="str">
         <f aca="false">IF($A83="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A83,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J83" s="5" t="str">
-        <f aca="false">IF($A83="","",$D83+$E83-$F83-$G83-$H83+$I83)</f>
-        <v/>
-      </c>
-      <c r="K83" s="4"/>
+      <c r="K83" s="5" t="str">
+        <f aca="false">IF($A83="","",$E83+$F83-$G83-$H83-$I83+$J83)</f>
+        <v/>
+      </c>
+      <c r="L83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="5" t="str">
+      <c r="E84" s="4"/>
+      <c r="F84" s="5" t="str">
         <f aca="false">IF($A84="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A84,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F84" s="5" t="str">
+      <c r="G84" s="5" t="str">
         <f aca="false">IF($A84="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A84,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G84" s="5" t="str">
+      <c r="H84" s="5" t="str">
         <f aca="false">IF($A84="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A84,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H84" s="5" t="str">
+      <c r="I84" s="5" t="str">
         <f aca="false">IF($A84="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A84,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I84" s="5" t="str">
+      <c r="J84" s="5" t="str">
         <f aca="false">IF($A84="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A84,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J84" s="5" t="str">
-        <f aca="false">IF($A84="","",$D84+$E84-$F84-$G84-$H84+$I84)</f>
-        <v/>
-      </c>
-      <c r="K84" s="4"/>
+      <c r="K84" s="5" t="str">
+        <f aca="false">IF($A84="","",$E84+$F84-$G84-$H84-$I84+$J84)</f>
+        <v/>
+      </c>
+      <c r="L84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="5" t="str">
+      <c r="E85" s="4"/>
+      <c r="F85" s="5" t="str">
         <f aca="false">IF($A85="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A85,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F85" s="5" t="str">
+      <c r="G85" s="5" t="str">
         <f aca="false">IF($A85="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A85,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G85" s="5" t="str">
+      <c r="H85" s="5" t="str">
         <f aca="false">IF($A85="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A85,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H85" s="5" t="str">
+      <c r="I85" s="5" t="str">
         <f aca="false">IF($A85="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A85,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I85" s="5" t="str">
+      <c r="J85" s="5" t="str">
         <f aca="false">IF($A85="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A85,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J85" s="5" t="str">
-        <f aca="false">IF($A85="","",$D85+$E85-$F85-$G85-$H85+$I85)</f>
-        <v/>
-      </c>
-      <c r="K85" s="4"/>
+      <c r="K85" s="5" t="str">
+        <f aca="false">IF($A85="","",$E85+$F85-$G85-$H85-$I85+$J85)</f>
+        <v/>
+      </c>
+      <c r="L85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="5" t="str">
+      <c r="E86" s="4"/>
+      <c r="F86" s="5" t="str">
         <f aca="false">IF($A86="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A86,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F86" s="5" t="str">
+      <c r="G86" s="5" t="str">
         <f aca="false">IF($A86="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A86,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G86" s="5" t="str">
+      <c r="H86" s="5" t="str">
         <f aca="false">IF($A86="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A86,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H86" s="5" t="str">
+      <c r="I86" s="5" t="str">
         <f aca="false">IF($A86="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A86,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I86" s="5" t="str">
+      <c r="J86" s="5" t="str">
         <f aca="false">IF($A86="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A86,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J86" s="5" t="str">
-        <f aca="false">IF($A86="","",$D86+$E86-$F86-$G86-$H86+$I86)</f>
-        <v/>
-      </c>
-      <c r="K86" s="4"/>
+      <c r="K86" s="5" t="str">
+        <f aca="false">IF($A86="","",$E86+$F86-$G86-$H86-$I86+$J86)</f>
+        <v/>
+      </c>
+      <c r="L86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
-      <c r="E87" s="5" t="str">
+      <c r="E87" s="4"/>
+      <c r="F87" s="5" t="str">
         <f aca="false">IF($A87="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A87,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F87" s="5" t="str">
+      <c r="G87" s="5" t="str">
         <f aca="false">IF($A87="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A87,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G87" s="5" t="str">
+      <c r="H87" s="5" t="str">
         <f aca="false">IF($A87="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A87,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H87" s="5" t="str">
+      <c r="I87" s="5" t="str">
         <f aca="false">IF($A87="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A87,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I87" s="5" t="str">
+      <c r="J87" s="5" t="str">
         <f aca="false">IF($A87="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A87,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J87" s="5" t="str">
-        <f aca="false">IF($A87="","",$D87+$E87-$F87-$G87-$H87+$I87)</f>
-        <v/>
-      </c>
-      <c r="K87" s="4"/>
+      <c r="K87" s="5" t="str">
+        <f aca="false">IF($A87="","",$E87+$F87-$G87-$H87-$I87+$J87)</f>
+        <v/>
+      </c>
+      <c r="L87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="5" t="str">
+      <c r="E88" s="4"/>
+      <c r="F88" s="5" t="str">
         <f aca="false">IF($A88="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A88,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F88" s="5" t="str">
+      <c r="G88" s="5" t="str">
         <f aca="false">IF($A88="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A88,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G88" s="5" t="str">
+      <c r="H88" s="5" t="str">
         <f aca="false">IF($A88="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A88,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H88" s="5" t="str">
+      <c r="I88" s="5" t="str">
         <f aca="false">IF($A88="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A88,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I88" s="5" t="str">
+      <c r="J88" s="5" t="str">
         <f aca="false">IF($A88="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A88,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J88" s="5" t="str">
-        <f aca="false">IF($A88="","",$D88+$E88-$F88-$G88-$H88+$I88)</f>
-        <v/>
-      </c>
-      <c r="K88" s="4"/>
+      <c r="K88" s="5" t="str">
+        <f aca="false">IF($A88="","",$E88+$F88-$G88-$H88-$I88+$J88)</f>
+        <v/>
+      </c>
+      <c r="L88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
-      <c r="E89" s="5" t="str">
+      <c r="E89" s="4"/>
+      <c r="F89" s="5" t="str">
         <f aca="false">IF($A89="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A89,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F89" s="5" t="str">
+      <c r="G89" s="5" t="str">
         <f aca="false">IF($A89="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A89,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G89" s="5" t="str">
+      <c r="H89" s="5" t="str">
         <f aca="false">IF($A89="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A89,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H89" s="5" t="str">
+      <c r="I89" s="5" t="str">
         <f aca="false">IF($A89="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A89,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I89" s="5" t="str">
+      <c r="J89" s="5" t="str">
         <f aca="false">IF($A89="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A89,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J89" s="5" t="str">
-        <f aca="false">IF($A89="","",$D89+$E89-$F89-$G89-$H89+$I89)</f>
-        <v/>
-      </c>
-      <c r="K89" s="4"/>
+      <c r="K89" s="5" t="str">
+        <f aca="false">IF($A89="","",$E89+$F89-$G89-$H89-$I89+$J89)</f>
+        <v/>
+      </c>
+      <c r="L89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="5" t="str">
+      <c r="E90" s="4"/>
+      <c r="F90" s="5" t="str">
         <f aca="false">IF($A90="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A90,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F90" s="5" t="str">
+      <c r="G90" s="5" t="str">
         <f aca="false">IF($A90="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A90,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G90" s="5" t="str">
+      <c r="H90" s="5" t="str">
         <f aca="false">IF($A90="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A90,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H90" s="5" t="str">
+      <c r="I90" s="5" t="str">
         <f aca="false">IF($A90="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A90,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I90" s="5" t="str">
+      <c r="J90" s="5" t="str">
         <f aca="false">IF($A90="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A90,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J90" s="5" t="str">
-        <f aca="false">IF($A90="","",$D90+$E90-$F90-$G90-$H90+$I90)</f>
-        <v/>
-      </c>
-      <c r="K90" s="4"/>
+      <c r="K90" s="5" t="str">
+        <f aca="false">IF($A90="","",$E90+$F90-$G90-$H90-$I90+$J90)</f>
+        <v/>
+      </c>
+      <c r="L90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
-      <c r="E91" s="5" t="str">
+      <c r="E91" s="4"/>
+      <c r="F91" s="5" t="str">
         <f aca="false">IF($A91="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A91,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F91" s="5" t="str">
+      <c r="G91" s="5" t="str">
         <f aca="false">IF($A91="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A91,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G91" s="5" t="str">
+      <c r="H91" s="5" t="str">
         <f aca="false">IF($A91="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A91,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H91" s="5" t="str">
+      <c r="I91" s="5" t="str">
         <f aca="false">IF($A91="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A91,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I91" s="5" t="str">
+      <c r="J91" s="5" t="str">
         <f aca="false">IF($A91="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A91,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J91" s="5" t="str">
-        <f aca="false">IF($A91="","",$D91+$E91-$F91-$G91-$H91+$I91)</f>
-        <v/>
-      </c>
-      <c r="K91" s="4"/>
+      <c r="K91" s="5" t="str">
+        <f aca="false">IF($A91="","",$E91+$F91-$G91-$H91-$I91+$J91)</f>
+        <v/>
+      </c>
+      <c r="L91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="5" t="str">
+      <c r="E92" s="4"/>
+      <c r="F92" s="5" t="str">
         <f aca="false">IF($A92="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A92,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F92" s="5" t="str">
+      <c r="G92" s="5" t="str">
         <f aca="false">IF($A92="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A92,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G92" s="5" t="str">
+      <c r="H92" s="5" t="str">
         <f aca="false">IF($A92="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A92,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H92" s="5" t="str">
+      <c r="I92" s="5" t="str">
         <f aca="false">IF($A92="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A92,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I92" s="5" t="str">
+      <c r="J92" s="5" t="str">
         <f aca="false">IF($A92="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A92,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J92" s="5" t="str">
-        <f aca="false">IF($A92="","",$D92+$E92-$F92-$G92-$H92+$I92)</f>
-        <v/>
-      </c>
-      <c r="K92" s="4"/>
+      <c r="K92" s="5" t="str">
+        <f aca="false">IF($A92="","",$E92+$F92-$G92-$H92-$I92+$J92)</f>
+        <v/>
+      </c>
+      <c r="L92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
-      <c r="E93" s="5" t="str">
+      <c r="E93" s="4"/>
+      <c r="F93" s="5" t="str">
         <f aca="false">IF($A93="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A93,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F93" s="5" t="str">
+      <c r="G93" s="5" t="str">
         <f aca="false">IF($A93="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A93,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G93" s="5" t="str">
+      <c r="H93" s="5" t="str">
         <f aca="false">IF($A93="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A93,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H93" s="5" t="str">
+      <c r="I93" s="5" t="str">
         <f aca="false">IF($A93="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A93,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I93" s="5" t="str">
+      <c r="J93" s="5" t="str">
         <f aca="false">IF($A93="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A93,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J93" s="5" t="str">
-        <f aca="false">IF($A93="","",$D93+$E93-$F93-$G93-$H93+$I93)</f>
-        <v/>
-      </c>
-      <c r="K93" s="4"/>
+      <c r="K93" s="5" t="str">
+        <f aca="false">IF($A93="","",$E93+$F93-$G93-$H93-$I93+$J93)</f>
+        <v/>
+      </c>
+      <c r="L93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
-      <c r="E94" s="5" t="str">
+      <c r="E94" s="4"/>
+      <c r="F94" s="5" t="str">
         <f aca="false">IF($A94="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A94,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F94" s="5" t="str">
+      <c r="G94" s="5" t="str">
         <f aca="false">IF($A94="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A94,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G94" s="5" t="str">
+      <c r="H94" s="5" t="str">
         <f aca="false">IF($A94="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A94,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H94" s="5" t="str">
+      <c r="I94" s="5" t="str">
         <f aca="false">IF($A94="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A94,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I94" s="5" t="str">
+      <c r="J94" s="5" t="str">
         <f aca="false">IF($A94="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A94,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J94" s="5" t="str">
-        <f aca="false">IF($A94="","",$D94+$E94-$F94-$G94-$H94+$I94)</f>
-        <v/>
-      </c>
-      <c r="K94" s="4"/>
+      <c r="K94" s="5" t="str">
+        <f aca="false">IF($A94="","",$E94+$F94-$G94-$H94-$I94+$J94)</f>
+        <v/>
+      </c>
+      <c r="L94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="5" t="str">
+      <c r="E95" s="4"/>
+      <c r="F95" s="5" t="str">
         <f aca="false">IF($A95="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A95,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F95" s="5" t="str">
+      <c r="G95" s="5" t="str">
         <f aca="false">IF($A95="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A95,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G95" s="5" t="str">
+      <c r="H95" s="5" t="str">
         <f aca="false">IF($A95="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A95,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H95" s="5" t="str">
+      <c r="I95" s="5" t="str">
         <f aca="false">IF($A95="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A95,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I95" s="5" t="str">
+      <c r="J95" s="5" t="str">
         <f aca="false">IF($A95="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A95,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J95" s="5" t="str">
-        <f aca="false">IF($A95="","",$D95+$E95-$F95-$G95-$H95+$I95)</f>
-        <v/>
-      </c>
-      <c r="K95" s="4"/>
+      <c r="K95" s="5" t="str">
+        <f aca="false">IF($A95="","",$E95+$F95-$G95-$H95-$I95+$J95)</f>
+        <v/>
+      </c>
+      <c r="L95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
-      <c r="E96" s="5" t="str">
+      <c r="E96" s="4"/>
+      <c r="F96" s="5" t="str">
         <f aca="false">IF($A96="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A96,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F96" s="5" t="str">
+      <c r="G96" s="5" t="str">
         <f aca="false">IF($A96="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A96,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G96" s="5" t="str">
+      <c r="H96" s="5" t="str">
         <f aca="false">IF($A96="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A96,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H96" s="5" t="str">
+      <c r="I96" s="5" t="str">
         <f aca="false">IF($A96="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A96,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I96" s="5" t="str">
+      <c r="J96" s="5" t="str">
         <f aca="false">IF($A96="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A96,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J96" s="5" t="str">
-        <f aca="false">IF($A96="","",$D96+$E96-$F96-$G96-$H96+$I96)</f>
-        <v/>
-      </c>
-      <c r="K96" s="4"/>
+      <c r="K96" s="5" t="str">
+        <f aca="false">IF($A96="","",$E96+$F96-$G96-$H96-$I96+$J96)</f>
+        <v/>
+      </c>
+      <c r="L96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="5" t="str">
+      <c r="E97" s="4"/>
+      <c r="F97" s="5" t="str">
         <f aca="false">IF($A97="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A97,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F97" s="5" t="str">
+      <c r="G97" s="5" t="str">
         <f aca="false">IF($A97="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A97,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G97" s="5" t="str">
+      <c r="H97" s="5" t="str">
         <f aca="false">IF($A97="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A97,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H97" s="5" t="str">
+      <c r="I97" s="5" t="str">
         <f aca="false">IF($A97="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A97,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I97" s="5" t="str">
+      <c r="J97" s="5" t="str">
         <f aca="false">IF($A97="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A97,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J97" s="5" t="str">
-        <f aca="false">IF($A97="","",$D97+$E97-$F97-$G97-$H97+$I97)</f>
-        <v/>
-      </c>
-      <c r="K97" s="4"/>
+      <c r="K97" s="5" t="str">
+        <f aca="false">IF($A97="","",$E97+$F97-$G97-$H97-$I97+$J97)</f>
+        <v/>
+      </c>
+      <c r="L97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
-      <c r="E98" s="5" t="str">
+      <c r="E98" s="4"/>
+      <c r="F98" s="5" t="str">
         <f aca="false">IF($A98="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A98,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F98" s="5" t="str">
+      <c r="G98" s="5" t="str">
         <f aca="false">IF($A98="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A98,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G98" s="5" t="str">
+      <c r="H98" s="5" t="str">
         <f aca="false">IF($A98="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A98,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H98" s="5" t="str">
+      <c r="I98" s="5" t="str">
         <f aca="false">IF($A98="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A98,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I98" s="5" t="str">
+      <c r="J98" s="5" t="str">
         <f aca="false">IF($A98="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A98,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J98" s="5" t="str">
-        <f aca="false">IF($A98="","",$D98+$E98-$F98-$G98-$H98+$I98)</f>
-        <v/>
-      </c>
-      <c r="K98" s="4"/>
+      <c r="K98" s="5" t="str">
+        <f aca="false">IF($A98="","",$E98+$F98-$G98-$H98-$I98+$J98)</f>
+        <v/>
+      </c>
+      <c r="L98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
-      <c r="E99" s="5" t="str">
+      <c r="E99" s="4"/>
+      <c r="F99" s="5" t="str">
         <f aca="false">IF($A99="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A99,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F99" s="5" t="str">
+      <c r="G99" s="5" t="str">
         <f aca="false">IF($A99="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A99,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G99" s="5" t="str">
+      <c r="H99" s="5" t="str">
         <f aca="false">IF($A99="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A99,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H99" s="5" t="str">
+      <c r="I99" s="5" t="str">
         <f aca="false">IF($A99="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A99,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I99" s="5" t="str">
+      <c r="J99" s="5" t="str">
         <f aca="false">IF($A99="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A99,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J99" s="5" t="str">
-        <f aca="false">IF($A99="","",$D99+$E99-$F99-$G99-$H99+$I99)</f>
-        <v/>
-      </c>
-      <c r="K99" s="4"/>
+      <c r="K99" s="5" t="str">
+        <f aca="false">IF($A99="","",$E99+$F99-$G99-$H99-$I99+$J99)</f>
+        <v/>
+      </c>
+      <c r="L99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
-      <c r="E100" s="5" t="str">
+      <c r="E100" s="4"/>
+      <c r="F100" s="5" t="str">
         <f aca="false">IF($A100="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A100,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F100" s="5" t="str">
+      <c r="G100" s="5" t="str">
         <f aca="false">IF($A100="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A100,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G100" s="5" t="str">
+      <c r="H100" s="5" t="str">
         <f aca="false">IF($A100="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A100,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H100" s="5" t="str">
+      <c r="I100" s="5" t="str">
         <f aca="false">IF($A100="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A100,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I100" s="5" t="str">
+      <c r="J100" s="5" t="str">
         <f aca="false">IF($A100="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A100,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J100" s="5" t="str">
-        <f aca="false">IF($A100="","",$D100+$E100-$F100-$G100-$H100+$I100)</f>
-        <v/>
-      </c>
-      <c r="K100" s="4"/>
+      <c r="K100" s="5" t="str">
+        <f aca="false">IF($A100="","",$E100+$F100-$G100-$H100-$I100+$J100)</f>
+        <v/>
+      </c>
+      <c r="L100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
-      <c r="E101" s="5" t="str">
+      <c r="E101" s="4"/>
+      <c r="F101" s="5" t="str">
         <f aca="false">IF($A101="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A101,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F101" s="5" t="str">
+      <c r="G101" s="5" t="str">
         <f aca="false">IF($A101="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A101,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G101" s="5" t="str">
+      <c r="H101" s="5" t="str">
         <f aca="false">IF($A101="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A101,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H101" s="5" t="str">
+      <c r="I101" s="5" t="str">
         <f aca="false">IF($A101="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A101,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I101" s="5" t="str">
+      <c r="J101" s="5" t="str">
         <f aca="false">IF($A101="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A101,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J101" s="5" t="str">
-        <f aca="false">IF($A101="","",$D101+$E101-$F101-$G101-$H101+$I101)</f>
-        <v/>
-      </c>
-      <c r="K101" s="4"/>
+      <c r="K101" s="5" t="str">
+        <f aca="false">IF($A101="","",$E101+$F101-$G101-$H101-$I101+$J101)</f>
+        <v/>
+      </c>
+      <c r="L101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
-      <c r="E102" s="5" t="str">
+      <c r="E102" s="4"/>
+      <c r="F102" s="5" t="str">
         <f aca="false">IF($A102="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A102,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F102" s="5" t="str">
+      <c r="G102" s="5" t="str">
         <f aca="false">IF($A102="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A102,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G102" s="5" t="str">
+      <c r="H102" s="5" t="str">
         <f aca="false">IF($A102="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A102,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H102" s="5" t="str">
+      <c r="I102" s="5" t="str">
         <f aca="false">IF($A102="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A102,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I102" s="5" t="str">
+      <c r="J102" s="5" t="str">
         <f aca="false">IF($A102="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A102,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J102" s="5" t="str">
-        <f aca="false">IF($A102="","",$D102+$E102-$F102-$G102-$H102+$I102)</f>
-        <v/>
-      </c>
-      <c r="K102" s="4"/>
+      <c r="K102" s="5" t="str">
+        <f aca="false">IF($A102="","",$E102+$F102-$G102-$H102-$I102+$J102)</f>
+        <v/>
+      </c>
+      <c r="L102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
-      <c r="E103" s="5" t="str">
+      <c r="E103" s="4"/>
+      <c r="F103" s="5" t="str">
         <f aca="false">IF($A103="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A103,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F103" s="5" t="str">
+      <c r="G103" s="5" t="str">
         <f aca="false">IF($A103="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A103,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G103" s="5" t="str">
+      <c r="H103" s="5" t="str">
         <f aca="false">IF($A103="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A103,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H103" s="5" t="str">
+      <c r="I103" s="5" t="str">
         <f aca="false">IF($A103="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A103,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I103" s="5" t="str">
+      <c r="J103" s="5" t="str">
         <f aca="false">IF($A103="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A103,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J103" s="5" t="str">
-        <f aca="false">IF($A103="","",$D103+$E103-$F103-$G103-$H103+$I103)</f>
-        <v/>
-      </c>
-      <c r="K103" s="4"/>
+      <c r="K103" s="5" t="str">
+        <f aca="false">IF($A103="","",$E103+$F103-$G103-$H103-$I103+$J103)</f>
+        <v/>
+      </c>
+      <c r="L103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
-      <c r="E104" s="5" t="str">
+      <c r="E104" s="4"/>
+      <c r="F104" s="5" t="str">
         <f aca="false">IF($A104="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A104,Movements!$B$5:$B$304,"Receive"))</f>
         <v/>
       </c>
-      <c r="F104" s="5" t="str">
+      <c r="G104" s="5" t="str">
         <f aca="false">IF($A104="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A104,Movements!$B$5:$B$304,"Sell"))</f>
         <v/>
       </c>
-      <c r="G104" s="5" t="str">
+      <c r="H104" s="5" t="str">
         <f aca="false">IF($A104="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A104,Recipes!$B$5:$B$104,"B"))</f>
         <v/>
       </c>
-      <c r="H104" s="5" t="str">
+      <c r="I104" s="5" t="str">
         <f aca="false">IF($A104="","",SUMIFS(Recipes!$H$5:$H$104,Recipes!$C$5:$C$104,$A104,Recipes!$B$5:$B$104,"C"))</f>
         <v/>
       </c>
-      <c r="I104" s="5" t="str">
+      <c r="J104" s="5" t="str">
         <f aca="false">IF($A104="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A104,Movements!$B$5:$B$304,"Adjust"))</f>
         <v/>
       </c>
-      <c r="J104" s="5" t="str">
-        <f aca="false">IF($A104="","",$D104+$E104-$F104-$G104-$H104+$I104)</f>
-        <v/>
-      </c>
-      <c r="K104" s="4"/>
+      <c r="K104" s="5" t="str">
+        <f aca="false">IF($A104="","",$E104+$F104-$G104-$H104-$I104+$J104)</f>
+        <v/>
+      </c>
+      <c r="L104" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D5:D104">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>NOT(OR($C5="Box",$C5="Pack",$C5="Set",$C5="Bundle",$C5="Dozen",$C5="Roll"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C104" type="list">
+      <formula1>"Pcs,Pack,Set,Pair,Dozen,Box,Bundle,Roll,Meters,Sheet,Kg,Grams"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Pcs per Pack applies to Box, Pack, Set, Bundle, Dozen and Roll. Set this row's Unit to one of those first, then enter how many single pieces are in one of them." errorStyle="stop" errorTitle="Only for a unit that holds pieces" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5:D104" type="custom">
+      <formula1>AND(OR($C5="Box",$C5="Pack",$C5="Set",$C5="Bundle",$C5="Dozen",$C5="Roll"),ISNUMBER($D5))</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4028,12 +4166,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4044,42 +4182,42 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" s="5" t="n">
         <f aca="false">IF($A5="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A5,Movements!$B$5:$B$304,"Build"))</f>
@@ -4118,15 +4256,15 @@
         <v>2</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">IF($A6="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A6,Movements!$B$5:$B$304,"Build"))</f>
@@ -4168,10 +4306,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="n">
         <f aca="false">IF($A7="","",SUMIFS(Movements!$D$5:$D$304,Movements!$C$5:$C$304,$A7,Movements!$B$5:$B$304,"Build"))</f>
@@ -8220,12 +8358,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8233,42 +8371,42 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>899</v>
@@ -8294,18 +8432,18 @@
         <v>Shares parts with other kits</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>1299</v>
@@ -11014,70 +11152,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>30</v>
@@ -11099,15 +11237,15 @@
         <v>660</v>
       </c>
       <c r="I5" s="6" t="n">
-        <f aca="false">IF($B5&lt;&gt;"B","",IFERROR(IF($D5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$D5,1)),0))</f>
+        <f aca="false">IF($B5&lt;&gt;"B","",IFERROR(IF($D5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$D5,1)),0))</f>
         <v>19</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
+        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
         <v/>
       </c>
       <c r="K5" s="6" t="str">
-        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
+        <f aca="false">IF($B5&lt;&gt;"C","",IFERROR(IF($E5="B",IF($D5=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C5,'B Made'!$A$5:$A$104,0)))/$D5,1)),IF($O5=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C5,'A Loose'!$A$5:$A$104,0)))/$O5,1))),0))</f>
         <v/>
       </c>
       <c r="L5" s="6" t="str">
@@ -11129,13 +11267,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
@@ -11157,15 +11295,15 @@
         <v>22</v>
       </c>
       <c r="I6" s="6" t="n">
-        <f aca="false">IF($B6&lt;&gt;"B","",IFERROR(IF($D6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$D6,1)),0))</f>
+        <f aca="false">IF($B6&lt;&gt;"B","",IFERROR(IF($D6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$D6,1)),0))</f>
         <v>38</v>
       </c>
       <c r="J6" s="6" t="str">
-        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
+        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
         <v/>
       </c>
       <c r="K6" s="6" t="str">
-        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
+        <f aca="false">IF($B6&lt;&gt;"C","",IFERROR(IF($E6="B",IF($D6=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C6,'B Made'!$A$5:$A$104,0)))/$D6,1)),IF($O6=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C6,'A Loose'!$A$5:$A$104,0)))/$O6,1))),0))</f>
         <v/>
       </c>
       <c r="L6" s="6" t="str">
@@ -11187,13 +11325,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1</v>
@@ -11215,15 +11353,15 @@
         <v>22</v>
       </c>
       <c r="I7" s="6" t="n">
-        <f aca="false">IF($B7&lt;&gt;"B","",IFERROR(IF($D7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$D7,1)),0))</f>
+        <f aca="false">IF($B7&lt;&gt;"B","",IFERROR(IF($D7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$D7,1)),0))</f>
         <v>178</v>
       </c>
       <c r="J7" s="6" t="str">
-        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
+        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
         <v/>
       </c>
       <c r="K7" s="6" t="str">
-        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
+        <f aca="false">IF($B7&lt;&gt;"C","",IFERROR(IF($E7="B",IF($D7=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C7,'B Made'!$A$5:$A$104,0)))/$D7,1)),IF($O7=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C7,'A Loose'!$A$5:$A$104,0)))/$O7,1))),0))</f>
         <v/>
       </c>
       <c r="L7" s="6" t="str">
@@ -11245,13 +11383,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>1</v>
@@ -11273,15 +11411,15 @@
         <v>12</v>
       </c>
       <c r="I8" s="6" t="n">
-        <f aca="false">IF($B8&lt;&gt;"B","",IFERROR(IF($D8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$D8,1)),0))</f>
+        <f aca="false">IF($B8&lt;&gt;"B","",IFERROR(IF($D8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$D8,1)),0))</f>
         <v>138</v>
       </c>
       <c r="J8" s="6" t="str">
-        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
+        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
         <v/>
       </c>
       <c r="K8" s="6" t="str">
-        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
+        <f aca="false">IF($B8&lt;&gt;"C","",IFERROR(IF($E8="B",IF($D8=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C8,'B Made'!$A$5:$A$104,0)))/$D8,1)),IF($O8=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C8,'A Loose'!$A$5:$A$104,0)))/$O8,1))),0))</f>
         <v/>
       </c>
       <c r="L8" s="6" t="str">
@@ -11303,13 +11441,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>10</v>
@@ -11331,15 +11469,15 @@
         <v>120</v>
       </c>
       <c r="I9" s="6" t="n">
-        <f aca="false">IF($B9&lt;&gt;"B","",IFERROR(IF($D9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$D9,1)),0))</f>
+        <f aca="false">IF($B9&lt;&gt;"B","",IFERROR(IF($D9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$D9,1)),0))</f>
         <v>58</v>
       </c>
       <c r="J9" s="6" t="str">
-        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
+        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
         <v/>
       </c>
       <c r="K9" s="6" t="str">
-        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
+        <f aca="false">IF($B9&lt;&gt;"C","",IFERROR(IF($E9="B",IF($D9=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C9,'B Made'!$A$5:$A$104,0)))/$D9,1)),IF($O9=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C9,'A Loose'!$A$5:$A$104,0)))/$O9,1))),0))</f>
         <v/>
       </c>
       <c r="L9" s="6" t="str">
@@ -11361,13 +11499,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1</v>
@@ -11389,15 +11527,15 @@
         <v>17</v>
       </c>
       <c r="I10" s="6" t="n">
-        <f aca="false">IF($B10&lt;&gt;"B","",IFERROR(IF($D10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$D10,1)),0))</f>
+        <f aca="false">IF($B10&lt;&gt;"B","",IFERROR(IF($D10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$D10,1)),0))</f>
         <v>63</v>
       </c>
       <c r="J10" s="6" t="str">
-        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
+        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
         <v/>
       </c>
       <c r="K10" s="6" t="str">
-        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
+        <f aca="false">IF($B10&lt;&gt;"C","",IFERROR(IF($E10="B",IF($D10=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C10,'B Made'!$A$5:$A$104,0)))/$D10,1)),IF($O10=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C10,'A Loose'!$A$5:$A$104,0)))/$O10,1))),0))</f>
         <v/>
       </c>
       <c r="L10" s="6" t="str">
@@ -11419,13 +11557,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>1</v>
@@ -11447,15 +11585,15 @@
         <v>12</v>
       </c>
       <c r="I11" s="6" t="str">
-        <f aca="false">IF($B11&lt;&gt;"B","",IFERROR(IF($D11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$D11,1)),0))</f>
+        <f aca="false">IF($B11&lt;&gt;"B","",IFERROR(IF($D11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$D11,1)),0))</f>
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
+        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
+        <f aca="false">IF($B11&lt;&gt;"C","",IFERROR(IF($E11="B",IF($D11=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C11,'B Made'!$A$5:$A$104,0)))/$D11,1)),IF($O11=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C11,'A Loose'!$A$5:$A$104,0)))/$O11,1))),0))</f>
         <v>19</v>
       </c>
       <c r="L11" s="6" t="str">
@@ -11477,13 +11615,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>1</v>
@@ -11505,15 +11643,15 @@
         <v>12</v>
       </c>
       <c r="I12" s="6" t="str">
-        <f aca="false">IF($B12&lt;&gt;"B","",IFERROR(IF($D12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$D12,1)),0))</f>
+        <f aca="false">IF($B12&lt;&gt;"B","",IFERROR(IF($D12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$D12,1)),0))</f>
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
+        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
-        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
+        <f aca="false">IF($B12&lt;&gt;"C","",IFERROR(IF($E12="B",IF($D12=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C12,'B Made'!$A$5:$A$104,0)))/$D12,1)),IF($O12=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C12,'A Loose'!$A$5:$A$104,0)))/$O12,1))),0))</f>
         <v>58</v>
       </c>
       <c r="L12" s="6" t="str">
@@ -11535,13 +11673,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1</v>
@@ -11563,15 +11701,15 @@
         <v>12</v>
       </c>
       <c r="I13" s="6" t="str">
-        <f aca="false">IF($B13&lt;&gt;"B","",IFERROR(IF($D13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$D13,1)),0))</f>
+        <f aca="false">IF($B13&lt;&gt;"B","",IFERROR(IF($D13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$D13,1)),0))</f>
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
+        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
+        <f aca="false">IF($B13&lt;&gt;"C","",IFERROR(IF($E13="B",IF($D13=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C13,'B Made'!$A$5:$A$104,0)))/$D13,1)),IF($O13=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C13,'A Loose'!$A$5:$A$104,0)))/$O13,1))),0))</f>
         <v>63</v>
       </c>
       <c r="L13" s="6" t="str">
@@ -11593,13 +11731,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>10</v>
@@ -11621,15 +11759,15 @@
         <v>120</v>
       </c>
       <c r="I14" s="6" t="str">
-        <f aca="false">IF($B14&lt;&gt;"B","",IFERROR(IF($D14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$D14,1)),0))</f>
+        <f aca="false">IF($B14&lt;&gt;"B","",IFERROR(IF($D14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$D14,1)),0))</f>
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
+        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
         <v>11</v>
       </c>
       <c r="K14" s="6" t="n">
-        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
+        <f aca="false">IF($B14&lt;&gt;"C","",IFERROR(IF($E14="B",IF($D14=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C14,'B Made'!$A$5:$A$104,0)))/$D14,1)),IF($O14=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C14,'A Loose'!$A$5:$A$104,0)))/$O14,1))),0))</f>
         <v>11</v>
       </c>
       <c r="L14" s="6" t="str">
@@ -11651,13 +11789,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>2</v>
@@ -11679,15 +11817,15 @@
         <v>10</v>
       </c>
       <c r="I15" s="6" t="str">
-        <f aca="false">IF($B15&lt;&gt;"B","",IFERROR(IF($D15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$D15,1)),0))</f>
+        <f aca="false">IF($B15&lt;&gt;"B","",IFERROR(IF($D15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$D15,1)),0))</f>
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
+        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
+        <f aca="false">IF($B15&lt;&gt;"C","",IFERROR(IF($E15="B",IF($D15=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C15,'B Made'!$A$5:$A$104,0)))/$D15,1)),IF($O15=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C15,'A Loose'!$A$5:$A$104,0)))/$O15,1))),0))</f>
         <v>9</v>
       </c>
       <c r="L15" s="6" t="str">
@@ -11709,13 +11847,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1</v>
@@ -11737,15 +11875,15 @@
         <v>5</v>
       </c>
       <c r="I16" s="6" t="str">
-        <f aca="false">IF($B16&lt;&gt;"B","",IFERROR(IF($D16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$D16,1)),0))</f>
+        <f aca="false">IF($B16&lt;&gt;"B","",IFERROR(IF($D16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$D16,1)),0))</f>
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
+        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
+        <f aca="false">IF($B16&lt;&gt;"C","",IFERROR(IF($E16="B",IF($D16=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C16,'B Made'!$A$5:$A$104,0)))/$D16,1)),IF($O16=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C16,'A Loose'!$A$5:$A$104,0)))/$O16,1))),0))</f>
         <v>63</v>
       </c>
       <c r="L16" s="6" t="str">
@@ -11787,15 +11925,15 @@
         <v/>
       </c>
       <c r="I17" s="6" t="str">
-        <f aca="false">IF($B17&lt;&gt;"B","",IFERROR(IF($D17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$D17,1)),0))</f>
+        <f aca="false">IF($B17&lt;&gt;"B","",IFERROR(IF($D17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$D17,1)),0))</f>
         <v/>
       </c>
       <c r="J17" s="6" t="str">
-        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
+        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
         <v/>
       </c>
       <c r="K17" s="6" t="str">
-        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
+        <f aca="false">IF($B17&lt;&gt;"C","",IFERROR(IF($E17="B",IF($D17=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C17,'B Made'!$A$5:$A$104,0)))/$D17,1)),IF($O17=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C17,'A Loose'!$A$5:$A$104,0)))/$O17,1))),0))</f>
         <v/>
       </c>
       <c r="L17" s="6" t="str">
@@ -11837,15 +11975,15 @@
         <v/>
       </c>
       <c r="I18" s="6" t="str">
-        <f aca="false">IF($B18&lt;&gt;"B","",IFERROR(IF($D18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$D18,1)),0))</f>
+        <f aca="false">IF($B18&lt;&gt;"B","",IFERROR(IF($D18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$D18,1)),0))</f>
         <v/>
       </c>
       <c r="J18" s="6" t="str">
-        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
+        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
         <v/>
       </c>
       <c r="K18" s="6" t="str">
-        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
+        <f aca="false">IF($B18&lt;&gt;"C","",IFERROR(IF($E18="B",IF($D18=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C18,'B Made'!$A$5:$A$104,0)))/$D18,1)),IF($O18=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C18,'A Loose'!$A$5:$A$104,0)))/$O18,1))),0))</f>
         <v/>
       </c>
       <c r="L18" s="6" t="str">
@@ -11887,15 +12025,15 @@
         <v/>
       </c>
       <c r="I19" s="6" t="str">
-        <f aca="false">IF($B19&lt;&gt;"B","",IFERROR(IF($D19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$D19,1)),0))</f>
+        <f aca="false">IF($B19&lt;&gt;"B","",IFERROR(IF($D19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$D19,1)),0))</f>
         <v/>
       </c>
       <c r="J19" s="6" t="str">
-        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
+        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
         <v/>
       </c>
       <c r="K19" s="6" t="str">
-        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
+        <f aca="false">IF($B19&lt;&gt;"C","",IFERROR(IF($E19="B",IF($D19=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C19,'B Made'!$A$5:$A$104,0)))/$D19,1)),IF($O19=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C19,'A Loose'!$A$5:$A$104,0)))/$O19,1))),0))</f>
         <v/>
       </c>
       <c r="L19" s="6" t="str">
@@ -11937,15 +12075,15 @@
         <v/>
       </c>
       <c r="I20" s="6" t="str">
-        <f aca="false">IF($B20&lt;&gt;"B","",IFERROR(IF($D20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$D20,1)),0))</f>
+        <f aca="false">IF($B20&lt;&gt;"B","",IFERROR(IF($D20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$D20,1)),0))</f>
         <v/>
       </c>
       <c r="J20" s="6" t="str">
-        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
+        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
         <v/>
       </c>
       <c r="K20" s="6" t="str">
-        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
+        <f aca="false">IF($B20&lt;&gt;"C","",IFERROR(IF($E20="B",IF($D20=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C20,'B Made'!$A$5:$A$104,0)))/$D20,1)),IF($O20=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C20,'A Loose'!$A$5:$A$104,0)))/$O20,1))),0))</f>
         <v/>
       </c>
       <c r="L20" s="6" t="str">
@@ -11987,15 +12125,15 @@
         <v/>
       </c>
       <c r="I21" s="6" t="str">
-        <f aca="false">IF($B21&lt;&gt;"B","",IFERROR(IF($D21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$D21,1)),0))</f>
+        <f aca="false">IF($B21&lt;&gt;"B","",IFERROR(IF($D21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$D21,1)),0))</f>
         <v/>
       </c>
       <c r="J21" s="6" t="str">
-        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
+        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
         <v/>
       </c>
       <c r="K21" s="6" t="str">
-        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
+        <f aca="false">IF($B21&lt;&gt;"C","",IFERROR(IF($E21="B",IF($D21=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C21,'B Made'!$A$5:$A$104,0)))/$D21,1)),IF($O21=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C21,'A Loose'!$A$5:$A$104,0)))/$O21,1))),0))</f>
         <v/>
       </c>
       <c r="L21" s="6" t="str">
@@ -12037,15 +12175,15 @@
         <v/>
       </c>
       <c r="I22" s="6" t="str">
-        <f aca="false">IF($B22&lt;&gt;"B","",IFERROR(IF($D22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$D22,1)),0))</f>
+        <f aca="false">IF($B22&lt;&gt;"B","",IFERROR(IF($D22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$D22,1)),0))</f>
         <v/>
       </c>
       <c r="J22" s="6" t="str">
-        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
+        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
         <v/>
       </c>
       <c r="K22" s="6" t="str">
-        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
+        <f aca="false">IF($B22&lt;&gt;"C","",IFERROR(IF($E22="B",IF($D22=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C22,'B Made'!$A$5:$A$104,0)))/$D22,1)),IF($O22=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C22,'A Loose'!$A$5:$A$104,0)))/$O22,1))),0))</f>
         <v/>
       </c>
       <c r="L22" s="6" t="str">
@@ -12087,15 +12225,15 @@
         <v/>
       </c>
       <c r="I23" s="6" t="str">
-        <f aca="false">IF($B23&lt;&gt;"B","",IFERROR(IF($D23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$D23,1)),0))</f>
+        <f aca="false">IF($B23&lt;&gt;"B","",IFERROR(IF($D23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$D23,1)),0))</f>
         <v/>
       </c>
       <c r="J23" s="6" t="str">
-        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
+        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
         <v/>
       </c>
       <c r="K23" s="6" t="str">
-        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
+        <f aca="false">IF($B23&lt;&gt;"C","",IFERROR(IF($E23="B",IF($D23=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C23,'B Made'!$A$5:$A$104,0)))/$D23,1)),IF($O23=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C23,'A Loose'!$A$5:$A$104,0)))/$O23,1))),0))</f>
         <v/>
       </c>
       <c r="L23" s="6" t="str">
@@ -12137,15 +12275,15 @@
         <v/>
       </c>
       <c r="I24" s="6" t="str">
-        <f aca="false">IF($B24&lt;&gt;"B","",IFERROR(IF($D24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$D24,1)),0))</f>
+        <f aca="false">IF($B24&lt;&gt;"B","",IFERROR(IF($D24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$D24,1)),0))</f>
         <v/>
       </c>
       <c r="J24" s="6" t="str">
-        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
+        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
         <v/>
       </c>
       <c r="K24" s="6" t="str">
-        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
+        <f aca="false">IF($B24&lt;&gt;"C","",IFERROR(IF($E24="B",IF($D24=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C24,'B Made'!$A$5:$A$104,0)))/$D24,1)),IF($O24=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C24,'A Loose'!$A$5:$A$104,0)))/$O24,1))),0))</f>
         <v/>
       </c>
       <c r="L24" s="6" t="str">
@@ -12187,15 +12325,15 @@
         <v/>
       </c>
       <c r="I25" s="6" t="str">
-        <f aca="false">IF($B25&lt;&gt;"B","",IFERROR(IF($D25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$D25,1)),0))</f>
+        <f aca="false">IF($B25&lt;&gt;"B","",IFERROR(IF($D25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$D25,1)),0))</f>
         <v/>
       </c>
       <c r="J25" s="6" t="str">
-        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
+        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
         <v/>
       </c>
       <c r="K25" s="6" t="str">
-        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
+        <f aca="false">IF($B25&lt;&gt;"C","",IFERROR(IF($E25="B",IF($D25=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C25,'B Made'!$A$5:$A$104,0)))/$D25,1)),IF($O25=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C25,'A Loose'!$A$5:$A$104,0)))/$O25,1))),0))</f>
         <v/>
       </c>
       <c r="L25" s="6" t="str">
@@ -12237,15 +12375,15 @@
         <v/>
       </c>
       <c r="I26" s="6" t="str">
-        <f aca="false">IF($B26&lt;&gt;"B","",IFERROR(IF($D26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$D26,1)),0))</f>
+        <f aca="false">IF($B26&lt;&gt;"B","",IFERROR(IF($D26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$D26,1)),0))</f>
         <v/>
       </c>
       <c r="J26" s="6" t="str">
-        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
+        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
         <v/>
       </c>
       <c r="K26" s="6" t="str">
-        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
+        <f aca="false">IF($B26&lt;&gt;"C","",IFERROR(IF($E26="B",IF($D26=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C26,'B Made'!$A$5:$A$104,0)))/$D26,1)),IF($O26=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C26,'A Loose'!$A$5:$A$104,0)))/$O26,1))),0))</f>
         <v/>
       </c>
       <c r="L26" s="6" t="str">
@@ -12287,15 +12425,15 @@
         <v/>
       </c>
       <c r="I27" s="6" t="str">
-        <f aca="false">IF($B27&lt;&gt;"B","",IFERROR(IF($D27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$D27,1)),0))</f>
+        <f aca="false">IF($B27&lt;&gt;"B","",IFERROR(IF($D27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$D27,1)),0))</f>
         <v/>
       </c>
       <c r="J27" s="6" t="str">
-        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
+        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
         <v/>
       </c>
       <c r="K27" s="6" t="str">
-        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
+        <f aca="false">IF($B27&lt;&gt;"C","",IFERROR(IF($E27="B",IF($D27=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C27,'B Made'!$A$5:$A$104,0)))/$D27,1)),IF($O27=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C27,'A Loose'!$A$5:$A$104,0)))/$O27,1))),0))</f>
         <v/>
       </c>
       <c r="L27" s="6" t="str">
@@ -12337,15 +12475,15 @@
         <v/>
       </c>
       <c r="I28" s="6" t="str">
-        <f aca="false">IF($B28&lt;&gt;"B","",IFERROR(IF($D28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$D28,1)),0))</f>
+        <f aca="false">IF($B28&lt;&gt;"B","",IFERROR(IF($D28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$D28,1)),0))</f>
         <v/>
       </c>
       <c r="J28" s="6" t="str">
-        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
+        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
         <v/>
       </c>
       <c r="K28" s="6" t="str">
-        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
+        <f aca="false">IF($B28&lt;&gt;"C","",IFERROR(IF($E28="B",IF($D28=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C28,'B Made'!$A$5:$A$104,0)))/$D28,1)),IF($O28=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C28,'A Loose'!$A$5:$A$104,0)))/$O28,1))),0))</f>
         <v/>
       </c>
       <c r="L28" s="6" t="str">
@@ -12387,15 +12525,15 @@
         <v/>
       </c>
       <c r="I29" s="6" t="str">
-        <f aca="false">IF($B29&lt;&gt;"B","",IFERROR(IF($D29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$D29,1)),0))</f>
+        <f aca="false">IF($B29&lt;&gt;"B","",IFERROR(IF($D29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$D29,1)),0))</f>
         <v/>
       </c>
       <c r="J29" s="6" t="str">
-        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
+        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
         <v/>
       </c>
       <c r="K29" s="6" t="str">
-        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
+        <f aca="false">IF($B29&lt;&gt;"C","",IFERROR(IF($E29="B",IF($D29=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C29,'B Made'!$A$5:$A$104,0)))/$D29,1)),IF($O29=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C29,'A Loose'!$A$5:$A$104,0)))/$O29,1))),0))</f>
         <v/>
       </c>
       <c r="L29" s="6" t="str">
@@ -12437,15 +12575,15 @@
         <v/>
       </c>
       <c r="I30" s="6" t="str">
-        <f aca="false">IF($B30&lt;&gt;"B","",IFERROR(IF($D30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$D30,1)),0))</f>
+        <f aca="false">IF($B30&lt;&gt;"B","",IFERROR(IF($D30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$D30,1)),0))</f>
         <v/>
       </c>
       <c r="J30" s="6" t="str">
-        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
+        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
         <v/>
       </c>
       <c r="K30" s="6" t="str">
-        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
+        <f aca="false">IF($B30&lt;&gt;"C","",IFERROR(IF($E30="B",IF($D30=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C30,'B Made'!$A$5:$A$104,0)))/$D30,1)),IF($O30=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C30,'A Loose'!$A$5:$A$104,0)))/$O30,1))),0))</f>
         <v/>
       </c>
       <c r="L30" s="6" t="str">
@@ -12487,15 +12625,15 @@
         <v/>
       </c>
       <c r="I31" s="6" t="str">
-        <f aca="false">IF($B31&lt;&gt;"B","",IFERROR(IF($D31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$D31,1)),0))</f>
+        <f aca="false">IF($B31&lt;&gt;"B","",IFERROR(IF($D31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$D31,1)),0))</f>
         <v/>
       </c>
       <c r="J31" s="6" t="str">
-        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
+        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
         <v/>
       </c>
       <c r="K31" s="6" t="str">
-        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
+        <f aca="false">IF($B31&lt;&gt;"C","",IFERROR(IF($E31="B",IF($D31=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C31,'B Made'!$A$5:$A$104,0)))/$D31,1)),IF($O31=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C31,'A Loose'!$A$5:$A$104,0)))/$O31,1))),0))</f>
         <v/>
       </c>
       <c r="L31" s="6" t="str">
@@ -12537,15 +12675,15 @@
         <v/>
       </c>
       <c r="I32" s="6" t="str">
-        <f aca="false">IF($B32&lt;&gt;"B","",IFERROR(IF($D32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$D32,1)),0))</f>
+        <f aca="false">IF($B32&lt;&gt;"B","",IFERROR(IF($D32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$D32,1)),0))</f>
         <v/>
       </c>
       <c r="J32" s="6" t="str">
-        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
+        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
         <v/>
       </c>
       <c r="K32" s="6" t="str">
-        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
+        <f aca="false">IF($B32&lt;&gt;"C","",IFERROR(IF($E32="B",IF($D32=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C32,'B Made'!$A$5:$A$104,0)))/$D32,1)),IF($O32=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C32,'A Loose'!$A$5:$A$104,0)))/$O32,1))),0))</f>
         <v/>
       </c>
       <c r="L32" s="6" t="str">
@@ -12587,15 +12725,15 @@
         <v/>
       </c>
       <c r="I33" s="6" t="str">
-        <f aca="false">IF($B33&lt;&gt;"B","",IFERROR(IF($D33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$D33,1)),0))</f>
+        <f aca="false">IF($B33&lt;&gt;"B","",IFERROR(IF($D33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$D33,1)),0))</f>
         <v/>
       </c>
       <c r="J33" s="6" t="str">
-        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
+        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
         <v/>
       </c>
       <c r="K33" s="6" t="str">
-        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
+        <f aca="false">IF($B33&lt;&gt;"C","",IFERROR(IF($E33="B",IF($D33=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C33,'B Made'!$A$5:$A$104,0)))/$D33,1)),IF($O33=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C33,'A Loose'!$A$5:$A$104,0)))/$O33,1))),0))</f>
         <v/>
       </c>
       <c r="L33" s="6" t="str">
@@ -12637,15 +12775,15 @@
         <v/>
       </c>
       <c r="I34" s="6" t="str">
-        <f aca="false">IF($B34&lt;&gt;"B","",IFERROR(IF($D34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$D34,1)),0))</f>
+        <f aca="false">IF($B34&lt;&gt;"B","",IFERROR(IF($D34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$D34,1)),0))</f>
         <v/>
       </c>
       <c r="J34" s="6" t="str">
-        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
+        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
         <v/>
       </c>
       <c r="K34" s="6" t="str">
-        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
+        <f aca="false">IF($B34&lt;&gt;"C","",IFERROR(IF($E34="B",IF($D34=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C34,'B Made'!$A$5:$A$104,0)))/$D34,1)),IF($O34=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C34,'A Loose'!$A$5:$A$104,0)))/$O34,1))),0))</f>
         <v/>
       </c>
       <c r="L34" s="6" t="str">
@@ -12687,15 +12825,15 @@
         <v/>
       </c>
       <c r="I35" s="6" t="str">
-        <f aca="false">IF($B35&lt;&gt;"B","",IFERROR(IF($D35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$D35,1)),0))</f>
+        <f aca="false">IF($B35&lt;&gt;"B","",IFERROR(IF($D35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$D35,1)),0))</f>
         <v/>
       </c>
       <c r="J35" s="6" t="str">
-        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
+        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
         <v/>
       </c>
       <c r="K35" s="6" t="str">
-        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
+        <f aca="false">IF($B35&lt;&gt;"C","",IFERROR(IF($E35="B",IF($D35=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C35,'B Made'!$A$5:$A$104,0)))/$D35,1)),IF($O35=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C35,'A Loose'!$A$5:$A$104,0)))/$O35,1))),0))</f>
         <v/>
       </c>
       <c r="L35" s="6" t="str">
@@ -12737,15 +12875,15 @@
         <v/>
       </c>
       <c r="I36" s="6" t="str">
-        <f aca="false">IF($B36&lt;&gt;"B","",IFERROR(IF($D36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$D36,1)),0))</f>
+        <f aca="false">IF($B36&lt;&gt;"B","",IFERROR(IF($D36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$D36,1)),0))</f>
         <v/>
       </c>
       <c r="J36" s="6" t="str">
-        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
+        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
         <v/>
       </c>
       <c r="K36" s="6" t="str">
-        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
+        <f aca="false">IF($B36&lt;&gt;"C","",IFERROR(IF($E36="B",IF($D36=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C36,'B Made'!$A$5:$A$104,0)))/$D36,1)),IF($O36=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C36,'A Loose'!$A$5:$A$104,0)))/$O36,1))),0))</f>
         <v/>
       </c>
       <c r="L36" s="6" t="str">
@@ -12787,15 +12925,15 @@
         <v/>
       </c>
       <c r="I37" s="6" t="str">
-        <f aca="false">IF($B37&lt;&gt;"B","",IFERROR(IF($D37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$D37,1)),0))</f>
+        <f aca="false">IF($B37&lt;&gt;"B","",IFERROR(IF($D37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$D37,1)),0))</f>
         <v/>
       </c>
       <c r="J37" s="6" t="str">
-        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
+        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
         <v/>
       </c>
       <c r="K37" s="6" t="str">
-        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
+        <f aca="false">IF($B37&lt;&gt;"C","",IFERROR(IF($E37="B",IF($D37=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C37,'B Made'!$A$5:$A$104,0)))/$D37,1)),IF($O37=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C37,'A Loose'!$A$5:$A$104,0)))/$O37,1))),0))</f>
         <v/>
       </c>
       <c r="L37" s="6" t="str">
@@ -12837,15 +12975,15 @@
         <v/>
       </c>
       <c r="I38" s="6" t="str">
-        <f aca="false">IF($B38&lt;&gt;"B","",IFERROR(IF($D38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$D38,1)),0))</f>
+        <f aca="false">IF($B38&lt;&gt;"B","",IFERROR(IF($D38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$D38,1)),0))</f>
         <v/>
       </c>
       <c r="J38" s="6" t="str">
-        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
+        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
         <v/>
       </c>
       <c r="K38" s="6" t="str">
-        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
+        <f aca="false">IF($B38&lt;&gt;"C","",IFERROR(IF($E38="B",IF($D38=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C38,'B Made'!$A$5:$A$104,0)))/$D38,1)),IF($O38=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C38,'A Loose'!$A$5:$A$104,0)))/$O38,1))),0))</f>
         <v/>
       </c>
       <c r="L38" s="6" t="str">
@@ -12887,15 +13025,15 @@
         <v/>
       </c>
       <c r="I39" s="6" t="str">
-        <f aca="false">IF($B39&lt;&gt;"B","",IFERROR(IF($D39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$D39,1)),0))</f>
+        <f aca="false">IF($B39&lt;&gt;"B","",IFERROR(IF($D39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$D39,1)),0))</f>
         <v/>
       </c>
       <c r="J39" s="6" t="str">
-        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
+        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
         <v/>
       </c>
       <c r="K39" s="6" t="str">
-        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
+        <f aca="false">IF($B39&lt;&gt;"C","",IFERROR(IF($E39="B",IF($D39=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C39,'B Made'!$A$5:$A$104,0)))/$D39,1)),IF($O39=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C39,'A Loose'!$A$5:$A$104,0)))/$O39,1))),0))</f>
         <v/>
       </c>
       <c r="L39" s="6" t="str">
@@ -12937,15 +13075,15 @@
         <v/>
       </c>
       <c r="I40" s="6" t="str">
-        <f aca="false">IF($B40&lt;&gt;"B","",IFERROR(IF($D40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$D40,1)),0))</f>
+        <f aca="false">IF($B40&lt;&gt;"B","",IFERROR(IF($D40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$D40,1)),0))</f>
         <v/>
       </c>
       <c r="J40" s="6" t="str">
-        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
+        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
         <v/>
       </c>
       <c r="K40" s="6" t="str">
-        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
+        <f aca="false">IF($B40&lt;&gt;"C","",IFERROR(IF($E40="B",IF($D40=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C40,'B Made'!$A$5:$A$104,0)))/$D40,1)),IF($O40=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C40,'A Loose'!$A$5:$A$104,0)))/$O40,1))),0))</f>
         <v/>
       </c>
       <c r="L40" s="6" t="str">
@@ -12987,15 +13125,15 @@
         <v/>
       </c>
       <c r="I41" s="6" t="str">
-        <f aca="false">IF($B41&lt;&gt;"B","",IFERROR(IF($D41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$D41,1)),0))</f>
+        <f aca="false">IF($B41&lt;&gt;"B","",IFERROR(IF($D41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$D41,1)),0))</f>
         <v/>
       </c>
       <c r="J41" s="6" t="str">
-        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
+        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
         <v/>
       </c>
       <c r="K41" s="6" t="str">
-        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
+        <f aca="false">IF($B41&lt;&gt;"C","",IFERROR(IF($E41="B",IF($D41=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C41,'B Made'!$A$5:$A$104,0)))/$D41,1)),IF($O41=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C41,'A Loose'!$A$5:$A$104,0)))/$O41,1))),0))</f>
         <v/>
       </c>
       <c r="L41" s="6" t="str">
@@ -13037,15 +13175,15 @@
         <v/>
       </c>
       <c r="I42" s="6" t="str">
-        <f aca="false">IF($B42&lt;&gt;"B","",IFERROR(IF($D42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$D42,1)),0))</f>
+        <f aca="false">IF($B42&lt;&gt;"B","",IFERROR(IF($D42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$D42,1)),0))</f>
         <v/>
       </c>
       <c r="J42" s="6" t="str">
-        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
+        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
         <v/>
       </c>
       <c r="K42" s="6" t="str">
-        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
+        <f aca="false">IF($B42&lt;&gt;"C","",IFERROR(IF($E42="B",IF($D42=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C42,'B Made'!$A$5:$A$104,0)))/$D42,1)),IF($O42=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C42,'A Loose'!$A$5:$A$104,0)))/$O42,1))),0))</f>
         <v/>
       </c>
       <c r="L42" s="6" t="str">
@@ -13087,15 +13225,15 @@
         <v/>
       </c>
       <c r="I43" s="6" t="str">
-        <f aca="false">IF($B43&lt;&gt;"B","",IFERROR(IF($D43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$D43,1)),0))</f>
+        <f aca="false">IF($B43&lt;&gt;"B","",IFERROR(IF($D43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$D43,1)),0))</f>
         <v/>
       </c>
       <c r="J43" s="6" t="str">
-        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
+        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
         <v/>
       </c>
       <c r="K43" s="6" t="str">
-        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
+        <f aca="false">IF($B43&lt;&gt;"C","",IFERROR(IF($E43="B",IF($D43=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C43,'B Made'!$A$5:$A$104,0)))/$D43,1)),IF($O43=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C43,'A Loose'!$A$5:$A$104,0)))/$O43,1))),0))</f>
         <v/>
       </c>
       <c r="L43" s="6" t="str">
@@ -13137,15 +13275,15 @@
         <v/>
       </c>
       <c r="I44" s="6" t="str">
-        <f aca="false">IF($B44&lt;&gt;"B","",IFERROR(IF($D44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$D44,1)),0))</f>
+        <f aca="false">IF($B44&lt;&gt;"B","",IFERROR(IF($D44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$D44,1)),0))</f>
         <v/>
       </c>
       <c r="J44" s="6" t="str">
-        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
+        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
         <v/>
       </c>
       <c r="K44" s="6" t="str">
-        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
+        <f aca="false">IF($B44&lt;&gt;"C","",IFERROR(IF($E44="B",IF($D44=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C44,'B Made'!$A$5:$A$104,0)))/$D44,1)),IF($O44=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C44,'A Loose'!$A$5:$A$104,0)))/$O44,1))),0))</f>
         <v/>
       </c>
       <c r="L44" s="6" t="str">
@@ -13187,15 +13325,15 @@
         <v/>
       </c>
       <c r="I45" s="6" t="str">
-        <f aca="false">IF($B45&lt;&gt;"B","",IFERROR(IF($D45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$D45,1)),0))</f>
+        <f aca="false">IF($B45&lt;&gt;"B","",IFERROR(IF($D45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$D45,1)),0))</f>
         <v/>
       </c>
       <c r="J45" s="6" t="str">
-        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
+        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
         <v/>
       </c>
       <c r="K45" s="6" t="str">
-        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
+        <f aca="false">IF($B45&lt;&gt;"C","",IFERROR(IF($E45="B",IF($D45=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C45,'B Made'!$A$5:$A$104,0)))/$D45,1)),IF($O45=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C45,'A Loose'!$A$5:$A$104,0)))/$O45,1))),0))</f>
         <v/>
       </c>
       <c r="L45" s="6" t="str">
@@ -13237,15 +13375,15 @@
         <v/>
       </c>
       <c r="I46" s="6" t="str">
-        <f aca="false">IF($B46&lt;&gt;"B","",IFERROR(IF($D46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$D46,1)),0))</f>
+        <f aca="false">IF($B46&lt;&gt;"B","",IFERROR(IF($D46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$D46,1)),0))</f>
         <v/>
       </c>
       <c r="J46" s="6" t="str">
-        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
+        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
         <v/>
       </c>
       <c r="K46" s="6" t="str">
-        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
+        <f aca="false">IF($B46&lt;&gt;"C","",IFERROR(IF($E46="B",IF($D46=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C46,'B Made'!$A$5:$A$104,0)))/$D46,1)),IF($O46=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C46,'A Loose'!$A$5:$A$104,0)))/$O46,1))),0))</f>
         <v/>
       </c>
       <c r="L46" s="6" t="str">
@@ -13287,15 +13425,15 @@
         <v/>
       </c>
       <c r="I47" s="6" t="str">
-        <f aca="false">IF($B47&lt;&gt;"B","",IFERROR(IF($D47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$D47,1)),0))</f>
+        <f aca="false">IF($B47&lt;&gt;"B","",IFERROR(IF($D47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$D47,1)),0))</f>
         <v/>
       </c>
       <c r="J47" s="6" t="str">
-        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
+        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
         <v/>
       </c>
       <c r="K47" s="6" t="str">
-        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
+        <f aca="false">IF($B47&lt;&gt;"C","",IFERROR(IF($E47="B",IF($D47=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C47,'B Made'!$A$5:$A$104,0)))/$D47,1)),IF($O47=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C47,'A Loose'!$A$5:$A$104,0)))/$O47,1))),0))</f>
         <v/>
       </c>
       <c r="L47" s="6" t="str">
@@ -13337,15 +13475,15 @@
         <v/>
       </c>
       <c r="I48" s="6" t="str">
-        <f aca="false">IF($B48&lt;&gt;"B","",IFERROR(IF($D48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$D48,1)),0))</f>
+        <f aca="false">IF($B48&lt;&gt;"B","",IFERROR(IF($D48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$D48,1)),0))</f>
         <v/>
       </c>
       <c r="J48" s="6" t="str">
-        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
+        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
         <v/>
       </c>
       <c r="K48" s="6" t="str">
-        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
+        <f aca="false">IF($B48&lt;&gt;"C","",IFERROR(IF($E48="B",IF($D48=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C48,'B Made'!$A$5:$A$104,0)))/$D48,1)),IF($O48=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C48,'A Loose'!$A$5:$A$104,0)))/$O48,1))),0))</f>
         <v/>
       </c>
       <c r="L48" s="6" t="str">
@@ -13387,15 +13525,15 @@
         <v/>
       </c>
       <c r="I49" s="6" t="str">
-        <f aca="false">IF($B49&lt;&gt;"B","",IFERROR(IF($D49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$D49,1)),0))</f>
+        <f aca="false">IF($B49&lt;&gt;"B","",IFERROR(IF($D49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$D49,1)),0))</f>
         <v/>
       </c>
       <c r="J49" s="6" t="str">
-        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
+        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
         <v/>
       </c>
       <c r="K49" s="6" t="str">
-        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
+        <f aca="false">IF($B49&lt;&gt;"C","",IFERROR(IF($E49="B",IF($D49=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C49,'B Made'!$A$5:$A$104,0)))/$D49,1)),IF($O49=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C49,'A Loose'!$A$5:$A$104,0)))/$O49,1))),0))</f>
         <v/>
       </c>
       <c r="L49" s="6" t="str">
@@ -13437,15 +13575,15 @@
         <v/>
       </c>
       <c r="I50" s="6" t="str">
-        <f aca="false">IF($B50&lt;&gt;"B","",IFERROR(IF($D50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$D50,1)),0))</f>
+        <f aca="false">IF($B50&lt;&gt;"B","",IFERROR(IF($D50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$D50,1)),0))</f>
         <v/>
       </c>
       <c r="J50" s="6" t="str">
-        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
+        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
         <v/>
       </c>
       <c r="K50" s="6" t="str">
-        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
+        <f aca="false">IF($B50&lt;&gt;"C","",IFERROR(IF($E50="B",IF($D50=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C50,'B Made'!$A$5:$A$104,0)))/$D50,1)),IF($O50=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C50,'A Loose'!$A$5:$A$104,0)))/$O50,1))),0))</f>
         <v/>
       </c>
       <c r="L50" s="6" t="str">
@@ -13487,15 +13625,15 @@
         <v/>
       </c>
       <c r="I51" s="6" t="str">
-        <f aca="false">IF($B51&lt;&gt;"B","",IFERROR(IF($D51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$D51,1)),0))</f>
+        <f aca="false">IF($B51&lt;&gt;"B","",IFERROR(IF($D51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$D51,1)),0))</f>
         <v/>
       </c>
       <c r="J51" s="6" t="str">
-        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
+        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
         <v/>
       </c>
       <c r="K51" s="6" t="str">
-        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
+        <f aca="false">IF($B51&lt;&gt;"C","",IFERROR(IF($E51="B",IF($D51=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C51,'B Made'!$A$5:$A$104,0)))/$D51,1)),IF($O51=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C51,'A Loose'!$A$5:$A$104,0)))/$O51,1))),0))</f>
         <v/>
       </c>
       <c r="L51" s="6" t="str">
@@ -13537,15 +13675,15 @@
         <v/>
       </c>
       <c r="I52" s="6" t="str">
-        <f aca="false">IF($B52&lt;&gt;"B","",IFERROR(IF($D52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$D52,1)),0))</f>
+        <f aca="false">IF($B52&lt;&gt;"B","",IFERROR(IF($D52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$D52,1)),0))</f>
         <v/>
       </c>
       <c r="J52" s="6" t="str">
-        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
+        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
         <v/>
       </c>
       <c r="K52" s="6" t="str">
-        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
+        <f aca="false">IF($B52&lt;&gt;"C","",IFERROR(IF($E52="B",IF($D52=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C52,'B Made'!$A$5:$A$104,0)))/$D52,1)),IF($O52=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C52,'A Loose'!$A$5:$A$104,0)))/$O52,1))),0))</f>
         <v/>
       </c>
       <c r="L52" s="6" t="str">
@@ -13587,15 +13725,15 @@
         <v/>
       </c>
       <c r="I53" s="6" t="str">
-        <f aca="false">IF($B53&lt;&gt;"B","",IFERROR(IF($D53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$D53,1)),0))</f>
+        <f aca="false">IF($B53&lt;&gt;"B","",IFERROR(IF($D53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$D53,1)),0))</f>
         <v/>
       </c>
       <c r="J53" s="6" t="str">
-        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
+        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
         <v/>
       </c>
       <c r="K53" s="6" t="str">
-        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
+        <f aca="false">IF($B53&lt;&gt;"C","",IFERROR(IF($E53="B",IF($D53=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C53,'B Made'!$A$5:$A$104,0)))/$D53,1)),IF($O53=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C53,'A Loose'!$A$5:$A$104,0)))/$O53,1))),0))</f>
         <v/>
       </c>
       <c r="L53" s="6" t="str">
@@ -13637,15 +13775,15 @@
         <v/>
       </c>
       <c r="I54" s="6" t="str">
-        <f aca="false">IF($B54&lt;&gt;"B","",IFERROR(IF($D54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$D54,1)),0))</f>
+        <f aca="false">IF($B54&lt;&gt;"B","",IFERROR(IF($D54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$D54,1)),0))</f>
         <v/>
       </c>
       <c r="J54" s="6" t="str">
-        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
+        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
         <v/>
       </c>
       <c r="K54" s="6" t="str">
-        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
+        <f aca="false">IF($B54&lt;&gt;"C","",IFERROR(IF($E54="B",IF($D54=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C54,'B Made'!$A$5:$A$104,0)))/$D54,1)),IF($O54=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C54,'A Loose'!$A$5:$A$104,0)))/$O54,1))),0))</f>
         <v/>
       </c>
       <c r="L54" s="6" t="str">
@@ -13687,15 +13825,15 @@
         <v/>
       </c>
       <c r="I55" s="6" t="str">
-        <f aca="false">IF($B55&lt;&gt;"B","",IFERROR(IF($D55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$D55,1)),0))</f>
+        <f aca="false">IF($B55&lt;&gt;"B","",IFERROR(IF($D55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$D55,1)),0))</f>
         <v/>
       </c>
       <c r="J55" s="6" t="str">
-        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
+        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
         <v/>
       </c>
       <c r="K55" s="6" t="str">
-        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
+        <f aca="false">IF($B55&lt;&gt;"C","",IFERROR(IF($E55="B",IF($D55=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C55,'B Made'!$A$5:$A$104,0)))/$D55,1)),IF($O55=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C55,'A Loose'!$A$5:$A$104,0)))/$O55,1))),0))</f>
         <v/>
       </c>
       <c r="L55" s="6" t="str">
@@ -13737,15 +13875,15 @@
         <v/>
       </c>
       <c r="I56" s="6" t="str">
-        <f aca="false">IF($B56&lt;&gt;"B","",IFERROR(IF($D56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$D56,1)),0))</f>
+        <f aca="false">IF($B56&lt;&gt;"B","",IFERROR(IF($D56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$D56,1)),0))</f>
         <v/>
       </c>
       <c r="J56" s="6" t="str">
-        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
+        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
         <v/>
       </c>
       <c r="K56" s="6" t="str">
-        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
+        <f aca="false">IF($B56&lt;&gt;"C","",IFERROR(IF($E56="B",IF($D56=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C56,'B Made'!$A$5:$A$104,0)))/$D56,1)),IF($O56=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C56,'A Loose'!$A$5:$A$104,0)))/$O56,1))),0))</f>
         <v/>
       </c>
       <c r="L56" s="6" t="str">
@@ -13787,15 +13925,15 @@
         <v/>
       </c>
       <c r="I57" s="6" t="str">
-        <f aca="false">IF($B57&lt;&gt;"B","",IFERROR(IF($D57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$D57,1)),0))</f>
+        <f aca="false">IF($B57&lt;&gt;"B","",IFERROR(IF($D57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$D57,1)),0))</f>
         <v/>
       </c>
       <c r="J57" s="6" t="str">
-        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
+        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
         <v/>
       </c>
       <c r="K57" s="6" t="str">
-        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
+        <f aca="false">IF($B57&lt;&gt;"C","",IFERROR(IF($E57="B",IF($D57=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C57,'B Made'!$A$5:$A$104,0)))/$D57,1)),IF($O57=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C57,'A Loose'!$A$5:$A$104,0)))/$O57,1))),0))</f>
         <v/>
       </c>
       <c r="L57" s="6" t="str">
@@ -13837,15 +13975,15 @@
         <v/>
       </c>
       <c r="I58" s="6" t="str">
-        <f aca="false">IF($B58&lt;&gt;"B","",IFERROR(IF($D58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$D58,1)),0))</f>
+        <f aca="false">IF($B58&lt;&gt;"B","",IFERROR(IF($D58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$D58,1)),0))</f>
         <v/>
       </c>
       <c r="J58" s="6" t="str">
-        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
+        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
         <v/>
       </c>
       <c r="K58" s="6" t="str">
-        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
+        <f aca="false">IF($B58&lt;&gt;"C","",IFERROR(IF($E58="B",IF($D58=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C58,'B Made'!$A$5:$A$104,0)))/$D58,1)),IF($O58=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C58,'A Loose'!$A$5:$A$104,0)))/$O58,1))),0))</f>
         <v/>
       </c>
       <c r="L58" s="6" t="str">
@@ -13887,15 +14025,15 @@
         <v/>
       </c>
       <c r="I59" s="6" t="str">
-        <f aca="false">IF($B59&lt;&gt;"B","",IFERROR(IF($D59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$D59,1)),0))</f>
+        <f aca="false">IF($B59&lt;&gt;"B","",IFERROR(IF($D59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$D59,1)),0))</f>
         <v/>
       </c>
       <c r="J59" s="6" t="str">
-        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
+        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
         <v/>
       </c>
       <c r="K59" s="6" t="str">
-        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
+        <f aca="false">IF($B59&lt;&gt;"C","",IFERROR(IF($E59="B",IF($D59=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C59,'B Made'!$A$5:$A$104,0)))/$D59,1)),IF($O59=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C59,'A Loose'!$A$5:$A$104,0)))/$O59,1))),0))</f>
         <v/>
       </c>
       <c r="L59" s="6" t="str">
@@ -13937,15 +14075,15 @@
         <v/>
       </c>
       <c r="I60" s="6" t="str">
-        <f aca="false">IF($B60&lt;&gt;"B","",IFERROR(IF($D60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$D60,1)),0))</f>
+        <f aca="false">IF($B60&lt;&gt;"B","",IFERROR(IF($D60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$D60,1)),0))</f>
         <v/>
       </c>
       <c r="J60" s="6" t="str">
-        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
+        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
         <v/>
       </c>
       <c r="K60" s="6" t="str">
-        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
+        <f aca="false">IF($B60&lt;&gt;"C","",IFERROR(IF($E60="B",IF($D60=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C60,'B Made'!$A$5:$A$104,0)))/$D60,1)),IF($O60=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C60,'A Loose'!$A$5:$A$104,0)))/$O60,1))),0))</f>
         <v/>
       </c>
       <c r="L60" s="6" t="str">
@@ -13987,15 +14125,15 @@
         <v/>
       </c>
       <c r="I61" s="6" t="str">
-        <f aca="false">IF($B61&lt;&gt;"B","",IFERROR(IF($D61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$D61,1)),0))</f>
+        <f aca="false">IF($B61&lt;&gt;"B","",IFERROR(IF($D61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$D61,1)),0))</f>
         <v/>
       </c>
       <c r="J61" s="6" t="str">
-        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
+        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
         <v/>
       </c>
       <c r="K61" s="6" t="str">
-        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
+        <f aca="false">IF($B61&lt;&gt;"C","",IFERROR(IF($E61="B",IF($D61=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C61,'B Made'!$A$5:$A$104,0)))/$D61,1)),IF($O61=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C61,'A Loose'!$A$5:$A$104,0)))/$O61,1))),0))</f>
         <v/>
       </c>
       <c r="L61" s="6" t="str">
@@ -14037,15 +14175,15 @@
         <v/>
       </c>
       <c r="I62" s="6" t="str">
-        <f aca="false">IF($B62&lt;&gt;"B","",IFERROR(IF($D62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$D62,1)),0))</f>
+        <f aca="false">IF($B62&lt;&gt;"B","",IFERROR(IF($D62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$D62,1)),0))</f>
         <v/>
       </c>
       <c r="J62" s="6" t="str">
-        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
+        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
         <v/>
       </c>
       <c r="K62" s="6" t="str">
-        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
+        <f aca="false">IF($B62&lt;&gt;"C","",IFERROR(IF($E62="B",IF($D62=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C62,'B Made'!$A$5:$A$104,0)))/$D62,1)),IF($O62=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C62,'A Loose'!$A$5:$A$104,0)))/$O62,1))),0))</f>
         <v/>
       </c>
       <c r="L62" s="6" t="str">
@@ -14087,15 +14225,15 @@
         <v/>
       </c>
       <c r="I63" s="6" t="str">
-        <f aca="false">IF($B63&lt;&gt;"B","",IFERROR(IF($D63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$D63,1)),0))</f>
+        <f aca="false">IF($B63&lt;&gt;"B","",IFERROR(IF($D63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$D63,1)),0))</f>
         <v/>
       </c>
       <c r="J63" s="6" t="str">
-        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
+        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
         <v/>
       </c>
       <c r="K63" s="6" t="str">
-        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
+        <f aca="false">IF($B63&lt;&gt;"C","",IFERROR(IF($E63="B",IF($D63=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C63,'B Made'!$A$5:$A$104,0)))/$D63,1)),IF($O63=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C63,'A Loose'!$A$5:$A$104,0)))/$O63,1))),0))</f>
         <v/>
       </c>
       <c r="L63" s="6" t="str">
@@ -14137,15 +14275,15 @@
         <v/>
       </c>
       <c r="I64" s="6" t="str">
-        <f aca="false">IF($B64&lt;&gt;"B","",IFERROR(IF($D64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$D64,1)),0))</f>
+        <f aca="false">IF($B64&lt;&gt;"B","",IFERROR(IF($D64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$D64,1)),0))</f>
         <v/>
       </c>
       <c r="J64" s="6" t="str">
-        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
+        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
         <v/>
       </c>
       <c r="K64" s="6" t="str">
-        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
+        <f aca="false">IF($B64&lt;&gt;"C","",IFERROR(IF($E64="B",IF($D64=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C64,'B Made'!$A$5:$A$104,0)))/$D64,1)),IF($O64=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C64,'A Loose'!$A$5:$A$104,0)))/$O64,1))),0))</f>
         <v/>
       </c>
       <c r="L64" s="6" t="str">
@@ -14187,15 +14325,15 @@
         <v/>
       </c>
       <c r="I65" s="6" t="str">
-        <f aca="false">IF($B65&lt;&gt;"B","",IFERROR(IF($D65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$D65,1)),0))</f>
+        <f aca="false">IF($B65&lt;&gt;"B","",IFERROR(IF($D65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$D65,1)),0))</f>
         <v/>
       </c>
       <c r="J65" s="6" t="str">
-        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
+        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
         <v/>
       </c>
       <c r="K65" s="6" t="str">
-        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
+        <f aca="false">IF($B65&lt;&gt;"C","",IFERROR(IF($E65="B",IF($D65=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C65,'B Made'!$A$5:$A$104,0)))/$D65,1)),IF($O65=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C65,'A Loose'!$A$5:$A$104,0)))/$O65,1))),0))</f>
         <v/>
       </c>
       <c r="L65" s="6" t="str">
@@ -14237,15 +14375,15 @@
         <v/>
       </c>
       <c r="I66" s="6" t="str">
-        <f aca="false">IF($B66&lt;&gt;"B","",IFERROR(IF($D66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$D66,1)),0))</f>
+        <f aca="false">IF($B66&lt;&gt;"B","",IFERROR(IF($D66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$D66,1)),0))</f>
         <v/>
       </c>
       <c r="J66" s="6" t="str">
-        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
+        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
         <v/>
       </c>
       <c r="K66" s="6" t="str">
-        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
+        <f aca="false">IF($B66&lt;&gt;"C","",IFERROR(IF($E66="B",IF($D66=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C66,'B Made'!$A$5:$A$104,0)))/$D66,1)),IF($O66=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C66,'A Loose'!$A$5:$A$104,0)))/$O66,1))),0))</f>
         <v/>
       </c>
       <c r="L66" s="6" t="str">
@@ -14287,15 +14425,15 @@
         <v/>
       </c>
       <c r="I67" s="6" t="str">
-        <f aca="false">IF($B67&lt;&gt;"B","",IFERROR(IF($D67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$D67,1)),0))</f>
+        <f aca="false">IF($B67&lt;&gt;"B","",IFERROR(IF($D67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$D67,1)),0))</f>
         <v/>
       </c>
       <c r="J67" s="6" t="str">
-        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
+        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
         <v/>
       </c>
       <c r="K67" s="6" t="str">
-        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
+        <f aca="false">IF($B67&lt;&gt;"C","",IFERROR(IF($E67="B",IF($D67=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C67,'B Made'!$A$5:$A$104,0)))/$D67,1)),IF($O67=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C67,'A Loose'!$A$5:$A$104,0)))/$O67,1))),0))</f>
         <v/>
       </c>
       <c r="L67" s="6" t="str">
@@ -14337,15 +14475,15 @@
         <v/>
       </c>
       <c r="I68" s="6" t="str">
-        <f aca="false">IF($B68&lt;&gt;"B","",IFERROR(IF($D68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$D68,1)),0))</f>
+        <f aca="false">IF($B68&lt;&gt;"B","",IFERROR(IF($D68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$D68,1)),0))</f>
         <v/>
       </c>
       <c r="J68" s="6" t="str">
-        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
+        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
         <v/>
       </c>
       <c r="K68" s="6" t="str">
-        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
+        <f aca="false">IF($B68&lt;&gt;"C","",IFERROR(IF($E68="B",IF($D68=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C68,'B Made'!$A$5:$A$104,0)))/$D68,1)),IF($O68=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C68,'A Loose'!$A$5:$A$104,0)))/$O68,1))),0))</f>
         <v/>
       </c>
       <c r="L68" s="6" t="str">
@@ -14387,15 +14525,15 @@
         <v/>
       </c>
       <c r="I69" s="6" t="str">
-        <f aca="false">IF($B69&lt;&gt;"B","",IFERROR(IF($D69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$D69,1)),0))</f>
+        <f aca="false">IF($B69&lt;&gt;"B","",IFERROR(IF($D69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$D69,1)),0))</f>
         <v/>
       </c>
       <c r="J69" s="6" t="str">
-        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
+        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
         <v/>
       </c>
       <c r="K69" s="6" t="str">
-        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
+        <f aca="false">IF($B69&lt;&gt;"C","",IFERROR(IF($E69="B",IF($D69=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C69,'B Made'!$A$5:$A$104,0)))/$D69,1)),IF($O69=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C69,'A Loose'!$A$5:$A$104,0)))/$O69,1))),0))</f>
         <v/>
       </c>
       <c r="L69" s="6" t="str">
@@ -14437,15 +14575,15 @@
         <v/>
       </c>
       <c r="I70" s="6" t="str">
-        <f aca="false">IF($B70&lt;&gt;"B","",IFERROR(IF($D70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$D70,1)),0))</f>
+        <f aca="false">IF($B70&lt;&gt;"B","",IFERROR(IF($D70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$D70,1)),0))</f>
         <v/>
       </c>
       <c r="J70" s="6" t="str">
-        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
+        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
         <v/>
       </c>
       <c r="K70" s="6" t="str">
-        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
+        <f aca="false">IF($B70&lt;&gt;"C","",IFERROR(IF($E70="B",IF($D70=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C70,'B Made'!$A$5:$A$104,0)))/$D70,1)),IF($O70=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C70,'A Loose'!$A$5:$A$104,0)))/$O70,1))),0))</f>
         <v/>
       </c>
       <c r="L70" s="6" t="str">
@@ -14487,15 +14625,15 @@
         <v/>
       </c>
       <c r="I71" s="6" t="str">
-        <f aca="false">IF($B71&lt;&gt;"B","",IFERROR(IF($D71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$D71,1)),0))</f>
+        <f aca="false">IF($B71&lt;&gt;"B","",IFERROR(IF($D71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$D71,1)),0))</f>
         <v/>
       </c>
       <c r="J71" s="6" t="str">
-        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
+        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
         <v/>
       </c>
       <c r="K71" s="6" t="str">
-        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
+        <f aca="false">IF($B71&lt;&gt;"C","",IFERROR(IF($E71="B",IF($D71=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C71,'B Made'!$A$5:$A$104,0)))/$D71,1)),IF($O71=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C71,'A Loose'!$A$5:$A$104,0)))/$O71,1))),0))</f>
         <v/>
       </c>
       <c r="L71" s="6" t="str">
@@ -14537,15 +14675,15 @@
         <v/>
       </c>
       <c r="I72" s="6" t="str">
-        <f aca="false">IF($B72&lt;&gt;"B","",IFERROR(IF($D72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$D72,1)),0))</f>
+        <f aca="false">IF($B72&lt;&gt;"B","",IFERROR(IF($D72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$D72,1)),0))</f>
         <v/>
       </c>
       <c r="J72" s="6" t="str">
-        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
+        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
         <v/>
       </c>
       <c r="K72" s="6" t="str">
-        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
+        <f aca="false">IF($B72&lt;&gt;"C","",IFERROR(IF($E72="B",IF($D72=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C72,'B Made'!$A$5:$A$104,0)))/$D72,1)),IF($O72=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C72,'A Loose'!$A$5:$A$104,0)))/$O72,1))),0))</f>
         <v/>
       </c>
       <c r="L72" s="6" t="str">
@@ -14587,15 +14725,15 @@
         <v/>
       </c>
       <c r="I73" s="6" t="str">
-        <f aca="false">IF($B73&lt;&gt;"B","",IFERROR(IF($D73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$D73,1)),0))</f>
+        <f aca="false">IF($B73&lt;&gt;"B","",IFERROR(IF($D73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$D73,1)),0))</f>
         <v/>
       </c>
       <c r="J73" s="6" t="str">
-        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
+        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
         <v/>
       </c>
       <c r="K73" s="6" t="str">
-        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
+        <f aca="false">IF($B73&lt;&gt;"C","",IFERROR(IF($E73="B",IF($D73=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C73,'B Made'!$A$5:$A$104,0)))/$D73,1)),IF($O73=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C73,'A Loose'!$A$5:$A$104,0)))/$O73,1))),0))</f>
         <v/>
       </c>
       <c r="L73" s="6" t="str">
@@ -14637,15 +14775,15 @@
         <v/>
       </c>
       <c r="I74" s="6" t="str">
-        <f aca="false">IF($B74&lt;&gt;"B","",IFERROR(IF($D74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$D74,1)),0))</f>
+        <f aca="false">IF($B74&lt;&gt;"B","",IFERROR(IF($D74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$D74,1)),0))</f>
         <v/>
       </c>
       <c r="J74" s="6" t="str">
-        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
+        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
         <v/>
       </c>
       <c r="K74" s="6" t="str">
-        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
+        <f aca="false">IF($B74&lt;&gt;"C","",IFERROR(IF($E74="B",IF($D74=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C74,'B Made'!$A$5:$A$104,0)))/$D74,1)),IF($O74=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C74,'A Loose'!$A$5:$A$104,0)))/$O74,1))),0))</f>
         <v/>
       </c>
       <c r="L74" s="6" t="str">
@@ -14687,15 +14825,15 @@
         <v/>
       </c>
       <c r="I75" s="6" t="str">
-        <f aca="false">IF($B75&lt;&gt;"B","",IFERROR(IF($D75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$D75,1)),0))</f>
+        <f aca="false">IF($B75&lt;&gt;"B","",IFERROR(IF($D75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$D75,1)),0))</f>
         <v/>
       </c>
       <c r="J75" s="6" t="str">
-        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
+        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
         <v/>
       </c>
       <c r="K75" s="6" t="str">
-        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
+        <f aca="false">IF($B75&lt;&gt;"C","",IFERROR(IF($E75="B",IF($D75=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C75,'B Made'!$A$5:$A$104,0)))/$D75,1)),IF($O75=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C75,'A Loose'!$A$5:$A$104,0)))/$O75,1))),0))</f>
         <v/>
       </c>
       <c r="L75" s="6" t="str">
@@ -14737,15 +14875,15 @@
         <v/>
       </c>
       <c r="I76" s="6" t="str">
-        <f aca="false">IF($B76&lt;&gt;"B","",IFERROR(IF($D76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$D76,1)),0))</f>
+        <f aca="false">IF($B76&lt;&gt;"B","",IFERROR(IF($D76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$D76,1)),0))</f>
         <v/>
       </c>
       <c r="J76" s="6" t="str">
-        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
+        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
         <v/>
       </c>
       <c r="K76" s="6" t="str">
-        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
+        <f aca="false">IF($B76&lt;&gt;"C","",IFERROR(IF($E76="B",IF($D76=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C76,'B Made'!$A$5:$A$104,0)))/$D76,1)),IF($O76=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C76,'A Loose'!$A$5:$A$104,0)))/$O76,1))),0))</f>
         <v/>
       </c>
       <c r="L76" s="6" t="str">
@@ -14787,15 +14925,15 @@
         <v/>
       </c>
       <c r="I77" s="6" t="str">
-        <f aca="false">IF($B77&lt;&gt;"B","",IFERROR(IF($D77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$D77,1)),0))</f>
+        <f aca="false">IF($B77&lt;&gt;"B","",IFERROR(IF($D77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$D77,1)),0))</f>
         <v/>
       </c>
       <c r="J77" s="6" t="str">
-        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
+        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
         <v/>
       </c>
       <c r="K77" s="6" t="str">
-        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
+        <f aca="false">IF($B77&lt;&gt;"C","",IFERROR(IF($E77="B",IF($D77=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C77,'B Made'!$A$5:$A$104,0)))/$D77,1)),IF($O77=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C77,'A Loose'!$A$5:$A$104,0)))/$O77,1))),0))</f>
         <v/>
       </c>
       <c r="L77" s="6" t="str">
@@ -14837,15 +14975,15 @@
         <v/>
       </c>
       <c r="I78" s="6" t="str">
-        <f aca="false">IF($B78&lt;&gt;"B","",IFERROR(IF($D78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$D78,1)),0))</f>
+        <f aca="false">IF($B78&lt;&gt;"B","",IFERROR(IF($D78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$D78,1)),0))</f>
         <v/>
       </c>
       <c r="J78" s="6" t="str">
-        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
+        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
         <v/>
       </c>
       <c r="K78" s="6" t="str">
-        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
+        <f aca="false">IF($B78&lt;&gt;"C","",IFERROR(IF($E78="B",IF($D78=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C78,'B Made'!$A$5:$A$104,0)))/$D78,1)),IF($O78=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C78,'A Loose'!$A$5:$A$104,0)))/$O78,1))),0))</f>
         <v/>
       </c>
       <c r="L78" s="6" t="str">
@@ -14887,15 +15025,15 @@
         <v/>
       </c>
       <c r="I79" s="6" t="str">
-        <f aca="false">IF($B79&lt;&gt;"B","",IFERROR(IF($D79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$D79,1)),0))</f>
+        <f aca="false">IF($B79&lt;&gt;"B","",IFERROR(IF($D79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$D79,1)),0))</f>
         <v/>
       </c>
       <c r="J79" s="6" t="str">
-        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
+        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
         <v/>
       </c>
       <c r="K79" s="6" t="str">
-        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
+        <f aca="false">IF($B79&lt;&gt;"C","",IFERROR(IF($E79="B",IF($D79=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C79,'B Made'!$A$5:$A$104,0)))/$D79,1)),IF($O79=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C79,'A Loose'!$A$5:$A$104,0)))/$O79,1))),0))</f>
         <v/>
       </c>
       <c r="L79" s="6" t="str">
@@ -14937,15 +15075,15 @@
         <v/>
       </c>
       <c r="I80" s="6" t="str">
-        <f aca="false">IF($B80&lt;&gt;"B","",IFERROR(IF($D80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$D80,1)),0))</f>
+        <f aca="false">IF($B80&lt;&gt;"B","",IFERROR(IF($D80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$D80,1)),0))</f>
         <v/>
       </c>
       <c r="J80" s="6" t="str">
-        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
+        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
         <v/>
       </c>
       <c r="K80" s="6" t="str">
-        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
+        <f aca="false">IF($B80&lt;&gt;"C","",IFERROR(IF($E80="B",IF($D80=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C80,'B Made'!$A$5:$A$104,0)))/$D80,1)),IF($O80=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C80,'A Loose'!$A$5:$A$104,0)))/$O80,1))),0))</f>
         <v/>
       </c>
       <c r="L80" s="6" t="str">
@@ -14987,15 +15125,15 @@
         <v/>
       </c>
       <c r="I81" s="6" t="str">
-        <f aca="false">IF($B81&lt;&gt;"B","",IFERROR(IF($D81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$D81,1)),0))</f>
+        <f aca="false">IF($B81&lt;&gt;"B","",IFERROR(IF($D81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$D81,1)),0))</f>
         <v/>
       </c>
       <c r="J81" s="6" t="str">
-        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
+        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
         <v/>
       </c>
       <c r="K81" s="6" t="str">
-        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
+        <f aca="false">IF($B81&lt;&gt;"C","",IFERROR(IF($E81="B",IF($D81=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C81,'B Made'!$A$5:$A$104,0)))/$D81,1)),IF($O81=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C81,'A Loose'!$A$5:$A$104,0)))/$O81,1))),0))</f>
         <v/>
       </c>
       <c r="L81" s="6" t="str">
@@ -15037,15 +15175,15 @@
         <v/>
       </c>
       <c r="I82" s="6" t="str">
-        <f aca="false">IF($B82&lt;&gt;"B","",IFERROR(IF($D82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$D82,1)),0))</f>
+        <f aca="false">IF($B82&lt;&gt;"B","",IFERROR(IF($D82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$D82,1)),0))</f>
         <v/>
       </c>
       <c r="J82" s="6" t="str">
-        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
+        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
         <v/>
       </c>
       <c r="K82" s="6" t="str">
-        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
+        <f aca="false">IF($B82&lt;&gt;"C","",IFERROR(IF($E82="B",IF($D82=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C82,'B Made'!$A$5:$A$104,0)))/$D82,1)),IF($O82=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C82,'A Loose'!$A$5:$A$104,0)))/$O82,1))),0))</f>
         <v/>
       </c>
       <c r="L82" s="6" t="str">
@@ -15087,15 +15225,15 @@
         <v/>
       </c>
       <c r="I83" s="6" t="str">
-        <f aca="false">IF($B83&lt;&gt;"B","",IFERROR(IF($D83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$D83,1)),0))</f>
+        <f aca="false">IF($B83&lt;&gt;"B","",IFERROR(IF($D83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$D83,1)),0))</f>
         <v/>
       </c>
       <c r="J83" s="6" t="str">
-        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
+        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
         <v/>
       </c>
       <c r="K83" s="6" t="str">
-        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
+        <f aca="false">IF($B83&lt;&gt;"C","",IFERROR(IF($E83="B",IF($D83=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C83,'B Made'!$A$5:$A$104,0)))/$D83,1)),IF($O83=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C83,'A Loose'!$A$5:$A$104,0)))/$O83,1))),0))</f>
         <v/>
       </c>
       <c r="L83" s="6" t="str">
@@ -15137,15 +15275,15 @@
         <v/>
       </c>
       <c r="I84" s="6" t="str">
-        <f aca="false">IF($B84&lt;&gt;"B","",IFERROR(IF($D84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$D84,1)),0))</f>
+        <f aca="false">IF($B84&lt;&gt;"B","",IFERROR(IF($D84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$D84,1)),0))</f>
         <v/>
       </c>
       <c r="J84" s="6" t="str">
-        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
+        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
         <v/>
       </c>
       <c r="K84" s="6" t="str">
-        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
+        <f aca="false">IF($B84&lt;&gt;"C","",IFERROR(IF($E84="B",IF($D84=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C84,'B Made'!$A$5:$A$104,0)))/$D84,1)),IF($O84=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C84,'A Loose'!$A$5:$A$104,0)))/$O84,1))),0))</f>
         <v/>
       </c>
       <c r="L84" s="6" t="str">
@@ -15187,15 +15325,15 @@
         <v/>
       </c>
       <c r="I85" s="6" t="str">
-        <f aca="false">IF($B85&lt;&gt;"B","",IFERROR(IF($D85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$D85,1)),0))</f>
+        <f aca="false">IF($B85&lt;&gt;"B","",IFERROR(IF($D85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$D85,1)),0))</f>
         <v/>
       </c>
       <c r="J85" s="6" t="str">
-        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
+        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
         <v/>
       </c>
       <c r="K85" s="6" t="str">
-        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
+        <f aca="false">IF($B85&lt;&gt;"C","",IFERROR(IF($E85="B",IF($D85=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C85,'B Made'!$A$5:$A$104,0)))/$D85,1)),IF($O85=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C85,'A Loose'!$A$5:$A$104,0)))/$O85,1))),0))</f>
         <v/>
       </c>
       <c r="L85" s="6" t="str">
@@ -15237,15 +15375,15 @@
         <v/>
       </c>
       <c r="I86" s="6" t="str">
-        <f aca="false">IF($B86&lt;&gt;"B","",IFERROR(IF($D86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$D86,1)),0))</f>
+        <f aca="false">IF($B86&lt;&gt;"B","",IFERROR(IF($D86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$D86,1)),0))</f>
         <v/>
       </c>
       <c r="J86" s="6" t="str">
-        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
+        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
         <v/>
       </c>
       <c r="K86" s="6" t="str">
-        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
+        <f aca="false">IF($B86&lt;&gt;"C","",IFERROR(IF($E86="B",IF($D86=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C86,'B Made'!$A$5:$A$104,0)))/$D86,1)),IF($O86=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C86,'A Loose'!$A$5:$A$104,0)))/$O86,1))),0))</f>
         <v/>
       </c>
       <c r="L86" s="6" t="str">
@@ -15287,15 +15425,15 @@
         <v/>
       </c>
       <c r="I87" s="6" t="str">
-        <f aca="false">IF($B87&lt;&gt;"B","",IFERROR(IF($D87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$D87,1)),0))</f>
+        <f aca="false">IF($B87&lt;&gt;"B","",IFERROR(IF($D87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$D87,1)),0))</f>
         <v/>
       </c>
       <c r="J87" s="6" t="str">
-        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
+        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
         <v/>
       </c>
       <c r="K87" s="6" t="str">
-        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
+        <f aca="false">IF($B87&lt;&gt;"C","",IFERROR(IF($E87="B",IF($D87=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C87,'B Made'!$A$5:$A$104,0)))/$D87,1)),IF($O87=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C87,'A Loose'!$A$5:$A$104,0)))/$O87,1))),0))</f>
         <v/>
       </c>
       <c r="L87" s="6" t="str">
@@ -15337,15 +15475,15 @@
         <v/>
       </c>
       <c r="I88" s="6" t="str">
-        <f aca="false">IF($B88&lt;&gt;"B","",IFERROR(IF($D88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$D88,1)),0))</f>
+        <f aca="false">IF($B88&lt;&gt;"B","",IFERROR(IF($D88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$D88,1)),0))</f>
         <v/>
       </c>
       <c r="J88" s="6" t="str">
-        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
+        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
         <v/>
       </c>
       <c r="K88" s="6" t="str">
-        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
+        <f aca="false">IF($B88&lt;&gt;"C","",IFERROR(IF($E88="B",IF($D88=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C88,'B Made'!$A$5:$A$104,0)))/$D88,1)),IF($O88=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C88,'A Loose'!$A$5:$A$104,0)))/$O88,1))),0))</f>
         <v/>
       </c>
       <c r="L88" s="6" t="str">
@@ -15387,15 +15525,15 @@
         <v/>
       </c>
       <c r="I89" s="6" t="str">
-        <f aca="false">IF($B89&lt;&gt;"B","",IFERROR(IF($D89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$D89,1)),0))</f>
+        <f aca="false">IF($B89&lt;&gt;"B","",IFERROR(IF($D89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$D89,1)),0))</f>
         <v/>
       </c>
       <c r="J89" s="6" t="str">
-        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
+        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
         <v/>
       </c>
       <c r="K89" s="6" t="str">
-        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
+        <f aca="false">IF($B89&lt;&gt;"C","",IFERROR(IF($E89="B",IF($D89=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C89,'B Made'!$A$5:$A$104,0)))/$D89,1)),IF($O89=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C89,'A Loose'!$A$5:$A$104,0)))/$O89,1))),0))</f>
         <v/>
       </c>
       <c r="L89" s="6" t="str">
@@ -15437,15 +15575,15 @@
         <v/>
       </c>
       <c r="I90" s="6" t="str">
-        <f aca="false">IF($B90&lt;&gt;"B","",IFERROR(IF($D90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$D90,1)),0))</f>
+        <f aca="false">IF($B90&lt;&gt;"B","",IFERROR(IF($D90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$D90,1)),0))</f>
         <v/>
       </c>
       <c r="J90" s="6" t="str">
-        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
+        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
         <v/>
       </c>
       <c r="K90" s="6" t="str">
-        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
+        <f aca="false">IF($B90&lt;&gt;"C","",IFERROR(IF($E90="B",IF($D90=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C90,'B Made'!$A$5:$A$104,0)))/$D90,1)),IF($O90=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C90,'A Loose'!$A$5:$A$104,0)))/$O90,1))),0))</f>
         <v/>
       </c>
       <c r="L90" s="6" t="str">
@@ -15487,15 +15625,15 @@
         <v/>
       </c>
       <c r="I91" s="6" t="str">
-        <f aca="false">IF($B91&lt;&gt;"B","",IFERROR(IF($D91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$D91,1)),0))</f>
+        <f aca="false">IF($B91&lt;&gt;"B","",IFERROR(IF($D91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$D91,1)),0))</f>
         <v/>
       </c>
       <c r="J91" s="6" t="str">
-        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
+        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
         <v/>
       </c>
       <c r="K91" s="6" t="str">
-        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
+        <f aca="false">IF($B91&lt;&gt;"C","",IFERROR(IF($E91="B",IF($D91=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C91,'B Made'!$A$5:$A$104,0)))/$D91,1)),IF($O91=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C91,'A Loose'!$A$5:$A$104,0)))/$O91,1))),0))</f>
         <v/>
       </c>
       <c r="L91" s="6" t="str">
@@ -15537,15 +15675,15 @@
         <v/>
       </c>
       <c r="I92" s="6" t="str">
-        <f aca="false">IF($B92&lt;&gt;"B","",IFERROR(IF($D92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$D92,1)),0))</f>
+        <f aca="false">IF($B92&lt;&gt;"B","",IFERROR(IF($D92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$D92,1)),0))</f>
         <v/>
       </c>
       <c r="J92" s="6" t="str">
-        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
+        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
         <v/>
       </c>
       <c r="K92" s="6" t="str">
-        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
+        <f aca="false">IF($B92&lt;&gt;"C","",IFERROR(IF($E92="B",IF($D92=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C92,'B Made'!$A$5:$A$104,0)))/$D92,1)),IF($O92=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C92,'A Loose'!$A$5:$A$104,0)))/$O92,1))),0))</f>
         <v/>
       </c>
       <c r="L92" s="6" t="str">
@@ -15587,15 +15725,15 @@
         <v/>
       </c>
       <c r="I93" s="6" t="str">
-        <f aca="false">IF($B93&lt;&gt;"B","",IFERROR(IF($D93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$D93,1)),0))</f>
+        <f aca="false">IF($B93&lt;&gt;"B","",IFERROR(IF($D93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$D93,1)),0))</f>
         <v/>
       </c>
       <c r="J93" s="6" t="str">
-        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
+        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
         <v/>
       </c>
       <c r="K93" s="6" t="str">
-        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
+        <f aca="false">IF($B93&lt;&gt;"C","",IFERROR(IF($E93="B",IF($D93=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C93,'B Made'!$A$5:$A$104,0)))/$D93,1)),IF($O93=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C93,'A Loose'!$A$5:$A$104,0)))/$O93,1))),0))</f>
         <v/>
       </c>
       <c r="L93" s="6" t="str">
@@ -15637,15 +15775,15 @@
         <v/>
       </c>
       <c r="I94" s="6" t="str">
-        <f aca="false">IF($B94&lt;&gt;"B","",IFERROR(IF($D94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$D94,1)),0))</f>
+        <f aca="false">IF($B94&lt;&gt;"B","",IFERROR(IF($D94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$D94,1)),0))</f>
         <v/>
       </c>
       <c r="J94" s="6" t="str">
-        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
+        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
         <v/>
       </c>
       <c r="K94" s="6" t="str">
-        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
+        <f aca="false">IF($B94&lt;&gt;"C","",IFERROR(IF($E94="B",IF($D94=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C94,'B Made'!$A$5:$A$104,0)))/$D94,1)),IF($O94=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C94,'A Loose'!$A$5:$A$104,0)))/$O94,1))),0))</f>
         <v/>
       </c>
       <c r="L94" s="6" t="str">
@@ -15687,15 +15825,15 @@
         <v/>
       </c>
       <c r="I95" s="6" t="str">
-        <f aca="false">IF($B95&lt;&gt;"B","",IFERROR(IF($D95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$D95,1)),0))</f>
+        <f aca="false">IF($B95&lt;&gt;"B","",IFERROR(IF($D95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$D95,1)),0))</f>
         <v/>
       </c>
       <c r="J95" s="6" t="str">
-        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
+        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
         <v/>
       </c>
       <c r="K95" s="6" t="str">
-        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
+        <f aca="false">IF($B95&lt;&gt;"C","",IFERROR(IF($E95="B",IF($D95=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C95,'B Made'!$A$5:$A$104,0)))/$D95,1)),IF($O95=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C95,'A Loose'!$A$5:$A$104,0)))/$O95,1))),0))</f>
         <v/>
       </c>
       <c r="L95" s="6" t="str">
@@ -15737,15 +15875,15 @@
         <v/>
       </c>
       <c r="I96" s="6" t="str">
-        <f aca="false">IF($B96&lt;&gt;"B","",IFERROR(IF($D96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$D96,1)),0))</f>
+        <f aca="false">IF($B96&lt;&gt;"B","",IFERROR(IF($D96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$D96,1)),0))</f>
         <v/>
       </c>
       <c r="J96" s="6" t="str">
-        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
+        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
         <v/>
       </c>
       <c r="K96" s="6" t="str">
-        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
+        <f aca="false">IF($B96&lt;&gt;"C","",IFERROR(IF($E96="B",IF($D96=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C96,'B Made'!$A$5:$A$104,0)))/$D96,1)),IF($O96=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C96,'A Loose'!$A$5:$A$104,0)))/$O96,1))),0))</f>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
@@ -15787,15 +15925,15 @@
         <v/>
       </c>
       <c r="I97" s="6" t="str">
-        <f aca="false">IF($B97&lt;&gt;"B","",IFERROR(IF($D97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$D97,1)),0))</f>
+        <f aca="false">IF($B97&lt;&gt;"B","",IFERROR(IF($D97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$D97,1)),0))</f>
         <v/>
       </c>
       <c r="J97" s="6" t="str">
-        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
+        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
         <v/>
       </c>
       <c r="K97" s="6" t="str">
-        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
+        <f aca="false">IF($B97&lt;&gt;"C","",IFERROR(IF($E97="B",IF($D97=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C97,'B Made'!$A$5:$A$104,0)))/$D97,1)),IF($O97=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C97,'A Loose'!$A$5:$A$104,0)))/$O97,1))),0))</f>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
@@ -15837,15 +15975,15 @@
         <v/>
       </c>
       <c r="I98" s="6" t="str">
-        <f aca="false">IF($B98&lt;&gt;"B","",IFERROR(IF($D98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$D98,1)),0))</f>
+        <f aca="false">IF($B98&lt;&gt;"B","",IFERROR(IF($D98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$D98,1)),0))</f>
         <v/>
       </c>
       <c r="J98" s="6" t="str">
-        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
+        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
         <v/>
       </c>
       <c r="K98" s="6" t="str">
-        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
+        <f aca="false">IF($B98&lt;&gt;"C","",IFERROR(IF($E98="B",IF($D98=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C98,'B Made'!$A$5:$A$104,0)))/$D98,1)),IF($O98=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C98,'A Loose'!$A$5:$A$104,0)))/$O98,1))),0))</f>
         <v/>
       </c>
       <c r="L98" s="6" t="str">
@@ -15887,15 +16025,15 @@
         <v/>
       </c>
       <c r="I99" s="6" t="str">
-        <f aca="false">IF($B99&lt;&gt;"B","",IFERROR(IF($D99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$D99,1)),0))</f>
+        <f aca="false">IF($B99&lt;&gt;"B","",IFERROR(IF($D99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$D99,1)),0))</f>
         <v/>
       </c>
       <c r="J99" s="6" t="str">
-        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
+        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
         <v/>
       </c>
       <c r="K99" s="6" t="str">
-        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
+        <f aca="false">IF($B99&lt;&gt;"C","",IFERROR(IF($E99="B",IF($D99=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C99,'B Made'!$A$5:$A$104,0)))/$D99,1)),IF($O99=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C99,'A Loose'!$A$5:$A$104,0)))/$O99,1))),0))</f>
         <v/>
       </c>
       <c r="L99" s="6" t="str">
@@ -15937,15 +16075,15 @@
         <v/>
       </c>
       <c r="I100" s="6" t="str">
-        <f aca="false">IF($B100&lt;&gt;"B","",IFERROR(IF($D100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$D100,1)),0))</f>
+        <f aca="false">IF($B100&lt;&gt;"B","",IFERROR(IF($D100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$D100,1)),0))</f>
         <v/>
       </c>
       <c r="J100" s="6" t="str">
-        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
+        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
         <v/>
       </c>
       <c r="K100" s="6" t="str">
-        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
+        <f aca="false">IF($B100&lt;&gt;"C","",IFERROR(IF($E100="B",IF($D100=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C100,'B Made'!$A$5:$A$104,0)))/$D100,1)),IF($O100=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C100,'A Loose'!$A$5:$A$104,0)))/$O100,1))),0))</f>
         <v/>
       </c>
       <c r="L100" s="6" t="str">
@@ -15987,15 +16125,15 @@
         <v/>
       </c>
       <c r="I101" s="6" t="str">
-        <f aca="false">IF($B101&lt;&gt;"B","",IFERROR(IF($D101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$D101,1)),0))</f>
+        <f aca="false">IF($B101&lt;&gt;"B","",IFERROR(IF($D101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$D101,1)),0))</f>
         <v/>
       </c>
       <c r="J101" s="6" t="str">
-        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
+        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
         <v/>
       </c>
       <c r="K101" s="6" t="str">
-        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
+        <f aca="false">IF($B101&lt;&gt;"C","",IFERROR(IF($E101="B",IF($D101=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C101,'B Made'!$A$5:$A$104,0)))/$D101,1)),IF($O101=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C101,'A Loose'!$A$5:$A$104,0)))/$O101,1))),0))</f>
         <v/>
       </c>
       <c r="L101" s="6" t="str">
@@ -16037,15 +16175,15 @@
         <v/>
       </c>
       <c r="I102" s="6" t="str">
-        <f aca="false">IF($B102&lt;&gt;"B","",IFERROR(IF($D102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$D102,1)),0))</f>
+        <f aca="false">IF($B102&lt;&gt;"B","",IFERROR(IF($D102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$D102,1)),0))</f>
         <v/>
       </c>
       <c r="J102" s="6" t="str">
-        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
+        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
         <v/>
       </c>
       <c r="K102" s="6" t="str">
-        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
+        <f aca="false">IF($B102&lt;&gt;"C","",IFERROR(IF($E102="B",IF($D102=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C102,'B Made'!$A$5:$A$104,0)))/$D102,1)),IF($O102=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C102,'A Loose'!$A$5:$A$104,0)))/$O102,1))),0))</f>
         <v/>
       </c>
       <c r="L102" s="6" t="str">
@@ -16087,15 +16225,15 @@
         <v/>
       </c>
       <c r="I103" s="6" t="str">
-        <f aca="false">IF($B103&lt;&gt;"B","",IFERROR(IF($D103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$D103,1)),0))</f>
+        <f aca="false">IF($B103&lt;&gt;"B","",IFERROR(IF($D103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$D103,1)),0))</f>
         <v/>
       </c>
       <c r="J103" s="6" t="str">
-        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
+        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
         <v/>
       </c>
       <c r="K103" s="6" t="str">
-        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
+        <f aca="false">IF($B103&lt;&gt;"C","",IFERROR(IF($E103="B",IF($D103=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C103,'B Made'!$A$5:$A$104,0)))/$D103,1)),IF($O103=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C103,'A Loose'!$A$5:$A$104,0)))/$O103,1))),0))</f>
         <v/>
       </c>
       <c r="L103" s="6" t="str">
@@ -16137,15 +16275,15 @@
         <v/>
       </c>
       <c r="I104" s="6" t="str">
-        <f aca="false">IF($B104&lt;&gt;"B","",IFERROR(IF($D104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$D104,1)),0))</f>
+        <f aca="false">IF($B104&lt;&gt;"B","",IFERROR(IF($D104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$D104,1)),0))</f>
         <v/>
       </c>
       <c r="J104" s="6" t="str">
-        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
+        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$F$5:$F$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
         <v/>
       </c>
       <c r="K104" s="6" t="str">
-        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$J$5:$J$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
+        <f aca="false">IF($B104&lt;&gt;"C","",IFERROR(IF($E104="B",IF($D104=0,0,FLOOR(MAX(0,INDEX('B Made'!$I$5:$I$104,MATCH($C104,'B Made'!$A$5:$A$104,0)))/$D104,1)),IF($O104=0,0,FLOOR(MAX(0,INDEX('A Loose'!$K$5:$K$104,MATCH($C104,'A Loose'!$A$5:$A$104,0)))/$O104,1))),0))</f>
         <v/>
       </c>
       <c r="L104" s="6" t="str">
@@ -16198,29 +16336,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16228,16 +16366,16 @@
         <v>46235</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16245,16 +16383,16 @@
         <v>46239</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16262,16 +16400,16 @@
         <v>46254</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16279,16 +16417,16 @@
         <v>46256</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16296,16 +16434,16 @@
         <v>46259</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>-20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18407,48 +18545,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">IF($D5="","",IF($B$3="Can pack now",INDEX('C Kits'!$F$5:$F$104,MATCH($A5,'C Kits'!$C$5:$C$104,0)),INDEX('C Kits'!$G$5:$G$104,MATCH($A5,'C Kits'!$C$5:$C$104,0))))</f>
@@ -18473,7 +18611,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">IF($D6="","",IF($B$3="Can pack now",INDEX('C Kits'!$F$5:$F$104,MATCH($A6,'C Kits'!$C$5:$C$104,0)),INDEX('C Kits'!$G$5:$G$104,MATCH($A6,'C Kits'!$C$5:$C$104,0))))</f>
@@ -18498,7 +18636,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="5" t="str">
         <f aca="false">IF($D7="","",IF($B$3="Can pack now",INDEX('C Kits'!$F$5:$F$104,MATCH($A7,'C Kits'!$C$5:$C$104,0)),INDEX('C Kits'!$G$5:$G$104,MATCH($A7,'C Kits'!$C$5:$C$104,0))))</f>
